--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46066.32178303241</v>
+        <v>46066.48844969907</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55563092593</v>
+        <v>46092.7222975926</v>
       </c>
       <c r="D4" s="5">
-        <v>46109.57094042824</v>
+        <v>46109.73760709491</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46066.32178334491</v>
+        <v>46066.48845001157</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55560032408</v>
+        <v>46092.72226699074</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.71756133102</v>
+        <v>46133.88422799768</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1610,13 +1610,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46066.32178355324</v>
+        <v>46066.488450219906</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55560085648</v>
+        <v>46092.722267523146</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.555631469906</v>
+        <v>46092.72229813658</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1673,13 +1673,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46066.32178377315</v>
+        <v>46066.488450439814</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55560128472</v>
+        <v>46092.722267951394</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55563128472</v>
+        <v>46092.72229795139</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1736,13 +1736,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46066.32178399306</v>
+        <v>46066.48845065972</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55560170139</v>
+        <v>46092.72226836806</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.60722690972</v>
+        <v>46100.77389357639</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1799,13 +1799,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46066.321784201384</v>
+        <v>46066.488450868055</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55560238426</v>
+        <v>46092.72226905092</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55563133102</v>
+        <v>46092.72229799769</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1862,11 +1862,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46066.32178439815</v>
+        <v>46066.48845106481</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.376563125</v>
+        <v>46097.54322979167</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1909,13 +1909,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46066.32178462963</v>
+        <v>46066.488451296296</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.37655447917</v>
+        <v>46097.54322114583</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.376569224536</v>
+        <v>46097.54323589121</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1974,11 +1974,11 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46066.321784872685</v>
+        <v>46066.48845153935</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46155.00118040509</v>
+        <v>46155.16784707176</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2037,13 +2037,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46066.32178510417</v>
+        <v>46066.488451770834</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.35867421296</v>
+        <v>46114.52534087963</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.35870145833</v>
+        <v>46114.525368125</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2090,13 +2090,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46066.32178384259</v>
+        <v>46066.48845050926</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.376044143515</v>
+        <v>46097.54271081019</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.37605961805</v>
+        <v>46097.54272628472</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2155,13 +2155,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46066.321784432876</v>
+        <v>46066.48845109953</v>
       </c>
       <c r="C15" s="8">
-        <v>46113.40140357639</v>
+        <v>46113.568070243055</v>
       </c>
       <c r="D15" s="8">
-        <v>46113.40142040509</v>
+        <v>46113.56808707176</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2220,13 +2220,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46066.321784687505</v>
+        <v>46066.48845135416</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.35864662037</v>
+        <v>46114.52531328704</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.358664837964</v>
+        <v>46114.52533150463</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2285,13 +2285,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46066.321784942134</v>
+        <v>46066.48845160879</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.35865797454</v>
+        <v>46114.5253246412</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.3586750463</v>
+        <v>46114.525341712964</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2350,13 +2350,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46066.32178550926</v>
+        <v>46066.48845217592</v>
       </c>
       <c r="C18" s="5">
-        <v>46167.38724696759</v>
+        <v>46167.553913634256</v>
       </c>
       <c r="D18" s="5">
-        <v>46167.38726354166</v>
+        <v>46167.553930208334</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2403,13 +2403,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46066.32178576389</v>
+        <v>46066.48845243055</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.376137893516</v>
+        <v>46097.54280456019</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.37615408565</v>
+        <v>46097.542820752315</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2468,13 +2468,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46066.32178601852</v>
+        <v>46066.48845268518</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.35878704861</v>
+        <v>46114.52545371528</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.358918530095</v>
+        <v>46114.52558519676</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2533,13 +2533,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46066.32178626157</v>
+        <v>46066.48845292824</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.3766475463</v>
+        <v>46097.54331421296</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.37666384259</v>
+        <v>46097.54333050926</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2598,13 +2598,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46066.32178650463</v>
+        <v>46066.488453171296</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.46288748842</v>
+        <v>46122.62955415509</v>
       </c>
       <c r="D22" s="5">
-        <v>46122.46290511574</v>
+        <v>46122.62957178241</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2663,13 +2663,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46066.32178327546</v>
+        <v>46066.48844994213</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.35883915509</v>
+        <v>46114.52550582176</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.35885458333</v>
+        <v>46114.525521250005</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2728,13 +2728,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46066.32178359954</v>
+        <v>46066.4884502662</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.4567107176</v>
+        <v>46157.623377384254</v>
       </c>
       <c r="D24" s="5">
-        <v>46184.41484805556</v>
+        <v>46184.581514722224</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2793,13 +2793,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46066.321783865744</v>
+        <v>46066.48845053241</v>
       </c>
       <c r="C25" s="8">
-        <v>46184.40966138889</v>
+        <v>46184.576328055555</v>
       </c>
       <c r="D25" s="8">
-        <v>46184.40969197916</v>
+        <v>46184.576358645834</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2844,13 +2844,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46066.32178412037</v>
+        <v>46066.48845078704</v>
       </c>
       <c r="C26" s="5">
-        <v>46128.45954239584</v>
+        <v>46128.626209062495</v>
       </c>
       <c r="D26" s="5">
-        <v>46128.45958377315</v>
+        <v>46128.62625043982</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2909,13 +2909,13 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46066.321784375</v>
+        <v>46066.48845104167</v>
       </c>
       <c r="C27" s="8">
-        <v>46128.45956122685</v>
+        <v>46128.62622789352</v>
       </c>
       <c r="D27" s="8">
-        <v>46128.45980510417</v>
+        <v>46128.62647177083</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -2970,13 +2970,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46066.32178462963</v>
+        <v>46066.488451296296</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.459557766204</v>
+        <v>46128.62622443287</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.45957040509</v>
+        <v>46128.62623707176</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3031,13 +3031,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46066.32178486111</v>
+        <v>46066.48845152778</v>
       </c>
       <c r="C29" s="8">
-        <v>46182.51320083333</v>
+        <v>46182.6798675</v>
       </c>
       <c r="D29" s="8">
-        <v>46182.51323557871</v>
+        <v>46182.67990224537</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3096,13 +3096,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46066.32178510417</v>
+        <v>46066.488451770834</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.377011550925</v>
+        <v>46097.5436782176</v>
       </c>
       <c r="D30" s="5">
-        <v>46169.68102278935</v>
+        <v>46169.847689456015</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3157,11 +3157,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46066.321785381944</v>
+        <v>46066.48845204861</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46182.51323063657</v>
+        <v>46182.67989730324</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3216,13 +3216,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46066.32178565972</v>
+        <v>46066.48845232639</v>
       </c>
       <c r="C32" s="5">
-        <v>46126.69341158565</v>
+        <v>46126.86007825231</v>
       </c>
       <c r="D32" s="5">
-        <v>46126.69342440972</v>
+        <v>46126.86009107639</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3281,13 +3281,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46066.32178542824</v>
+        <v>46066.48845209491</v>
       </c>
       <c r="C33" s="8">
-        <v>46126.69293872685</v>
+        <v>46126.85960539352</v>
       </c>
       <c r="D33" s="8">
-        <v>46126.69293993055</v>
+        <v>46126.85960659722</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3342,13 +3342,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46066.32178599537</v>
+        <v>46066.48845266204</v>
       </c>
       <c r="C34" s="5">
-        <v>46126.6929933912</v>
+        <v>46126.859660057875</v>
       </c>
       <c r="D34" s="5">
-        <v>46126.69299459491</v>
+        <v>46126.85966126157</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3403,13 +3403,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46066.321786319444</v>
+        <v>46066.488452986116</v>
       </c>
       <c r="C35" s="8">
-        <v>46126.64103636574</v>
+        <v>46126.807703032406</v>
       </c>
       <c r="D35" s="8">
-        <v>46176.03135493056</v>
+        <v>46176.19802159722</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3468,13 +3468,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46066.32178665509</v>
+        <v>46066.488453321756</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.37621940972</v>
+        <v>46097.54288607639</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.37622104167</v>
+        <v>46097.54288770833</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3529,13 +3529,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46066.321786967594</v>
+        <v>46066.48845363426</v>
       </c>
       <c r="C37" s="8">
-        <v>46126.64102027778</v>
+        <v>46126.80768694445</v>
       </c>
       <c r="D37" s="8">
-        <v>46126.64102221065</v>
+        <v>46126.807688877314</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3590,13 +3590,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46066.321787361114</v>
+        <v>46066.48845402778</v>
       </c>
       <c r="C38" s="5">
-        <v>46114.35992371528</v>
+        <v>46114.526590381945</v>
       </c>
       <c r="D38" s="5">
-        <v>46114.359924965276</v>
+        <v>46114.52659163195</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3651,13 +3651,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46066.32178769676</v>
+        <v>46066.488454363425</v>
       </c>
       <c r="C39" s="8">
-        <v>46157.458965439815</v>
+        <v>46157.62563210649</v>
       </c>
       <c r="D39" s="8">
-        <v>46157.45898106482</v>
+        <v>46157.62564773148</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3716,13 +3716,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46066.32178804398</v>
+        <v>46066.48845471065</v>
       </c>
       <c r="C40" s="5">
-        <v>46157.456767800926</v>
+        <v>46157.62343446759</v>
       </c>
       <c r="D40" s="5">
-        <v>46157.45676883102</v>
+        <v>46157.623435497684</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3777,13 +3777,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46066.32178835648</v>
+        <v>46066.48845502315</v>
       </c>
       <c r="C41" s="8">
-        <v>46157.456836770834</v>
+        <v>46157.6235034375</v>
       </c>
       <c r="D41" s="8">
-        <v>46157.45683802084</v>
+        <v>46157.6235046875</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -3838,13 +3838,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46066.32178866898</v>
+        <v>46066.48845533565</v>
       </c>
       <c r="C42" s="5">
-        <v>46154.70064498842</v>
+        <v>46154.86731165509</v>
       </c>
       <c r="D42" s="5">
-        <v>46157.45958581018</v>
+        <v>46157.62625247685</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3903,13 +3903,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46066.32178486111</v>
+        <v>46066.48845152778</v>
       </c>
       <c r="C43" s="8">
-        <v>46154.70050896991</v>
+        <v>46154.86717563657</v>
       </c>
       <c r="D43" s="8">
-        <v>46154.70051097222</v>
+        <v>46154.86717763889</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3964,13 +3964,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46066.32178549768</v>
+        <v>46066.488452164354</v>
       </c>
       <c r="C44" s="5">
-        <v>46154.70058172454</v>
+        <v>46154.86724839121</v>
       </c>
       <c r="D44" s="5">
-        <v>46154.700582986115</v>
+        <v>46154.86724965277</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4025,11 +4025,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46066.32178594907</v>
+        <v>46066.48845261574</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46157.46663646991</v>
+        <v>46157.63330313658</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4072,13 +4072,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.587331793984</v>
+        <v>46070.75399846065</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.35973473379</v>
+        <v>46114.526401400464</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.359754062505</v>
+        <v>46114.52642072916</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4137,13 +4137,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46066.321786307875</v>
+        <v>46066.48845297453</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.35998150463</v>
+        <v>46114.5266481713</v>
       </c>
       <c r="D47" s="8">
-        <v>46114.359996643514</v>
+        <v>46114.526663310186</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>167</v>
@@ -4202,13 +4202,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.47779013889</v>
+        <v>46091.64445680556</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.36002435185</v>
+        <v>46114.52669101852</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.36003887732</v>
+        <v>46114.526705543976</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4265,11 +4265,11 @@
         <v>178</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.47783655093</v>
+        <v>46091.6445032176</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46184.04039730324</v>
+        <v>46184.20706396991</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>179</v>
@@ -4326,13 +4326,13 @@
         <v>182</v>
       </c>
       <c r="B50" s="5">
-        <v>46066.321786817134</v>
+        <v>46066.48845348379</v>
       </c>
       <c r="C50" s="5">
-        <v>46157.46662641204</v>
+        <v>46157.6332930787</v>
       </c>
       <c r="D50" s="5">
-        <v>46157.46671620371</v>
+        <v>46157.63338287037</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>183</v>
@@ -4375,13 +4375,13 @@
         <v>185</v>
       </c>
       <c r="B51" s="8">
-        <v>46066.321787256944</v>
+        <v>46066.48845392361</v>
       </c>
       <c r="C51" s="8">
-        <v>46157.45907391203</v>
+        <v>46157.625740578704</v>
       </c>
       <c r="D51" s="8">
-        <v>46157.459090335644</v>
+        <v>46157.625757002315</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>186</v>
@@ -4440,13 +4440,13 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46066.321787719906</v>
+        <v>46066.48845438658</v>
       </c>
       <c r="C52" s="5">
-        <v>46157.4666078125</v>
+        <v>46157.633274479165</v>
       </c>
       <c r="D52" s="5">
-        <v>46157.46662734954</v>
+        <v>46157.6332940162</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4505,11 +4505,11 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46066.321788113426</v>
+        <v>46066.48845478009</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46156.68656667824</v>
+        <v>46156.85323334491</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4552,11 +4552,11 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46066.32178854167</v>
+        <v>46066.48845520834</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46176.38907939815</v>
+        <v>46176.55574606481</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4615,11 +4615,11 @@
         <v>203</v>
       </c>
       <c r="B55" s="8">
-        <v>46066.321789050926</v>
+        <v>46066.4884557176</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46157.468873645834</v>
+        <v>46157.635540312505</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>204</v>
@@ -4678,11 +4678,11 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46066.321783865744</v>
+        <v>46066.48845053241</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46127.02794674769</v>
+        <v>46127.19461341435</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>208</v>
@@ -4741,11 +4741,11 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46066.32178423611</v>
+        <v>46066.488450902776</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46127.48855717592</v>
+        <v>46127.655223842594</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>183</v>
@@ -4788,11 +4788,11 @@
         <v>213</v>
       </c>
       <c r="B58" s="5">
-        <v>46066.32178452546</v>
+        <v>46066.48845119213</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46155.08366583333</v>
+        <v>46155.2503325</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4851,13 +4851,13 @@
         <v>216</v>
       </c>
       <c r="B59" s="8">
-        <v>46066.32178478009</v>
+        <v>46066.488451446756</v>
       </c>
       <c r="C59" s="8">
-        <v>46127.48844644676</v>
+        <v>46127.655113113426</v>
       </c>
       <c r="D59" s="8">
-        <v>46127.48846443287</v>
+        <v>46127.65513109954</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>217</v>
@@ -4916,13 +4916,13 @@
         <v>219</v>
       </c>
       <c r="B60" s="5">
-        <v>46066.321785057866</v>
+        <v>46066.48845172454</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.4885496875</v>
+        <v>46127.655216354164</v>
       </c>
       <c r="D60" s="5">
-        <v>46178.02050702546</v>
+        <v>46178.18717369213</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>220</v>
@@ -4981,11 +4981,11 @@
         <v>222</v>
       </c>
       <c r="B61" s="8">
-        <v>46066.3217853588</v>
+        <v>46066.48845202546</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46182.513236238425</v>
+        <v>46182.67990290509</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>55</v>
@@ -5044,11 +5044,11 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46066.32178564815</v>
+        <v>46066.488452314814</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46158.00271868055</v>
+        <v>46158.169385347224</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5107,11 +5107,11 @@
         <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46066.32178592593</v>
+        <v>46066.48845259259</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46091.488060625</v>
+        <v>46091.654727291665</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>228</v>
@@ -5154,11 +5154,11 @@
         <v>230</v>
       </c>
       <c r="B64" s="5">
-        <v>46066.321786203705</v>
+        <v>46066.48845287037</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46146.001646979166</v>
+        <v>46146.16831364583</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5217,11 +5217,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46066.32178646991</v>
+        <v>46066.488453136575</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46182.0022325</v>
+        <v>46182.16889916667</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5280,11 +5280,11 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46066.32178421297</v>
+        <v>46066.48845087963</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46158.00271916667</v>
+        <v>46158.16938583333</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>238</v>
@@ -5343,11 +5343,11 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46066.32178489583</v>
+        <v>46066.4884515625</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46162.03787155093</v>
+        <v>46162.20453821759</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5406,11 +5406,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46066.32178524305</v>
+        <v>46066.488451909725</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46165.00380186342</v>
+        <v>46165.170468530094</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5469,11 +5469,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46066.32178569444</v>
+        <v>46066.48845236111</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46183.02853340278</v>
+        <v>46183.195200069444</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>180</v>
@@ -5530,11 +5530,11 @@
         <v>248</v>
       </c>
       <c r="B70" s="5">
-        <v>46066.32178611111</v>
+        <v>46066.488452777776</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46185.00493481482</v>
+        <v>46185.17160148148</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>181</v>
@@ -5591,11 +5591,11 @@
         <v>250</v>
       </c>
       <c r="B71" s="8">
-        <v>46066.3217865162</v>
+        <v>46066.48845318287</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.4847465162</v>
+        <v>46091.65141318287</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>251</v>
@@ -5638,11 +5638,11 @@
         <v>253</v>
       </c>
       <c r="B72" s="5">
-        <v>46066.321786875</v>
+        <v>46066.488453541664</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46185.004934826386</v>
+        <v>46185.17160149306</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>249</v>
@@ -5701,11 +5701,11 @@
         <v>257</v>
       </c>
       <c r="B73" s="8">
-        <v>46066.32178724537</v>
+        <v>46066.48845391204</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46182.02030574074</v>
+        <v>46182.186972407406</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>258</v>
@@ -5764,11 +5764,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46066.32178759259</v>
+        <v>46066.48845425926</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46183.02539090278</v>
+        <v>46183.192057569446</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>262</v>
@@ -5827,11 +5827,11 @@
         <v>266</v>
       </c>
       <c r="B75" s="8">
-        <v>46066.321787928246</v>
+        <v>46066.4884545949</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46184.03658305555</v>
+        <v>46184.203249722224</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>267</v>
@@ -5890,11 +5890,11 @@
         <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46066.32178459491</v>
+        <v>46066.488451261575</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.484746145834</v>
+        <v>46091.6514128125</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>270</v>
@@ -5937,11 +5937,11 @@
         <v>272</v>
       </c>
       <c r="B77" s="8">
-        <v>46066.32178489583</v>
+        <v>46066.4884515625</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.358685520834</v>
+        <v>46114.5253521875</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>273</v>
@@ -6000,11 +6000,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46066.321785196764</v>
+        <v>46066.48845186342</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46091.496179444446</v>
+        <v>46091.66284611111</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6063,11 +6063,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.47794063657</v>
+        <v>46091.64460730324</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.48533783565</v>
+        <v>46091.65200450231</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6116,11 +6116,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.47832231481</v>
+        <v>46091.64498898148</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46091.529054583334</v>
+        <v>46091.69572125</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6179,11 +6179,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.47849136574</v>
+        <v>46091.64515803241</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46091.49624552083</v>
+        <v>46091.6629121875</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -5705,7 +5705,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46182.186972407406</v>
+        <v>46190.176506909724</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>258</v>
@@ -5752,8 +5752,8 @@
       <c r="S73" s="9">
         <v>0</v>
       </c>
-      <c r="T73" s="12" t="s">
-        <v>117</v>
+      <c r="T73" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="U73" s="10" t="s">
         <v>58</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -5768,7 +5768,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46183.192057569446</v>
+        <v>46191.17529449074</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>262</v>
@@ -5815,8 +5815,8 @@
       <c r="S74" s="6">
         <v>0</v>
       </c>
-      <c r="T74" s="12" t="s">
-        <v>117</v>
+      <c r="T74" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="U74" s="10" t="s">
         <v>58</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46176.55574606481</v>
+        <v>46191.783963043985</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46127.655223842594</v>
+        <v>46191.7832978125</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>183</v>
@@ -4790,9 +4790,11 @@
       <c r="B58" s="5">
         <v>46066.48845119213</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46191.78328978009</v>
+      </c>
       <c r="D58" s="5">
-        <v>46155.2503325</v>
+        <v>46191.783308530095</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4837,13 +4839,13 @@
         <v>46155</v>
       </c>
       <c r="S58" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="U58" s="12" t="s">
-        <v>107</v>
+      <c r="U58" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5048,7 +5050,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46158.169385347224</v>
+        <v>46191.784467627316</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5284,7 +5286,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46158.16938583333</v>
+        <v>46191.78329880787</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>238</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -3037,7 +3037,7 @@
         <v>46182.6798675</v>
       </c>
       <c r="D29" s="8">
-        <v>46182.67990224537</v>
+        <v>46191.90442258102</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46184.203249722224</v>
+        <v>46192.196944131945</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>267</v>
@@ -5880,8 +5880,8 @@
       <c r="S75" s="9">
         <v>0</v>
       </c>
-      <c r="T75" s="12" t="s">
-        <v>117</v>
+      <c r="T75" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="U75" s="10" t="s">
         <v>58</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46191.783963043985</v>
+        <v>46192.78649950231</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46191.784467627316</v>
+        <v>46192.78934293981</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -5943,7 +5943,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46114.5253521875</v>
+        <v>46195.205822268515</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>273</v>
@@ -5990,8 +5990,8 @@
       <c r="S77" s="9">
         <v>0</v>
       </c>
-      <c r="T77" s="11" t="s">
-        <v>57</v>
+      <c r="T77" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="U77" s="10" t="s">
         <v>58</v>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46091.66284611111</v>
+        <v>46195.20582737269</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6053,8 +6053,8 @@
       <c r="S78" s="6">
         <v>0</v>
       </c>
-      <c r="T78" s="11" t="s">
-        <v>57</v>
+      <c r="T78" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="U78" s="10" t="s">
         <v>58</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46146.16831364583</v>
+        <v>46195.596250057875</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46183.195200069444</v>
+        <v>46195.596534745375</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>180</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -4509,7 +4509,7 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46156.85323334491</v>
+        <v>46195.697430960645</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4554,9 +4554,11 @@
       <c r="B54" s="5">
         <v>46066.48845520834</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46195.69727907407</v>
+      </c>
       <c r="D54" s="5">
-        <v>46192.78649950231</v>
+        <v>46195.69729675926</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4601,13 +4603,13 @@
         <v>46104</v>
       </c>
       <c r="S54" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U54" s="12" t="s">
-        <v>107</v>
+      <c r="U54" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4619,7 +4621,7 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46157.635540312505</v>
+        <v>46195.70018221065</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>204</v>
@@ -4664,13 +4666,13 @@
         <v>46122</v>
       </c>
       <c r="S55" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U55" s="10" t="s">
-        <v>58</v>
+      <c r="U55" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4682,7 +4684,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46127.19461341435</v>
+        <v>46195.69743164352</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>208</v>
@@ -4732,8 +4734,8 @@
       <c r="T56" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U56" s="10" t="s">
-        <v>58</v>
+      <c r="U56" s="12" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -6124,7 +6124,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46091.69572125</v>
+        <v>46196.18589472222</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6171,8 +6171,8 @@
       <c r="S80" s="6">
         <v>0</v>
       </c>
-      <c r="T80" s="11" t="s">
-        <v>57</v>
+      <c r="T80" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="U80" s="10" t="s">
         <v>58</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -5162,7 +5162,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46195.596250057875</v>
+        <v>46196.59712994213</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.596534745375</v>
+        <v>46196.601929791665</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>180</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -5477,7 +5477,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46196.601929791665</v>
+        <v>46196.60710679398</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>180</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -5115,7 +5115,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46091.654727291665</v>
+        <v>46197.59005347222</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>228</v>
@@ -5286,9 +5286,11 @@
       <c r="B66" s="5">
         <v>46066.48845087963</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46197.590047060185</v>
+      </c>
       <c r="D66" s="5">
-        <v>46191.78329880787</v>
+        <v>46197.59006386574</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>238</v>
@@ -5333,13 +5335,13 @@
         <v>46157</v>
       </c>
       <c r="S66" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U66" s="10" t="s">
-        <v>58</v>
+      <c r="U66" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5477,7 +5479,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46196.60710679398</v>
+        <v>46197.59005303241</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>180</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46066.48844969907</v>
+        <v>46066.32178303241</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.7222975926</v>
+        <v>46092.55563092593</v>
       </c>
       <c r="D4" s="5">
-        <v>46109.73760709491</v>
+        <v>46109.57094042824</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46066.48845001157</v>
+        <v>46066.32178334491</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.72226699074</v>
+        <v>46092.55560032408</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.88422799768</v>
+        <v>46133.71756133102</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1610,13 +1610,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46066.488450219906</v>
+        <v>46066.32178355324</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.722267523146</v>
+        <v>46092.55560085648</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.72229813658</v>
+        <v>46092.555631469906</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1673,13 +1673,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46066.488450439814</v>
+        <v>46066.32178377315</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.722267951394</v>
+        <v>46092.55560128472</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72229795139</v>
+        <v>46092.55563128472</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1736,13 +1736,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46066.48845065972</v>
+        <v>46066.32178399306</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72226836806</v>
+        <v>46092.55560170139</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.77389357639</v>
+        <v>46100.60722690972</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1799,13 +1799,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46066.488450868055</v>
+        <v>46066.321784201384</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72226905092</v>
+        <v>46092.55560238426</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.72229799769</v>
+        <v>46092.55563133102</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1862,11 +1862,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46066.48845106481</v>
+        <v>46066.32178439815</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.54322979167</v>
+        <v>46097.376563125</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1909,13 +1909,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46066.488451296296</v>
+        <v>46066.32178462963</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.54322114583</v>
+        <v>46097.37655447917</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.54323589121</v>
+        <v>46097.376569224536</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1974,11 +1974,11 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46066.48845153935</v>
+        <v>46066.321784872685</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46155.16784707176</v>
+        <v>46155.00118040509</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2037,13 +2037,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46066.488451770834</v>
+        <v>46066.32178510417</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.52534087963</v>
+        <v>46114.35867421296</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.525368125</v>
+        <v>46114.35870145833</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2090,13 +2090,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46066.48845050926</v>
+        <v>46066.32178384259</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.54271081019</v>
+        <v>46097.376044143515</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.54272628472</v>
+        <v>46097.37605961805</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2155,13 +2155,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46066.48845109953</v>
+        <v>46066.321784432876</v>
       </c>
       <c r="C15" s="8">
-        <v>46113.568070243055</v>
+        <v>46113.40140357639</v>
       </c>
       <c r="D15" s="8">
-        <v>46113.56808707176</v>
+        <v>46113.40142040509</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2220,13 +2220,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46066.48845135416</v>
+        <v>46066.321784687505</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.52531328704</v>
+        <v>46114.35864662037</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.52533150463</v>
+        <v>46114.358664837964</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2285,13 +2285,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46066.48845160879</v>
+        <v>46066.321784942134</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.5253246412</v>
+        <v>46114.35865797454</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.525341712964</v>
+        <v>46114.3586750463</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2350,13 +2350,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46066.48845217592</v>
+        <v>46066.32178550926</v>
       </c>
       <c r="C18" s="5">
-        <v>46167.553913634256</v>
+        <v>46167.38724696759</v>
       </c>
       <c r="D18" s="5">
-        <v>46167.553930208334</v>
+        <v>46167.38726354166</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2403,13 +2403,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46066.48845243055</v>
+        <v>46066.32178576389</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.54280456019</v>
+        <v>46097.376137893516</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.542820752315</v>
+        <v>46097.37615408565</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2468,13 +2468,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46066.48845268518</v>
+        <v>46066.32178601852</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.52545371528</v>
+        <v>46114.35878704861</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.52558519676</v>
+        <v>46114.358918530095</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2533,13 +2533,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46066.48845292824</v>
+        <v>46066.32178626157</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.54331421296</v>
+        <v>46097.3766475463</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.54333050926</v>
+        <v>46097.37666384259</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2598,13 +2598,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46066.488453171296</v>
+        <v>46066.32178650463</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.62955415509</v>
+        <v>46122.46288748842</v>
       </c>
       <c r="D22" s="5">
-        <v>46122.62957178241</v>
+        <v>46122.46290511574</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2663,13 +2663,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46066.48844994213</v>
+        <v>46066.32178327546</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.52550582176</v>
+        <v>46114.35883915509</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.525521250005</v>
+        <v>46114.35885458333</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2728,13 +2728,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46066.4884502662</v>
+        <v>46066.32178359954</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.623377384254</v>
+        <v>46157.4567107176</v>
       </c>
       <c r="D24" s="5">
-        <v>46184.581514722224</v>
+        <v>46184.41484805556</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2793,13 +2793,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46066.48845053241</v>
+        <v>46066.321783865744</v>
       </c>
       <c r="C25" s="8">
-        <v>46184.576328055555</v>
+        <v>46184.40966138889</v>
       </c>
       <c r="D25" s="8">
-        <v>46184.576358645834</v>
+        <v>46184.40969197916</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2844,13 +2844,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46066.48845078704</v>
+        <v>46066.32178412037</v>
       </c>
       <c r="C26" s="5">
-        <v>46128.626209062495</v>
+        <v>46128.45954239584</v>
       </c>
       <c r="D26" s="5">
-        <v>46128.62625043982</v>
+        <v>46128.45958377315</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2909,13 +2909,13 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46066.48845104167</v>
+        <v>46066.321784375</v>
       </c>
       <c r="C27" s="8">
-        <v>46128.62622789352</v>
+        <v>46128.45956122685</v>
       </c>
       <c r="D27" s="8">
-        <v>46128.62647177083</v>
+        <v>46128.45980510417</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -2970,13 +2970,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46066.488451296296</v>
+        <v>46066.32178462963</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.62622443287</v>
+        <v>46128.459557766204</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.62623707176</v>
+        <v>46128.45957040509</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3031,13 +3031,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46066.48845152778</v>
+        <v>46066.32178486111</v>
       </c>
       <c r="C29" s="8">
-        <v>46182.6798675</v>
+        <v>46182.51320083333</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.90442258102</v>
+        <v>46191.73775591435</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3096,13 +3096,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46066.488451770834</v>
+        <v>46066.32178510417</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.5436782176</v>
+        <v>46097.377011550925</v>
       </c>
       <c r="D30" s="5">
-        <v>46169.847689456015</v>
+        <v>46169.68102278935</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3157,11 +3157,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46066.48845204861</v>
+        <v>46066.321785381944</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46182.67989730324</v>
+        <v>46182.51323063657</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3216,13 +3216,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46066.48845232639</v>
+        <v>46066.32178565972</v>
       </c>
       <c r="C32" s="5">
-        <v>46126.86007825231</v>
+        <v>46126.69341158565</v>
       </c>
       <c r="D32" s="5">
-        <v>46126.86009107639</v>
+        <v>46126.69342440972</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3281,13 +3281,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46066.48845209491</v>
+        <v>46066.32178542824</v>
       </c>
       <c r="C33" s="8">
-        <v>46126.85960539352</v>
+        <v>46126.69293872685</v>
       </c>
       <c r="D33" s="8">
-        <v>46126.85960659722</v>
+        <v>46126.69293993055</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3342,13 +3342,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46066.48845266204</v>
+        <v>46066.32178599537</v>
       </c>
       <c r="C34" s="5">
-        <v>46126.859660057875</v>
+        <v>46126.6929933912</v>
       </c>
       <c r="D34" s="5">
-        <v>46126.85966126157</v>
+        <v>46126.69299459491</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3403,13 +3403,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46066.488452986116</v>
+        <v>46066.321786319444</v>
       </c>
       <c r="C35" s="8">
-        <v>46126.807703032406</v>
+        <v>46126.64103636574</v>
       </c>
       <c r="D35" s="8">
-        <v>46176.19802159722</v>
+        <v>46176.03135493056</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3468,13 +3468,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46066.488453321756</v>
+        <v>46066.32178665509</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.54288607639</v>
+        <v>46097.37621940972</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.54288770833</v>
+        <v>46097.37622104167</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3529,13 +3529,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46066.48845363426</v>
+        <v>46066.321786967594</v>
       </c>
       <c r="C37" s="8">
-        <v>46126.80768694445</v>
+        <v>46126.64102027778</v>
       </c>
       <c r="D37" s="8">
-        <v>46126.807688877314</v>
+        <v>46126.64102221065</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3590,13 +3590,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46066.48845402778</v>
+        <v>46066.321787361114</v>
       </c>
       <c r="C38" s="5">
-        <v>46114.526590381945</v>
+        <v>46114.35992371528</v>
       </c>
       <c r="D38" s="5">
-        <v>46114.52659163195</v>
+        <v>46114.359924965276</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3651,13 +3651,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46066.488454363425</v>
+        <v>46066.32178769676</v>
       </c>
       <c r="C39" s="8">
-        <v>46157.62563210649</v>
+        <v>46157.458965439815</v>
       </c>
       <c r="D39" s="8">
-        <v>46157.62564773148</v>
+        <v>46157.45898106482</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3716,13 +3716,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46066.48845471065</v>
+        <v>46066.32178804398</v>
       </c>
       <c r="C40" s="5">
-        <v>46157.62343446759</v>
+        <v>46157.456767800926</v>
       </c>
       <c r="D40" s="5">
-        <v>46157.623435497684</v>
+        <v>46157.45676883102</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3777,13 +3777,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46066.48845502315</v>
+        <v>46066.32178835648</v>
       </c>
       <c r="C41" s="8">
-        <v>46157.6235034375</v>
+        <v>46157.456836770834</v>
       </c>
       <c r="D41" s="8">
-        <v>46157.6235046875</v>
+        <v>46157.45683802084</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -3838,13 +3838,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46066.48845533565</v>
+        <v>46066.32178866898</v>
       </c>
       <c r="C42" s="5">
-        <v>46154.86731165509</v>
+        <v>46154.70064498842</v>
       </c>
       <c r="D42" s="5">
-        <v>46157.62625247685</v>
+        <v>46157.45958581018</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3903,13 +3903,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46066.48845152778</v>
+        <v>46066.32178486111</v>
       </c>
       <c r="C43" s="8">
-        <v>46154.86717563657</v>
+        <v>46154.70050896991</v>
       </c>
       <c r="D43" s="8">
-        <v>46154.86717763889</v>
+        <v>46154.70051097222</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3964,13 +3964,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46066.488452164354</v>
+        <v>46066.32178549768</v>
       </c>
       <c r="C44" s="5">
-        <v>46154.86724839121</v>
+        <v>46154.70058172454</v>
       </c>
       <c r="D44" s="5">
-        <v>46154.86724965277</v>
+        <v>46154.700582986115</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4025,11 +4025,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46066.48845261574</v>
+        <v>46066.32178594907</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46157.63330313658</v>
+        <v>46157.46663646991</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4072,13 +4072,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.75399846065</v>
+        <v>46070.587331793984</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.526401400464</v>
+        <v>46114.35973473379</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.52642072916</v>
+        <v>46114.359754062505</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4137,13 +4137,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46066.48845297453</v>
+        <v>46066.321786307875</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.5266481713</v>
+        <v>46114.35998150463</v>
       </c>
       <c r="D47" s="8">
-        <v>46114.526663310186</v>
+        <v>46114.359996643514</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>167</v>
@@ -4202,13 +4202,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.64445680556</v>
+        <v>46091.47779013889</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.52669101852</v>
+        <v>46114.36002435185</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.526705543976</v>
+        <v>46114.36003887732</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4265,11 +4265,11 @@
         <v>178</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.6445032176</v>
+        <v>46091.47783655093</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46184.20706396991</v>
+        <v>46184.04039730324</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>179</v>
@@ -4326,13 +4326,13 @@
         <v>182</v>
       </c>
       <c r="B50" s="5">
-        <v>46066.48845348379</v>
+        <v>46066.321786817134</v>
       </c>
       <c r="C50" s="5">
-        <v>46157.6332930787</v>
+        <v>46157.46662641204</v>
       </c>
       <c r="D50" s="5">
-        <v>46157.63338287037</v>
+        <v>46157.46671620371</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>183</v>
@@ -4375,13 +4375,13 @@
         <v>185</v>
       </c>
       <c r="B51" s="8">
-        <v>46066.48845392361</v>
+        <v>46066.321787256944</v>
       </c>
       <c r="C51" s="8">
-        <v>46157.625740578704</v>
+        <v>46157.45907391203</v>
       </c>
       <c r="D51" s="8">
-        <v>46157.625757002315</v>
+        <v>46157.459090335644</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>186</v>
@@ -4440,13 +4440,13 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46066.48845438658</v>
+        <v>46066.321787719906</v>
       </c>
       <c r="C52" s="5">
-        <v>46157.633274479165</v>
+        <v>46157.4666078125</v>
       </c>
       <c r="D52" s="5">
-        <v>46157.6332940162</v>
+        <v>46157.46662734954</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4505,11 +4505,11 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46066.48845478009</v>
+        <v>46066.321788113426</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.697430960645</v>
+        <v>46195.53076429398</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4552,13 +4552,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46066.48845520834</v>
+        <v>46066.32178854167</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.69727907407</v>
+        <v>46195.53061240741</v>
       </c>
       <c r="D54" s="5">
-        <v>46195.69729675926</v>
+        <v>46195.53063009259</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4617,11 +4617,11 @@
         <v>203</v>
       </c>
       <c r="B55" s="8">
-        <v>46066.4884557176</v>
+        <v>46066.321789050926</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.70018221065</v>
+        <v>46195.53351554398</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>204</v>
@@ -4680,11 +4680,11 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46066.48845053241</v>
+        <v>46066.321783865744</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.69743164352</v>
+        <v>46195.53076497685</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>208</v>
@@ -4743,11 +4743,11 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46066.488450902776</v>
+        <v>46066.32178423611</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.7832978125</v>
+        <v>46191.61663114584</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>183</v>
@@ -4790,13 +4790,13 @@
         <v>213</v>
       </c>
       <c r="B58" s="5">
-        <v>46066.48845119213</v>
+        <v>46066.32178452546</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.78328978009</v>
+        <v>46191.61662311343</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.783308530095</v>
+        <v>46191.616641863424</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4855,13 +4855,13 @@
         <v>216</v>
       </c>
       <c r="B59" s="8">
-        <v>46066.488451446756</v>
+        <v>46066.32178478009</v>
       </c>
       <c r="C59" s="8">
-        <v>46127.655113113426</v>
+        <v>46127.48844644676</v>
       </c>
       <c r="D59" s="8">
-        <v>46127.65513109954</v>
+        <v>46127.48846443287</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>217</v>
@@ -4920,13 +4920,13 @@
         <v>219</v>
       </c>
       <c r="B60" s="5">
-        <v>46066.48845172454</v>
+        <v>46066.321785057866</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.655216354164</v>
+        <v>46127.4885496875</v>
       </c>
       <c r="D60" s="5">
-        <v>46178.18717369213</v>
+        <v>46178.02050702546</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>220</v>
@@ -4985,11 +4985,11 @@
         <v>222</v>
       </c>
       <c r="B61" s="8">
-        <v>46066.48845202546</v>
+        <v>46066.3217853588</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46182.67990290509</v>
+        <v>46182.513236238425</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>55</v>
@@ -5048,11 +5048,11 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46066.488452314814</v>
+        <v>46066.32178564815</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46192.78934293981</v>
+        <v>46192.62267627315</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5111,11 +5111,11 @@
         <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46066.48845259259</v>
+        <v>46066.32178592593</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46197.59005347222</v>
+        <v>46197.42338680556</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>228</v>
@@ -5158,11 +5158,11 @@
         <v>230</v>
       </c>
       <c r="B64" s="5">
-        <v>46066.48845287037</v>
+        <v>46066.321786203705</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46196.59712994213</v>
+        <v>46196.430463275465</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5221,11 +5221,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46066.488453136575</v>
+        <v>46066.32178646991</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46182.16889916667</v>
+        <v>46182.0022325</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5284,13 +5284,13 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46066.48845087963</v>
+        <v>46066.32178421297</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.590047060185</v>
+        <v>46197.42338039352</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.59006386574</v>
+        <v>46197.423397199076</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>238</v>
@@ -5349,11 +5349,11 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46066.4884515625</v>
+        <v>46066.32178489583</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46162.20453821759</v>
+        <v>46162.03787155093</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5412,11 +5412,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46066.488451909725</v>
+        <v>46066.32178524305</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46165.170468530094</v>
+        <v>46165.00380186342</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5475,11 +5475,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46066.48845236111</v>
+        <v>46066.32178569444</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.59005303241</v>
+        <v>46197.42338636574</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>180</v>
@@ -5536,11 +5536,11 @@
         <v>248</v>
       </c>
       <c r="B70" s="5">
-        <v>46066.488452777776</v>
+        <v>46066.32178611111</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46185.17160148148</v>
+        <v>46185.00493481482</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>181</v>
@@ -5597,11 +5597,11 @@
         <v>250</v>
       </c>
       <c r="B71" s="8">
-        <v>46066.48845318287</v>
+        <v>46066.3217865162</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.65141318287</v>
+        <v>46091.4847465162</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>251</v>
@@ -5644,11 +5644,11 @@
         <v>253</v>
       </c>
       <c r="B72" s="5">
-        <v>46066.488453541664</v>
+        <v>46066.321786875</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46185.17160149306</v>
+        <v>46185.004934826386</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>249</v>
@@ -5707,11 +5707,11 @@
         <v>257</v>
       </c>
       <c r="B73" s="8">
-        <v>46066.48845391204</v>
+        <v>46066.32178724537</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46190.176506909724</v>
+        <v>46190.00984024306</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>258</v>
@@ -5770,11 +5770,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46066.48845425926</v>
+        <v>46066.32178759259</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46191.17529449074</v>
+        <v>46191.00862782408</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>262</v>
@@ -5833,11 +5833,11 @@
         <v>266</v>
       </c>
       <c r="B75" s="8">
-        <v>46066.4884545949</v>
+        <v>46066.321787928246</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46192.196944131945</v>
+        <v>46192.03027746528</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>267</v>
@@ -5896,11 +5896,11 @@
         <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46066.488451261575</v>
+        <v>46066.32178459491</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.6514128125</v>
+        <v>46091.484746145834</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>270</v>
@@ -5943,11 +5943,11 @@
         <v>272</v>
       </c>
       <c r="B77" s="8">
-        <v>46066.4884515625</v>
+        <v>46066.32178489583</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.205822268515</v>
+        <v>46195.03915560185</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>273</v>
@@ -6006,11 +6006,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46066.48845186342</v>
+        <v>46066.321785196764</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.20582737269</v>
+        <v>46195.039160706016</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6069,11 +6069,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.64460730324</v>
+        <v>46091.47794063657</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.65200450231</v>
+        <v>46091.48533783565</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6122,11 +6122,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.64498898148</v>
+        <v>46091.47832231481</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46196.18589472222</v>
+        <v>46196.01922805556</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6185,11 +6185,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.64515803241</v>
+        <v>46091.47849136574</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46091.6629121875</v>
+        <v>46091.49624552083</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46066.32178303241</v>
+        <v>46066.48844969907</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55563092593</v>
+        <v>46092.7222975926</v>
       </c>
       <c r="D4" s="5">
-        <v>46109.57094042824</v>
+        <v>46109.73760709491</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46066.32178334491</v>
+        <v>46066.48845001157</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55560032408</v>
+        <v>46092.72226699074</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.71756133102</v>
+        <v>46133.88422799768</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1610,13 +1610,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46066.32178355324</v>
+        <v>46066.488450219906</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55560085648</v>
+        <v>46092.722267523146</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.555631469906</v>
+        <v>46092.72229813658</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1673,13 +1673,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46066.32178377315</v>
+        <v>46066.488450439814</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55560128472</v>
+        <v>46092.722267951394</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55563128472</v>
+        <v>46092.72229795139</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1736,13 +1736,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46066.32178399306</v>
+        <v>46066.48845065972</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55560170139</v>
+        <v>46092.72226836806</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.60722690972</v>
+        <v>46100.77389357639</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1799,13 +1799,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46066.321784201384</v>
+        <v>46066.488450868055</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55560238426</v>
+        <v>46092.72226905092</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55563133102</v>
+        <v>46092.72229799769</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1862,11 +1862,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46066.32178439815</v>
+        <v>46066.48845106481</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.376563125</v>
+        <v>46097.54322979167</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1909,13 +1909,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46066.32178462963</v>
+        <v>46066.488451296296</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.37655447917</v>
+        <v>46097.54322114583</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.376569224536</v>
+        <v>46097.54323589121</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1974,11 +1974,11 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46066.321784872685</v>
+        <v>46066.48845153935</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46155.00118040509</v>
+        <v>46155.16784707176</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2037,13 +2037,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46066.32178510417</v>
+        <v>46066.488451770834</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.35867421296</v>
+        <v>46114.52534087963</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.35870145833</v>
+        <v>46114.525368125</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2090,13 +2090,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46066.32178384259</v>
+        <v>46066.48845050926</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.376044143515</v>
+        <v>46097.54271081019</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.37605961805</v>
+        <v>46097.54272628472</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2155,13 +2155,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46066.321784432876</v>
+        <v>46066.48845109953</v>
       </c>
       <c r="C15" s="8">
-        <v>46113.40140357639</v>
+        <v>46113.568070243055</v>
       </c>
       <c r="D15" s="8">
-        <v>46113.40142040509</v>
+        <v>46113.56808707176</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2220,13 +2220,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46066.321784687505</v>
+        <v>46066.48845135416</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.35864662037</v>
+        <v>46114.52531328704</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.358664837964</v>
+        <v>46114.52533150463</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2285,13 +2285,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46066.321784942134</v>
+        <v>46066.48845160879</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.35865797454</v>
+        <v>46114.5253246412</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.3586750463</v>
+        <v>46114.525341712964</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2350,13 +2350,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46066.32178550926</v>
+        <v>46066.48845217592</v>
       </c>
       <c r="C18" s="5">
-        <v>46167.38724696759</v>
+        <v>46167.553913634256</v>
       </c>
       <c r="D18" s="5">
-        <v>46167.38726354166</v>
+        <v>46167.553930208334</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2403,13 +2403,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46066.32178576389</v>
+        <v>46066.48845243055</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.376137893516</v>
+        <v>46097.54280456019</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.37615408565</v>
+        <v>46097.542820752315</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2468,13 +2468,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46066.32178601852</v>
+        <v>46066.48845268518</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.35878704861</v>
+        <v>46114.52545371528</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.358918530095</v>
+        <v>46114.52558519676</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2533,13 +2533,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46066.32178626157</v>
+        <v>46066.48845292824</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.3766475463</v>
+        <v>46097.54331421296</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.37666384259</v>
+        <v>46097.54333050926</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2598,13 +2598,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46066.32178650463</v>
+        <v>46066.488453171296</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.46288748842</v>
+        <v>46122.62955415509</v>
       </c>
       <c r="D22" s="5">
-        <v>46122.46290511574</v>
+        <v>46122.62957178241</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2663,13 +2663,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46066.32178327546</v>
+        <v>46066.48844994213</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.35883915509</v>
+        <v>46114.52550582176</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.35885458333</v>
+        <v>46114.525521250005</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2728,13 +2728,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46066.32178359954</v>
+        <v>46066.4884502662</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.4567107176</v>
+        <v>46157.623377384254</v>
       </c>
       <c r="D24" s="5">
-        <v>46184.41484805556</v>
+        <v>46184.581514722224</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2793,13 +2793,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46066.321783865744</v>
+        <v>46066.48845053241</v>
       </c>
       <c r="C25" s="8">
-        <v>46184.40966138889</v>
+        <v>46184.576328055555</v>
       </c>
       <c r="D25" s="8">
-        <v>46184.40969197916</v>
+        <v>46184.576358645834</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2844,13 +2844,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46066.32178412037</v>
+        <v>46066.48845078704</v>
       </c>
       <c r="C26" s="5">
-        <v>46128.45954239584</v>
+        <v>46128.626209062495</v>
       </c>
       <c r="D26" s="5">
-        <v>46128.45958377315</v>
+        <v>46128.62625043982</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2909,13 +2909,13 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46066.321784375</v>
+        <v>46066.48845104167</v>
       </c>
       <c r="C27" s="8">
-        <v>46128.45956122685</v>
+        <v>46128.62622789352</v>
       </c>
       <c r="D27" s="8">
-        <v>46128.45980510417</v>
+        <v>46128.62647177083</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -2970,13 +2970,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46066.32178462963</v>
+        <v>46066.488451296296</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.459557766204</v>
+        <v>46128.62622443287</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.45957040509</v>
+        <v>46128.62623707176</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3031,13 +3031,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46066.32178486111</v>
+        <v>46066.48845152778</v>
       </c>
       <c r="C29" s="8">
-        <v>46182.51320083333</v>
+        <v>46182.6798675</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.73775591435</v>
+        <v>46191.90442258102</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3096,13 +3096,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46066.32178510417</v>
+        <v>46066.488451770834</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.377011550925</v>
+        <v>46097.5436782176</v>
       </c>
       <c r="D30" s="5">
-        <v>46169.68102278935</v>
+        <v>46169.847689456015</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3157,11 +3157,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46066.321785381944</v>
+        <v>46066.48845204861</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46182.51323063657</v>
+        <v>46182.67989730324</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3216,13 +3216,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46066.32178565972</v>
+        <v>46066.48845232639</v>
       </c>
       <c r="C32" s="5">
-        <v>46126.69341158565</v>
+        <v>46126.86007825231</v>
       </c>
       <c r="D32" s="5">
-        <v>46126.69342440972</v>
+        <v>46126.86009107639</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3281,13 +3281,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46066.32178542824</v>
+        <v>46066.48845209491</v>
       </c>
       <c r="C33" s="8">
-        <v>46126.69293872685</v>
+        <v>46126.85960539352</v>
       </c>
       <c r="D33" s="8">
-        <v>46126.69293993055</v>
+        <v>46126.85960659722</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3342,13 +3342,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46066.32178599537</v>
+        <v>46066.48845266204</v>
       </c>
       <c r="C34" s="5">
-        <v>46126.6929933912</v>
+        <v>46126.859660057875</v>
       </c>
       <c r="D34" s="5">
-        <v>46126.69299459491</v>
+        <v>46126.85966126157</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3403,13 +3403,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46066.321786319444</v>
+        <v>46066.488452986116</v>
       </c>
       <c r="C35" s="8">
-        <v>46126.64103636574</v>
+        <v>46126.807703032406</v>
       </c>
       <c r="D35" s="8">
-        <v>46176.03135493056</v>
+        <v>46176.19802159722</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3468,13 +3468,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46066.32178665509</v>
+        <v>46066.488453321756</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.37621940972</v>
+        <v>46097.54288607639</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.37622104167</v>
+        <v>46097.54288770833</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3529,13 +3529,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46066.321786967594</v>
+        <v>46066.48845363426</v>
       </c>
       <c r="C37" s="8">
-        <v>46126.64102027778</v>
+        <v>46126.80768694445</v>
       </c>
       <c r="D37" s="8">
-        <v>46126.64102221065</v>
+        <v>46126.807688877314</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3590,13 +3590,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46066.321787361114</v>
+        <v>46066.48845402778</v>
       </c>
       <c r="C38" s="5">
-        <v>46114.35992371528</v>
+        <v>46114.526590381945</v>
       </c>
       <c r="D38" s="5">
-        <v>46114.359924965276</v>
+        <v>46114.52659163195</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3651,13 +3651,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46066.32178769676</v>
+        <v>46066.488454363425</v>
       </c>
       <c r="C39" s="8">
-        <v>46157.458965439815</v>
+        <v>46157.62563210649</v>
       </c>
       <c r="D39" s="8">
-        <v>46157.45898106482</v>
+        <v>46157.62564773148</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3716,13 +3716,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46066.32178804398</v>
+        <v>46066.48845471065</v>
       </c>
       <c r="C40" s="5">
-        <v>46157.456767800926</v>
+        <v>46157.62343446759</v>
       </c>
       <c r="D40" s="5">
-        <v>46157.45676883102</v>
+        <v>46157.623435497684</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3777,13 +3777,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46066.32178835648</v>
+        <v>46066.48845502315</v>
       </c>
       <c r="C41" s="8">
-        <v>46157.456836770834</v>
+        <v>46157.6235034375</v>
       </c>
       <c r="D41" s="8">
-        <v>46157.45683802084</v>
+        <v>46157.6235046875</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -3838,13 +3838,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46066.32178866898</v>
+        <v>46066.48845533565</v>
       </c>
       <c r="C42" s="5">
-        <v>46154.70064498842</v>
+        <v>46154.86731165509</v>
       </c>
       <c r="D42" s="5">
-        <v>46157.45958581018</v>
+        <v>46157.62625247685</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3903,13 +3903,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46066.32178486111</v>
+        <v>46066.48845152778</v>
       </c>
       <c r="C43" s="8">
-        <v>46154.70050896991</v>
+        <v>46154.86717563657</v>
       </c>
       <c r="D43" s="8">
-        <v>46154.70051097222</v>
+        <v>46154.86717763889</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3964,13 +3964,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46066.32178549768</v>
+        <v>46066.488452164354</v>
       </c>
       <c r="C44" s="5">
-        <v>46154.70058172454</v>
+        <v>46154.86724839121</v>
       </c>
       <c r="D44" s="5">
-        <v>46154.700582986115</v>
+        <v>46154.86724965277</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4025,11 +4025,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46066.32178594907</v>
+        <v>46066.48845261574</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46157.46663646991</v>
+        <v>46157.63330313658</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4072,13 +4072,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.587331793984</v>
+        <v>46070.75399846065</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.35973473379</v>
+        <v>46114.526401400464</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.359754062505</v>
+        <v>46114.52642072916</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4137,13 +4137,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46066.321786307875</v>
+        <v>46066.48845297453</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.35998150463</v>
+        <v>46114.5266481713</v>
       </c>
       <c r="D47" s="8">
-        <v>46114.359996643514</v>
+        <v>46114.526663310186</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>167</v>
@@ -4202,13 +4202,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.47779013889</v>
+        <v>46091.64445680556</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.36002435185</v>
+        <v>46114.52669101852</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.36003887732</v>
+        <v>46114.526705543976</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4265,11 +4265,11 @@
         <v>178</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.47783655093</v>
+        <v>46091.6445032176</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46184.04039730324</v>
+        <v>46184.20706396991</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>179</v>
@@ -4326,13 +4326,13 @@
         <v>182</v>
       </c>
       <c r="B50" s="5">
-        <v>46066.321786817134</v>
+        <v>46066.48845348379</v>
       </c>
       <c r="C50" s="5">
-        <v>46157.46662641204</v>
+        <v>46157.6332930787</v>
       </c>
       <c r="D50" s="5">
-        <v>46157.46671620371</v>
+        <v>46157.63338287037</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>183</v>
@@ -4375,13 +4375,13 @@
         <v>185</v>
       </c>
       <c r="B51" s="8">
-        <v>46066.321787256944</v>
+        <v>46066.48845392361</v>
       </c>
       <c r="C51" s="8">
-        <v>46157.45907391203</v>
+        <v>46157.625740578704</v>
       </c>
       <c r="D51" s="8">
-        <v>46157.459090335644</v>
+        <v>46157.625757002315</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>186</v>
@@ -4440,13 +4440,13 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46066.321787719906</v>
+        <v>46066.48845438658</v>
       </c>
       <c r="C52" s="5">
-        <v>46157.4666078125</v>
+        <v>46157.633274479165</v>
       </c>
       <c r="D52" s="5">
-        <v>46157.46662734954</v>
+        <v>46157.6332940162</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4505,11 +4505,11 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46066.321788113426</v>
+        <v>46066.48845478009</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.53076429398</v>
+        <v>46195.697430960645</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4552,13 +4552,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46066.32178854167</v>
+        <v>46066.48845520834</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.53061240741</v>
+        <v>46195.69727907407</v>
       </c>
       <c r="D54" s="5">
-        <v>46195.53063009259</v>
+        <v>46195.69729675926</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4617,11 +4617,11 @@
         <v>203</v>
       </c>
       <c r="B55" s="8">
-        <v>46066.321789050926</v>
+        <v>46066.4884557176</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.53351554398</v>
+        <v>46195.70018221065</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>204</v>
@@ -4680,11 +4680,11 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46066.321783865744</v>
+        <v>46066.48845053241</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.53076497685</v>
+        <v>46195.69743164352</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>208</v>
@@ -4743,11 +4743,11 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46066.32178423611</v>
+        <v>46066.488450902776</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.61663114584</v>
+        <v>46191.7832978125</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>183</v>
@@ -4790,13 +4790,13 @@
         <v>213</v>
       </c>
       <c r="B58" s="5">
-        <v>46066.32178452546</v>
+        <v>46066.48845119213</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.61662311343</v>
+        <v>46191.78328978009</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.616641863424</v>
+        <v>46191.783308530095</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -4855,13 +4855,13 @@
         <v>216</v>
       </c>
       <c r="B59" s="8">
-        <v>46066.32178478009</v>
+        <v>46066.488451446756</v>
       </c>
       <c r="C59" s="8">
-        <v>46127.48844644676</v>
+        <v>46127.655113113426</v>
       </c>
       <c r="D59" s="8">
-        <v>46127.48846443287</v>
+        <v>46127.65513109954</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>217</v>
@@ -4920,13 +4920,13 @@
         <v>219</v>
       </c>
       <c r="B60" s="5">
-        <v>46066.321785057866</v>
+        <v>46066.48845172454</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.4885496875</v>
+        <v>46127.655216354164</v>
       </c>
       <c r="D60" s="5">
-        <v>46178.02050702546</v>
+        <v>46178.18717369213</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>220</v>
@@ -4985,11 +4985,11 @@
         <v>222</v>
       </c>
       <c r="B61" s="8">
-        <v>46066.3217853588</v>
+        <v>46066.48845202546</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46182.513236238425</v>
+        <v>46182.67990290509</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>55</v>
@@ -5048,11 +5048,11 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46066.32178564815</v>
+        <v>46066.488452314814</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46192.62267627315</v>
+        <v>46192.78934293981</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5111,11 +5111,11 @@
         <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46066.32178592593</v>
+        <v>46066.48845259259</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46197.42338680556</v>
+        <v>46197.59005347222</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>228</v>
@@ -5158,11 +5158,11 @@
         <v>230</v>
       </c>
       <c r="B64" s="5">
-        <v>46066.321786203705</v>
+        <v>46066.48845287037</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46196.430463275465</v>
+        <v>46196.59712994213</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5221,11 +5221,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46066.32178646991</v>
+        <v>46066.488453136575</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46182.0022325</v>
+        <v>46182.16889916667</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5284,13 +5284,13 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46066.32178421297</v>
+        <v>46066.48845087963</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.42338039352</v>
+        <v>46197.590047060185</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.423397199076</v>
+        <v>46197.59006386574</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>238</v>
@@ -5349,11 +5349,11 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46066.32178489583</v>
+        <v>46066.4884515625</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46162.03787155093</v>
+        <v>46162.20453821759</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5412,11 +5412,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46066.32178524305</v>
+        <v>46066.488451909725</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46165.00380186342</v>
+        <v>46165.170468530094</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5475,11 +5475,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46066.32178569444</v>
+        <v>46066.48845236111</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.42338636574</v>
+        <v>46197.59005303241</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>180</v>
@@ -5536,11 +5536,11 @@
         <v>248</v>
       </c>
       <c r="B70" s="5">
-        <v>46066.32178611111</v>
+        <v>46066.488452777776</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46185.00493481482</v>
+        <v>46185.17160148148</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>181</v>
@@ -5597,11 +5597,11 @@
         <v>250</v>
       </c>
       <c r="B71" s="8">
-        <v>46066.3217865162</v>
+        <v>46066.48845318287</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.4847465162</v>
+        <v>46091.65141318287</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>251</v>
@@ -5644,11 +5644,11 @@
         <v>253</v>
       </c>
       <c r="B72" s="5">
-        <v>46066.321786875</v>
+        <v>46066.488453541664</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46185.004934826386</v>
+        <v>46185.17160149306</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>249</v>
@@ -5707,11 +5707,11 @@
         <v>257</v>
       </c>
       <c r="B73" s="8">
-        <v>46066.32178724537</v>
+        <v>46066.48845391204</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46190.00984024306</v>
+        <v>46190.176506909724</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>258</v>
@@ -5770,11 +5770,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46066.32178759259</v>
+        <v>46066.48845425926</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46191.00862782408</v>
+        <v>46191.17529449074</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>262</v>
@@ -5833,11 +5833,11 @@
         <v>266</v>
       </c>
       <c r="B75" s="8">
-        <v>46066.321787928246</v>
+        <v>46066.4884545949</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46192.03027746528</v>
+        <v>46192.196944131945</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>267</v>
@@ -5896,11 +5896,11 @@
         <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46066.32178459491</v>
+        <v>46066.488451261575</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.484746145834</v>
+        <v>46091.6514128125</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>270</v>
@@ -5943,11 +5943,11 @@
         <v>272</v>
       </c>
       <c r="B77" s="8">
-        <v>46066.32178489583</v>
+        <v>46066.4884515625</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.03915560185</v>
+        <v>46195.205822268515</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>273</v>
@@ -6006,11 +6006,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46066.321785196764</v>
+        <v>46066.48845186342</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.039160706016</v>
+        <v>46195.20582737269</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6069,11 +6069,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.47794063657</v>
+        <v>46091.64460730324</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.48533783565</v>
+        <v>46091.65200450231</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6122,11 +6122,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.47832231481</v>
+        <v>46091.64498898148</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46196.01922805556</v>
+        <v>46196.18589472222</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6185,11 +6185,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.47849136574</v>
+        <v>46091.64515803241</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46091.49624552083</v>
+        <v>46091.6629121875</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="289">
   <si>
     <t>50001506 - ZCO EPM FRIO AIRE</t>
   </si>
@@ -551,6 +551,12 @@
   </si>
   <si>
     <t>Check Pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
   </si>
   <si>
     <t>Pruebas FAT</t>
@@ -4269,7 +4275,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46184.20706396991</v>
+        <v>46198.82239263889</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>179</v>
@@ -4278,10 +4284,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4300,10 +4306,10 @@
         <v>166</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="8">
         <v>46183</v>
@@ -4323,7 +4329,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46066.48845348379</v>
@@ -4335,7 +4341,7 @@
         <v>46157.63338287037</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4359,7 +4365,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4372,7 +4378,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B51" s="8">
         <v>46066.48845392361</v>
@@ -4384,16 +4390,16 @@
         <v>46157.625757002315</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I51" s="8">
         <v>46087</v>
@@ -4411,13 +4417,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>154</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="8">
         <v>46087</v>
@@ -4437,7 +4443,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46066.48845438658</v>
@@ -4449,16 +4455,16 @@
         <v>46157.6332940162</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I52" s="5">
         <v>46092</v>
@@ -4476,13 +4482,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q52" s="5">
         <v>46091</v>
@@ -4502,7 +4508,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B53" s="8">
         <v>46066.48845478009</v>
@@ -4512,7 +4518,7 @@
         <v>46195.697430960645</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4536,7 +4542,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4549,7 +4555,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46066.48845520834</v>
@@ -4561,16 +4567,16 @@
         <v>46195.69729675926</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I54" s="5">
         <v>46094</v>
@@ -4588,13 +4594,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46094</v>
@@ -4614,7 +4620,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B55" s="8">
         <v>46066.4884557176</v>
@@ -4624,16 +4630,16 @@
         <v>46195.70018221065</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I55" s="8">
         <v>46105</v>
@@ -4651,13 +4657,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q55" s="8">
         <v>46105</v>
@@ -4677,7 +4683,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B56" s="5">
         <v>46066.48845053241</v>
@@ -4687,16 +4693,16 @@
         <v>46195.69743164352</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -4714,13 +4720,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q56" s="5">
         <v>46125</v>
@@ -4740,7 +4746,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B57" s="8">
         <v>46066.488450902776</v>
@@ -4750,7 +4756,7 @@
         <v>46191.7832978125</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4774,7 +4780,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4787,7 +4793,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
         <v>46066.48845119213</v>
@@ -4799,16 +4805,16 @@
         <v>46191.783308530095</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I58" s="5">
         <v>46154</v>
@@ -4826,13 +4832,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>112</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="5">
         <v>46154</v>
@@ -4852,7 +4858,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B59" s="8">
         <v>46066.488451446756</v>
@@ -4864,16 +4870,16 @@
         <v>46127.65513109954</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I59" s="8">
         <v>46091</v>
@@ -4891,13 +4897,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>131</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q59" s="8">
         <v>46091</v>
@@ -4917,7 +4923,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B60" s="5">
         <v>46066.48845172454</v>
@@ -4929,16 +4935,16 @@
         <v>46178.18717369213</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I60" s="5">
         <v>46176</v>
@@ -4956,13 +4962,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q60" s="5">
         <v>46176</v>
@@ -4982,7 +4988,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B61" s="8">
         <v>46066.48845202546</v>
@@ -4998,10 +5004,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I61" s="8">
         <v>46146</v>
@@ -5019,13 +5025,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>122</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q61" s="8">
         <v>46146</v>
@@ -5045,7 +5051,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
         <v>46066.488452314814</v>
@@ -5055,16 +5061,16 @@
         <v>46192.78934293981</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I62" s="5">
         <v>46156</v>
@@ -5082,13 +5088,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>163</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q62" s="5">
         <v>46156</v>
@@ -5108,7 +5114,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B63" s="8">
         <v>46066.48845259259</v>
@@ -5118,7 +5124,7 @@
         <v>46197.59005347222</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5142,7 +5148,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5155,7 +5161,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B64" s="5">
         <v>46066.48845287037</v>
@@ -5165,7 +5171,7 @@
         <v>46196.59712994213</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5192,13 +5198,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q64" s="5">
         <v>46125</v>
@@ -5218,7 +5224,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B65" s="8">
         <v>46066.488453136575</v>
@@ -5228,7 +5234,7 @@
         <v>46182.16889916667</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5255,13 +5261,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q65" s="8">
         <v>46178</v>
@@ -5281,7 +5287,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B66" s="5">
         <v>46066.48845087963</v>
@@ -5293,7 +5299,7 @@
         <v>46197.59006386574</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5320,13 +5326,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="5">
         <v>46156</v>
@@ -5346,7 +5352,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B67" s="8">
         <v>46066.4884515625</v>
@@ -5356,7 +5362,7 @@
         <v>46162.20453821759</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5383,13 +5389,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q67" s="8">
         <v>46160</v>
@@ -5409,7 +5415,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B68" s="5">
         <v>46066.488451909725</v>
@@ -5419,7 +5425,7 @@
         <v>46165.170468530094</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5446,13 +5452,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q68" s="5">
         <v>46162</v>
@@ -5472,7 +5478,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B69" s="8">
         <v>46066.48845236111</v>
@@ -5482,7 +5488,7 @@
         <v>46197.59005303241</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5507,10 +5513,10 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>179</v>
@@ -5533,7 +5539,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B70" s="5">
         <v>46066.488452777776</v>
@@ -5543,7 +5549,7 @@
         <v>46185.17160148148</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5568,13 +5574,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>179</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q70" s="5">
         <v>46184</v>
@@ -5594,7 +5600,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B71" s="8">
         <v>46066.48845318287</v>
@@ -5604,7 +5610,7 @@
         <v>46091.65141318287</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5628,7 +5634,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5641,7 +5647,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B72" s="5">
         <v>46066.488453541664</v>
@@ -5651,16 +5657,16 @@
         <v>46185.17160149306</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I72" s="5">
         <v>46185</v>
@@ -5678,13 +5684,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q72" s="5">
         <v>46184</v>
@@ -5704,7 +5710,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B73" s="8">
         <v>46066.48845391204</v>
@@ -5714,7 +5720,7 @@
         <v>46190.176506909724</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5741,13 +5747,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q73" s="8">
         <v>46189</v>
@@ -5767,7 +5773,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B74" s="5">
         <v>46066.48845425926</v>
@@ -5777,16 +5783,16 @@
         <v>46191.17529449074</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I74" s="5">
         <v>46191</v>
@@ -5804,13 +5810,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q74" s="5">
         <v>46190</v>
@@ -5830,7 +5836,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B75" s="8">
         <v>46066.4884545949</v>
@@ -5840,16 +5846,16 @@
         <v>46192.196944131945</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I75" s="8">
         <v>46192</v>
@@ -5867,13 +5873,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q75" s="8">
         <v>46191</v>
@@ -5893,7 +5899,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B76" s="5">
         <v>46066.488451261575</v>
@@ -5903,7 +5909,7 @@
         <v>46091.6514128125</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5927,7 +5933,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5940,7 +5946,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B77" s="8">
         <v>46066.4884515625</v>
@@ -5950,16 +5956,16 @@
         <v>46195.205822268515</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I77" s="8">
         <v>46195</v>
@@ -5977,13 +5983,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q77" s="8">
         <v>46192</v>
@@ -6003,7 +6009,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B78" s="5">
         <v>46066.48845186342</v>
@@ -6013,16 +6019,16 @@
         <v>46195.20582737269</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I78" s="5">
         <v>46195</v>
@@ -6040,13 +6046,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q78" s="5">
         <v>46192</v>
@@ -6066,7 +6072,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B79" s="8">
         <v>46091.64460730324</v>
@@ -6076,7 +6082,7 @@
         <v>46091.65200450231</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6100,7 +6106,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6119,7 +6125,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B80" s="5">
         <v>46091.64498898148</v>
@@ -6129,7 +6135,7 @@
         <v>46196.18589472222</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6156,13 +6162,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q80" s="5">
         <v>46195</v>
@@ -6182,7 +6188,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B81" s="8">
         <v>46091.64515803241</v>
@@ -6192,7 +6198,7 @@
         <v>46091.6629121875</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6219,13 +6225,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q81" s="8">
         <v>46204</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -5953,7 +5953,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.205822268515</v>
+        <v>46203.19655709491</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>275</v>
@@ -6000,8 +6000,8 @@
       <c r="S77" s="9">
         <v>0</v>
       </c>
-      <c r="T77" s="12" t="s">
-        <v>117</v>
+      <c r="T77" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="U77" s="10" t="s">
         <v>58</v>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.20582737269</v>
+        <v>46203.19655721065</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>280</v>
@@ -6063,8 +6063,8 @@
       <c r="S78" s="6">
         <v>0</v>
       </c>
-      <c r="T78" s="12" t="s">
-        <v>117</v>
+      <c r="T78" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="U78" s="10" t="s">
         <v>58</v>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46196.18589472222</v>
+        <v>46203.16836844907</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>285</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -6132,7 +6132,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46203.16836844907</v>
+        <v>46204.19897075232</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>285</v>
@@ -6179,8 +6179,8 @@
       <c r="S80" s="6">
         <v>0</v>
       </c>
-      <c r="T80" s="12" t="s">
-        <v>117</v>
+      <c r="T80" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="U80" s="10" t="s">
         <v>58</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46195.697430960645</v>
+        <v>46204.59404633102</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>198</v>
@@ -4625,9 +4625,11 @@
       <c r="B55" s="8">
         <v>46066.4884557176</v>
       </c>
-      <c r="C55" s="9"/>
+      <c r="C55" s="8">
+        <v>46204.594040208336</v>
+      </c>
       <c r="D55" s="8">
-        <v>46195.70018221065</v>
+        <v>46204.594042916666</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>206</v>
@@ -4690,7 +4692,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46195.69743164352</v>
+        <v>46204.59404793981</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -1504,13 +1504,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46066.48844969907</v>
+        <v>46066.32178303241</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.7222975926</v>
+        <v>46092.55563092593</v>
       </c>
       <c r="D4" s="5">
-        <v>46109.73760709491</v>
+        <v>46109.57094042824</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1553,13 +1553,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46066.48845001157</v>
+        <v>46066.32178334491</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.72226699074</v>
+        <v>46092.55560032408</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.88422799768</v>
+        <v>46133.71756133102</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1616,13 +1616,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46066.488450219906</v>
+        <v>46066.32178355324</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.722267523146</v>
+        <v>46092.55560085648</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.72229813658</v>
+        <v>46092.555631469906</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1679,13 +1679,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46066.488450439814</v>
+        <v>46066.32178377315</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.722267951394</v>
+        <v>46092.55560128472</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72229795139</v>
+        <v>46092.55563128472</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1742,13 +1742,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46066.48845065972</v>
+        <v>46066.32178399306</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72226836806</v>
+        <v>46092.55560170139</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.77389357639</v>
+        <v>46100.60722690972</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1805,13 +1805,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46066.488450868055</v>
+        <v>46066.321784201384</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72226905092</v>
+        <v>46092.55560238426</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.72229799769</v>
+        <v>46092.55563133102</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1868,11 +1868,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46066.48845106481</v>
+        <v>46066.32178439815</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.54322979167</v>
+        <v>46097.376563125</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1915,13 +1915,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46066.488451296296</v>
+        <v>46066.32178462963</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.54322114583</v>
+        <v>46097.37655447917</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.54323589121</v>
+        <v>46097.376569224536</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1980,11 +1980,11 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46066.48845153935</v>
+        <v>46066.321784872685</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46155.16784707176</v>
+        <v>46155.00118040509</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2043,13 +2043,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46066.488451770834</v>
+        <v>46066.32178510417</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.52534087963</v>
+        <v>46114.35867421296</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.525368125</v>
+        <v>46114.35870145833</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2096,13 +2096,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46066.48845050926</v>
+        <v>46066.32178384259</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.54271081019</v>
+        <v>46097.376044143515</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.54272628472</v>
+        <v>46097.37605961805</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2161,13 +2161,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46066.48845109953</v>
+        <v>46066.321784432876</v>
       </c>
       <c r="C15" s="8">
-        <v>46113.568070243055</v>
+        <v>46113.40140357639</v>
       </c>
       <c r="D15" s="8">
-        <v>46113.56808707176</v>
+        <v>46113.40142040509</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2226,13 +2226,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46066.48845135416</v>
+        <v>46066.321784687505</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.52531328704</v>
+        <v>46114.35864662037</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.52533150463</v>
+        <v>46114.358664837964</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2291,13 +2291,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46066.48845160879</v>
+        <v>46066.321784942134</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.5253246412</v>
+        <v>46114.35865797454</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.525341712964</v>
+        <v>46114.3586750463</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2356,13 +2356,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46066.48845217592</v>
+        <v>46066.32178550926</v>
       </c>
       <c r="C18" s="5">
-        <v>46167.553913634256</v>
+        <v>46167.38724696759</v>
       </c>
       <c r="D18" s="5">
-        <v>46167.553930208334</v>
+        <v>46167.38726354166</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2409,13 +2409,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46066.48845243055</v>
+        <v>46066.32178576389</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.54280456019</v>
+        <v>46097.376137893516</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.542820752315</v>
+        <v>46097.37615408565</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2474,13 +2474,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46066.48845268518</v>
+        <v>46066.32178601852</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.52545371528</v>
+        <v>46114.35878704861</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.52558519676</v>
+        <v>46114.358918530095</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2539,13 +2539,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46066.48845292824</v>
+        <v>46066.32178626157</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.54331421296</v>
+        <v>46097.3766475463</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.54333050926</v>
+        <v>46097.37666384259</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2604,13 +2604,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46066.488453171296</v>
+        <v>46066.32178650463</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.62955415509</v>
+        <v>46122.46288748842</v>
       </c>
       <c r="D22" s="5">
-        <v>46122.62957178241</v>
+        <v>46122.46290511574</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2669,13 +2669,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46066.48844994213</v>
+        <v>46066.32178327546</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.52550582176</v>
+        <v>46114.35883915509</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.525521250005</v>
+        <v>46114.35885458333</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2734,13 +2734,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46066.4884502662</v>
+        <v>46066.32178359954</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.623377384254</v>
+        <v>46157.4567107176</v>
       </c>
       <c r="D24" s="5">
-        <v>46184.581514722224</v>
+        <v>46184.41484805556</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2799,13 +2799,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46066.48845053241</v>
+        <v>46066.321783865744</v>
       </c>
       <c r="C25" s="8">
-        <v>46184.576328055555</v>
+        <v>46184.40966138889</v>
       </c>
       <c r="D25" s="8">
-        <v>46184.576358645834</v>
+        <v>46184.40969197916</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2850,13 +2850,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46066.48845078704</v>
+        <v>46066.32178412037</v>
       </c>
       <c r="C26" s="5">
-        <v>46128.626209062495</v>
+        <v>46128.45954239584</v>
       </c>
       <c r="D26" s="5">
-        <v>46128.62625043982</v>
+        <v>46128.45958377315</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2915,13 +2915,13 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46066.48845104167</v>
+        <v>46066.321784375</v>
       </c>
       <c r="C27" s="8">
-        <v>46128.62622789352</v>
+        <v>46128.45956122685</v>
       </c>
       <c r="D27" s="8">
-        <v>46128.62647177083</v>
+        <v>46128.45980510417</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -2976,13 +2976,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46066.488451296296</v>
+        <v>46066.32178462963</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.62622443287</v>
+        <v>46128.459557766204</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.62623707176</v>
+        <v>46128.45957040509</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3037,13 +3037,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46066.48845152778</v>
+        <v>46066.32178486111</v>
       </c>
       <c r="C29" s="8">
-        <v>46182.6798675</v>
+        <v>46182.51320083333</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.90442258102</v>
+        <v>46191.73775591435</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3102,13 +3102,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46066.488451770834</v>
+        <v>46066.32178510417</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.5436782176</v>
+        <v>46097.377011550925</v>
       </c>
       <c r="D30" s="5">
-        <v>46169.847689456015</v>
+        <v>46169.68102278935</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3163,11 +3163,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46066.48845204861</v>
+        <v>46066.321785381944</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46182.67989730324</v>
+        <v>46182.51323063657</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3222,13 +3222,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46066.48845232639</v>
+        <v>46066.32178565972</v>
       </c>
       <c r="C32" s="5">
-        <v>46126.86007825231</v>
+        <v>46126.69341158565</v>
       </c>
       <c r="D32" s="5">
-        <v>46126.86009107639</v>
+        <v>46126.69342440972</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3287,13 +3287,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46066.48845209491</v>
+        <v>46066.32178542824</v>
       </c>
       <c r="C33" s="8">
-        <v>46126.85960539352</v>
+        <v>46126.69293872685</v>
       </c>
       <c r="D33" s="8">
-        <v>46126.85960659722</v>
+        <v>46126.69293993055</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3348,13 +3348,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46066.48845266204</v>
+        <v>46066.32178599537</v>
       </c>
       <c r="C34" s="5">
-        <v>46126.859660057875</v>
+        <v>46126.6929933912</v>
       </c>
       <c r="D34" s="5">
-        <v>46126.85966126157</v>
+        <v>46126.69299459491</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3409,13 +3409,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46066.488452986116</v>
+        <v>46066.321786319444</v>
       </c>
       <c r="C35" s="8">
-        <v>46126.807703032406</v>
+        <v>46126.64103636574</v>
       </c>
       <c r="D35" s="8">
-        <v>46176.19802159722</v>
+        <v>46176.03135493056</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3474,13 +3474,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46066.488453321756</v>
+        <v>46066.32178665509</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.54288607639</v>
+        <v>46097.37621940972</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.54288770833</v>
+        <v>46097.37622104167</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3535,13 +3535,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46066.48845363426</v>
+        <v>46066.321786967594</v>
       </c>
       <c r="C37" s="8">
-        <v>46126.80768694445</v>
+        <v>46126.64102027778</v>
       </c>
       <c r="D37" s="8">
-        <v>46126.807688877314</v>
+        <v>46126.64102221065</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3596,13 +3596,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46066.48845402778</v>
+        <v>46066.321787361114</v>
       </c>
       <c r="C38" s="5">
-        <v>46114.526590381945</v>
+        <v>46114.35992371528</v>
       </c>
       <c r="D38" s="5">
-        <v>46114.52659163195</v>
+        <v>46114.359924965276</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3657,13 +3657,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46066.488454363425</v>
+        <v>46066.32178769676</v>
       </c>
       <c r="C39" s="8">
-        <v>46157.62563210649</v>
+        <v>46157.458965439815</v>
       </c>
       <c r="D39" s="8">
-        <v>46157.62564773148</v>
+        <v>46157.45898106482</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3722,13 +3722,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46066.48845471065</v>
+        <v>46066.32178804398</v>
       </c>
       <c r="C40" s="5">
-        <v>46157.62343446759</v>
+        <v>46157.456767800926</v>
       </c>
       <c r="D40" s="5">
-        <v>46157.623435497684</v>
+        <v>46157.45676883102</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3783,13 +3783,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46066.48845502315</v>
+        <v>46066.32178835648</v>
       </c>
       <c r="C41" s="8">
-        <v>46157.6235034375</v>
+        <v>46157.456836770834</v>
       </c>
       <c r="D41" s="8">
-        <v>46157.6235046875</v>
+        <v>46157.45683802084</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -3844,13 +3844,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46066.48845533565</v>
+        <v>46066.32178866898</v>
       </c>
       <c r="C42" s="5">
-        <v>46154.86731165509</v>
+        <v>46154.70064498842</v>
       </c>
       <c r="D42" s="5">
-        <v>46157.62625247685</v>
+        <v>46157.45958581018</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3909,13 +3909,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46066.48845152778</v>
+        <v>46066.32178486111</v>
       </c>
       <c r="C43" s="8">
-        <v>46154.86717563657</v>
+        <v>46154.70050896991</v>
       </c>
       <c r="D43" s="8">
-        <v>46154.86717763889</v>
+        <v>46154.70051097222</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3970,13 +3970,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46066.488452164354</v>
+        <v>46066.32178549768</v>
       </c>
       <c r="C44" s="5">
-        <v>46154.86724839121</v>
+        <v>46154.70058172454</v>
       </c>
       <c r="D44" s="5">
-        <v>46154.86724965277</v>
+        <v>46154.700582986115</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4031,11 +4031,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46066.48845261574</v>
+        <v>46066.32178594907</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46157.63330313658</v>
+        <v>46157.46663646991</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4078,13 +4078,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.75399846065</v>
+        <v>46070.587331793984</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.526401400464</v>
+        <v>46114.35973473379</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.52642072916</v>
+        <v>46114.359754062505</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4143,13 +4143,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46066.48845297453</v>
+        <v>46066.321786307875</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.5266481713</v>
+        <v>46114.35998150463</v>
       </c>
       <c r="D47" s="8">
-        <v>46114.526663310186</v>
+        <v>46114.359996643514</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>167</v>
@@ -4208,13 +4208,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.64445680556</v>
+        <v>46091.47779013889</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.52669101852</v>
+        <v>46114.36002435185</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.526705543976</v>
+        <v>46114.36003887732</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4271,11 +4271,11 @@
         <v>178</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.6445032176</v>
+        <v>46091.47783655093</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46198.82239263889</v>
+        <v>46198.65572597222</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>179</v>
@@ -4332,13 +4332,13 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46066.48845348379</v>
+        <v>46066.321786817134</v>
       </c>
       <c r="C50" s="5">
-        <v>46157.6332930787</v>
+        <v>46157.46662641204</v>
       </c>
       <c r="D50" s="5">
-        <v>46157.63338287037</v>
+        <v>46157.46671620371</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4381,13 +4381,13 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46066.48845392361</v>
+        <v>46066.321787256944</v>
       </c>
       <c r="C51" s="8">
-        <v>46157.625740578704</v>
+        <v>46157.45907391203</v>
       </c>
       <c r="D51" s="8">
-        <v>46157.625757002315</v>
+        <v>46157.459090335644</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4446,13 +4446,13 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46066.48845438658</v>
+        <v>46066.321787719906</v>
       </c>
       <c r="C52" s="5">
-        <v>46157.633274479165</v>
+        <v>46157.4666078125</v>
       </c>
       <c r="D52" s="5">
-        <v>46157.6332940162</v>
+        <v>46157.46662734954</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4511,11 +4511,11 @@
         <v>197</v>
       </c>
       <c r="B53" s="8">
-        <v>46066.48845478009</v>
+        <v>46066.321788113426</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46204.59404633102</v>
+        <v>46204.427379664354</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>198</v>
@@ -4558,13 +4558,13 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46066.48845520834</v>
+        <v>46066.32178854167</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.69727907407</v>
+        <v>46195.53061240741</v>
       </c>
       <c r="D54" s="5">
-        <v>46195.69729675926</v>
+        <v>46195.53063009259</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4623,13 +4623,13 @@
         <v>205</v>
       </c>
       <c r="B55" s="8">
-        <v>46066.4884557176</v>
+        <v>46066.321789050926</v>
       </c>
       <c r="C55" s="8">
-        <v>46204.594040208336</v>
+        <v>46204.427373541665</v>
       </c>
       <c r="D55" s="8">
-        <v>46204.594042916666</v>
+        <v>46204.42737625</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>206</v>
@@ -4688,11 +4688,11 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46066.48845053241</v>
+        <v>46066.321783865744</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46204.59404793981</v>
+        <v>46204.42738127315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4751,11 +4751,11 @@
         <v>213</v>
       </c>
       <c r="B57" s="8">
-        <v>46066.488450902776</v>
+        <v>46066.32178423611</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.7832978125</v>
+        <v>46191.61663114584</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>185</v>
@@ -4798,13 +4798,13 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46066.48845119213</v>
+        <v>46066.32178452546</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.78328978009</v>
+        <v>46191.61662311343</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.783308530095</v>
+        <v>46191.616641863424</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>216</v>
@@ -4863,13 +4863,13 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46066.488451446756</v>
+        <v>46066.32178478009</v>
       </c>
       <c r="C59" s="8">
-        <v>46127.655113113426</v>
+        <v>46127.48844644676</v>
       </c>
       <c r="D59" s="8">
-        <v>46127.65513109954</v>
+        <v>46127.48846443287</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>219</v>
@@ -4928,13 +4928,13 @@
         <v>221</v>
       </c>
       <c r="B60" s="5">
-        <v>46066.48845172454</v>
+        <v>46066.321785057866</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.655216354164</v>
+        <v>46127.4885496875</v>
       </c>
       <c r="D60" s="5">
-        <v>46178.18717369213</v>
+        <v>46178.02050702546</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>222</v>
@@ -4993,11 +4993,11 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46066.48845202546</v>
+        <v>46066.3217853588</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46182.67990290509</v>
+        <v>46182.513236238425</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>55</v>
@@ -5056,11 +5056,11 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46066.488452314814</v>
+        <v>46066.32178564815</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46192.78934293981</v>
+        <v>46192.62267627315</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5119,11 +5119,11 @@
         <v>229</v>
       </c>
       <c r="B63" s="8">
-        <v>46066.48845259259</v>
+        <v>46066.32178592593</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46197.59005347222</v>
+        <v>46197.42338680556</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>230</v>
@@ -5166,11 +5166,11 @@
         <v>232</v>
       </c>
       <c r="B64" s="5">
-        <v>46066.48845287037</v>
+        <v>46066.321786203705</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46196.59712994213</v>
+        <v>46196.430463275465</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5229,11 +5229,11 @@
         <v>235</v>
       </c>
       <c r="B65" s="8">
-        <v>46066.488453136575</v>
+        <v>46066.32178646991</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46182.16889916667</v>
+        <v>46182.0022325</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>236</v>
@@ -5292,13 +5292,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46066.48845087963</v>
+        <v>46066.32178421297</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.590047060185</v>
+        <v>46197.42338039352</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.59006386574</v>
+        <v>46197.423397199076</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5357,11 +5357,11 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46066.4884515625</v>
+        <v>46066.32178489583</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46162.20453821759</v>
+        <v>46162.03787155093</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5420,11 +5420,11 @@
         <v>245</v>
       </c>
       <c r="B68" s="5">
-        <v>46066.488451909725</v>
+        <v>46066.32178524305</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46165.170468530094</v>
+        <v>46165.00380186342</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -5483,11 +5483,11 @@
         <v>248</v>
       </c>
       <c r="B69" s="8">
-        <v>46066.48845236111</v>
+        <v>46066.32178569444</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.59005303241</v>
+        <v>46197.42338636574</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>182</v>
@@ -5544,11 +5544,11 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46066.488452777776</v>
+        <v>46066.32178611111</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46185.17160148148</v>
+        <v>46185.00493481482</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>183</v>
@@ -5605,11 +5605,11 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46066.48845318287</v>
+        <v>46066.3217865162</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.65141318287</v>
+        <v>46091.4847465162</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5652,11 +5652,11 @@
         <v>255</v>
       </c>
       <c r="B72" s="5">
-        <v>46066.488453541664</v>
+        <v>46066.321786875</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46185.17160149306</v>
+        <v>46185.004934826386</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>251</v>
@@ -5715,11 +5715,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46066.48845391204</v>
+        <v>46066.32178724537</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46190.176506909724</v>
+        <v>46190.00984024306</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5778,11 +5778,11 @@
         <v>263</v>
       </c>
       <c r="B74" s="5">
-        <v>46066.48845425926</v>
+        <v>46066.32178759259</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46191.17529449074</v>
+        <v>46191.00862782408</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -5841,11 +5841,11 @@
         <v>268</v>
       </c>
       <c r="B75" s="8">
-        <v>46066.4884545949</v>
+        <v>46066.321787928246</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46192.196944131945</v>
+        <v>46192.03027746528</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>269</v>
@@ -5904,11 +5904,11 @@
         <v>271</v>
       </c>
       <c r="B76" s="5">
-        <v>46066.488451261575</v>
+        <v>46066.32178459491</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.6514128125</v>
+        <v>46091.484746145834</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>272</v>
@@ -5951,11 +5951,11 @@
         <v>274</v>
       </c>
       <c r="B77" s="8">
-        <v>46066.4884515625</v>
+        <v>46066.32178489583</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46203.19655709491</v>
+        <v>46203.02989042824</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>275</v>
@@ -6014,11 +6014,11 @@
         <v>279</v>
       </c>
       <c r="B78" s="5">
-        <v>46066.48845186342</v>
+        <v>46066.321785196764</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46203.19655721065</v>
+        <v>46203.029890543985</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>280</v>
@@ -6077,11 +6077,11 @@
         <v>281</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.64460730324</v>
+        <v>46091.47794063657</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.65200450231</v>
+        <v>46091.48533783565</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>282</v>
@@ -6130,11 +6130,11 @@
         <v>284</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.64498898148</v>
+        <v>46091.47832231481</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46204.19897075232</v>
+        <v>46204.032304085646</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>285</v>
@@ -6193,11 +6193,11 @@
         <v>287</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.64515803241</v>
+        <v>46091.47849136574</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46091.6629121875</v>
+        <v>46205.03340306713</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>288</v>
@@ -6244,8 +6244,8 @@
       <c r="S81" s="9">
         <v>0</v>
       </c>
-      <c r="T81" s="11" t="s">
-        <v>57</v>
+      <c r="T81" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="U81" s="10" t="s">
         <v>58</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -1504,13 +1504,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46066.32178303241</v>
+        <v>46066.48844969907</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55563092593</v>
+        <v>46092.7222975926</v>
       </c>
       <c r="D4" s="5">
-        <v>46109.57094042824</v>
+        <v>46109.73760709491</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1553,13 +1553,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46066.32178334491</v>
+        <v>46066.48845001157</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55560032408</v>
+        <v>46092.72226699074</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.71756133102</v>
+        <v>46133.88422799768</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1616,13 +1616,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46066.32178355324</v>
+        <v>46066.488450219906</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55560085648</v>
+        <v>46092.722267523146</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.555631469906</v>
+        <v>46092.72229813658</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1679,13 +1679,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46066.32178377315</v>
+        <v>46066.488450439814</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55560128472</v>
+        <v>46092.722267951394</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55563128472</v>
+        <v>46092.72229795139</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1742,13 +1742,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46066.32178399306</v>
+        <v>46066.48845065972</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55560170139</v>
+        <v>46092.72226836806</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.60722690972</v>
+        <v>46100.77389357639</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1805,13 +1805,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46066.321784201384</v>
+        <v>46066.488450868055</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55560238426</v>
+        <v>46092.72226905092</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55563133102</v>
+        <v>46092.72229799769</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1868,11 +1868,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46066.32178439815</v>
+        <v>46066.48845106481</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.376563125</v>
+        <v>46097.54322979167</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1915,13 +1915,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46066.32178462963</v>
+        <v>46066.488451296296</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.37655447917</v>
+        <v>46097.54322114583</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.376569224536</v>
+        <v>46097.54323589121</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1980,11 +1980,11 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46066.321784872685</v>
+        <v>46066.48845153935</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46155.00118040509</v>
+        <v>46155.16784707176</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2043,13 +2043,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46066.32178510417</v>
+        <v>46066.488451770834</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.35867421296</v>
+        <v>46114.52534087963</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.35870145833</v>
+        <v>46114.525368125</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2096,13 +2096,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46066.32178384259</v>
+        <v>46066.48845050926</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.376044143515</v>
+        <v>46097.54271081019</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.37605961805</v>
+        <v>46097.54272628472</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2161,13 +2161,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46066.321784432876</v>
+        <v>46066.48845109953</v>
       </c>
       <c r="C15" s="8">
-        <v>46113.40140357639</v>
+        <v>46113.568070243055</v>
       </c>
       <c r="D15" s="8">
-        <v>46113.40142040509</v>
+        <v>46113.56808707176</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2226,13 +2226,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46066.321784687505</v>
+        <v>46066.48845135416</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.35864662037</v>
+        <v>46114.52531328704</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.358664837964</v>
+        <v>46114.52533150463</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2291,13 +2291,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46066.321784942134</v>
+        <v>46066.48845160879</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.35865797454</v>
+        <v>46114.5253246412</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.3586750463</v>
+        <v>46114.525341712964</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2356,13 +2356,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46066.32178550926</v>
+        <v>46066.48845217592</v>
       </c>
       <c r="C18" s="5">
-        <v>46167.38724696759</v>
+        <v>46167.553913634256</v>
       </c>
       <c r="D18" s="5">
-        <v>46167.38726354166</v>
+        <v>46167.553930208334</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2409,13 +2409,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46066.32178576389</v>
+        <v>46066.48845243055</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.376137893516</v>
+        <v>46097.54280456019</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.37615408565</v>
+        <v>46097.542820752315</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2474,13 +2474,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46066.32178601852</v>
+        <v>46066.48845268518</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.35878704861</v>
+        <v>46114.52545371528</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.358918530095</v>
+        <v>46114.52558519676</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2539,13 +2539,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46066.32178626157</v>
+        <v>46066.48845292824</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.3766475463</v>
+        <v>46097.54331421296</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.37666384259</v>
+        <v>46097.54333050926</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2604,13 +2604,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46066.32178650463</v>
+        <v>46066.488453171296</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.46288748842</v>
+        <v>46122.62955415509</v>
       </c>
       <c r="D22" s="5">
-        <v>46122.46290511574</v>
+        <v>46122.62957178241</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2669,13 +2669,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46066.32178327546</v>
+        <v>46066.48844994213</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.35883915509</v>
+        <v>46114.52550582176</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.35885458333</v>
+        <v>46114.525521250005</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2734,13 +2734,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46066.32178359954</v>
+        <v>46066.4884502662</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.4567107176</v>
+        <v>46157.623377384254</v>
       </c>
       <c r="D24" s="5">
-        <v>46184.41484805556</v>
+        <v>46184.581514722224</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2799,13 +2799,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46066.321783865744</v>
+        <v>46066.48845053241</v>
       </c>
       <c r="C25" s="8">
-        <v>46184.40966138889</v>
+        <v>46184.576328055555</v>
       </c>
       <c r="D25" s="8">
-        <v>46184.40969197916</v>
+        <v>46184.576358645834</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2850,13 +2850,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46066.32178412037</v>
+        <v>46066.48845078704</v>
       </c>
       <c r="C26" s="5">
-        <v>46128.45954239584</v>
+        <v>46128.626209062495</v>
       </c>
       <c r="D26" s="5">
-        <v>46128.45958377315</v>
+        <v>46128.62625043982</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2915,13 +2915,13 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46066.321784375</v>
+        <v>46066.48845104167</v>
       </c>
       <c r="C27" s="8">
-        <v>46128.45956122685</v>
+        <v>46128.62622789352</v>
       </c>
       <c r="D27" s="8">
-        <v>46128.45980510417</v>
+        <v>46128.62647177083</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -2976,13 +2976,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46066.32178462963</v>
+        <v>46066.488451296296</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.459557766204</v>
+        <v>46128.62622443287</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.45957040509</v>
+        <v>46128.62623707176</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3037,13 +3037,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46066.32178486111</v>
+        <v>46066.48845152778</v>
       </c>
       <c r="C29" s="8">
-        <v>46182.51320083333</v>
+        <v>46182.6798675</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.73775591435</v>
+        <v>46191.90442258102</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3102,13 +3102,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46066.32178510417</v>
+        <v>46066.488451770834</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.377011550925</v>
+        <v>46097.5436782176</v>
       </c>
       <c r="D30" s="5">
-        <v>46169.68102278935</v>
+        <v>46169.847689456015</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3163,11 +3163,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46066.321785381944</v>
+        <v>46066.48845204861</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46182.51323063657</v>
+        <v>46182.67989730324</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3222,13 +3222,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46066.32178565972</v>
+        <v>46066.48845232639</v>
       </c>
       <c r="C32" s="5">
-        <v>46126.69341158565</v>
+        <v>46126.86007825231</v>
       </c>
       <c r="D32" s="5">
-        <v>46126.69342440972</v>
+        <v>46126.86009107639</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3287,13 +3287,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46066.32178542824</v>
+        <v>46066.48845209491</v>
       </c>
       <c r="C33" s="8">
-        <v>46126.69293872685</v>
+        <v>46126.85960539352</v>
       </c>
       <c r="D33" s="8">
-        <v>46126.69293993055</v>
+        <v>46126.85960659722</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3348,13 +3348,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46066.32178599537</v>
+        <v>46066.48845266204</v>
       </c>
       <c r="C34" s="5">
-        <v>46126.6929933912</v>
+        <v>46126.859660057875</v>
       </c>
       <c r="D34" s="5">
-        <v>46126.69299459491</v>
+        <v>46126.85966126157</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3409,13 +3409,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46066.321786319444</v>
+        <v>46066.488452986116</v>
       </c>
       <c r="C35" s="8">
-        <v>46126.64103636574</v>
+        <v>46126.807703032406</v>
       </c>
       <c r="D35" s="8">
-        <v>46176.03135493056</v>
+        <v>46176.19802159722</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3474,13 +3474,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46066.32178665509</v>
+        <v>46066.488453321756</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.37621940972</v>
+        <v>46097.54288607639</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.37622104167</v>
+        <v>46097.54288770833</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3535,13 +3535,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46066.321786967594</v>
+        <v>46066.48845363426</v>
       </c>
       <c r="C37" s="8">
-        <v>46126.64102027778</v>
+        <v>46126.80768694445</v>
       </c>
       <c r="D37" s="8">
-        <v>46126.64102221065</v>
+        <v>46126.807688877314</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3596,13 +3596,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46066.321787361114</v>
+        <v>46066.48845402778</v>
       </c>
       <c r="C38" s="5">
-        <v>46114.35992371528</v>
+        <v>46114.526590381945</v>
       </c>
       <c r="D38" s="5">
-        <v>46114.359924965276</v>
+        <v>46114.52659163195</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3657,13 +3657,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46066.32178769676</v>
+        <v>46066.488454363425</v>
       </c>
       <c r="C39" s="8">
-        <v>46157.458965439815</v>
+        <v>46157.62563210649</v>
       </c>
       <c r="D39" s="8">
-        <v>46157.45898106482</v>
+        <v>46157.62564773148</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3722,13 +3722,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46066.32178804398</v>
+        <v>46066.48845471065</v>
       </c>
       <c r="C40" s="5">
-        <v>46157.456767800926</v>
+        <v>46157.62343446759</v>
       </c>
       <c r="D40" s="5">
-        <v>46157.45676883102</v>
+        <v>46157.623435497684</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3783,13 +3783,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46066.32178835648</v>
+        <v>46066.48845502315</v>
       </c>
       <c r="C41" s="8">
-        <v>46157.456836770834</v>
+        <v>46157.6235034375</v>
       </c>
       <c r="D41" s="8">
-        <v>46157.45683802084</v>
+        <v>46157.6235046875</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -3844,13 +3844,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46066.32178866898</v>
+        <v>46066.48845533565</v>
       </c>
       <c r="C42" s="5">
-        <v>46154.70064498842</v>
+        <v>46154.86731165509</v>
       </c>
       <c r="D42" s="5">
-        <v>46157.45958581018</v>
+        <v>46157.62625247685</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3909,13 +3909,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46066.32178486111</v>
+        <v>46066.48845152778</v>
       </c>
       <c r="C43" s="8">
-        <v>46154.70050896991</v>
+        <v>46154.86717563657</v>
       </c>
       <c r="D43" s="8">
-        <v>46154.70051097222</v>
+        <v>46154.86717763889</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3970,13 +3970,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46066.32178549768</v>
+        <v>46066.488452164354</v>
       </c>
       <c r="C44" s="5">
-        <v>46154.70058172454</v>
+        <v>46154.86724839121</v>
       </c>
       <c r="D44" s="5">
-        <v>46154.700582986115</v>
+        <v>46154.86724965277</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4031,11 +4031,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46066.32178594907</v>
+        <v>46066.48845261574</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46157.46663646991</v>
+        <v>46157.63330313658</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4078,13 +4078,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.587331793984</v>
+        <v>46070.75399846065</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.35973473379</v>
+        <v>46114.526401400464</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.359754062505</v>
+        <v>46114.52642072916</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4143,13 +4143,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46066.321786307875</v>
+        <v>46066.48845297453</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.35998150463</v>
+        <v>46114.5266481713</v>
       </c>
       <c r="D47" s="8">
-        <v>46114.359996643514</v>
+        <v>46114.526663310186</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>167</v>
@@ -4208,13 +4208,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.47779013889</v>
+        <v>46091.64445680556</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.36002435185</v>
+        <v>46114.52669101852</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.36003887732</v>
+        <v>46114.526705543976</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4271,11 +4271,11 @@
         <v>178</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.47783655093</v>
+        <v>46091.6445032176</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46198.65572597222</v>
+        <v>46198.82239263889</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>179</v>
@@ -4332,13 +4332,13 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46066.321786817134</v>
+        <v>46066.48845348379</v>
       </c>
       <c r="C50" s="5">
-        <v>46157.46662641204</v>
+        <v>46157.6332930787</v>
       </c>
       <c r="D50" s="5">
-        <v>46157.46671620371</v>
+        <v>46157.63338287037</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4381,13 +4381,13 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46066.321787256944</v>
+        <v>46066.48845392361</v>
       </c>
       <c r="C51" s="8">
-        <v>46157.45907391203</v>
+        <v>46157.625740578704</v>
       </c>
       <c r="D51" s="8">
-        <v>46157.459090335644</v>
+        <v>46157.625757002315</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4446,13 +4446,13 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46066.321787719906</v>
+        <v>46066.48845438658</v>
       </c>
       <c r="C52" s="5">
-        <v>46157.4666078125</v>
+        <v>46157.633274479165</v>
       </c>
       <c r="D52" s="5">
-        <v>46157.46662734954</v>
+        <v>46157.6332940162</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4511,11 +4511,11 @@
         <v>197</v>
       </c>
       <c r="B53" s="8">
-        <v>46066.321788113426</v>
+        <v>46066.48845478009</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46204.427379664354</v>
+        <v>46204.59404633102</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>198</v>
@@ -4558,13 +4558,13 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46066.32178854167</v>
+        <v>46066.48845520834</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.53061240741</v>
+        <v>46195.69727907407</v>
       </c>
       <c r="D54" s="5">
-        <v>46195.53063009259</v>
+        <v>46195.69729675926</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4623,13 +4623,13 @@
         <v>205</v>
       </c>
       <c r="B55" s="8">
-        <v>46066.321789050926</v>
+        <v>46066.4884557176</v>
       </c>
       <c r="C55" s="8">
-        <v>46204.427373541665</v>
+        <v>46204.594040208336</v>
       </c>
       <c r="D55" s="8">
-        <v>46204.42737625</v>
+        <v>46204.594042916666</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>206</v>
@@ -4688,11 +4688,11 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46066.321783865744</v>
+        <v>46066.48845053241</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46204.42738127315</v>
+        <v>46204.59404793981</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4751,11 +4751,11 @@
         <v>213</v>
       </c>
       <c r="B57" s="8">
-        <v>46066.32178423611</v>
+        <v>46066.488450902776</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.61663114584</v>
+        <v>46191.7832978125</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>185</v>
@@ -4798,13 +4798,13 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46066.32178452546</v>
+        <v>46066.48845119213</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.61662311343</v>
+        <v>46191.78328978009</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.616641863424</v>
+        <v>46191.783308530095</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>216</v>
@@ -4863,13 +4863,13 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46066.32178478009</v>
+        <v>46066.488451446756</v>
       </c>
       <c r="C59" s="8">
-        <v>46127.48844644676</v>
+        <v>46127.655113113426</v>
       </c>
       <c r="D59" s="8">
-        <v>46127.48846443287</v>
+        <v>46127.65513109954</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>219</v>
@@ -4928,13 +4928,13 @@
         <v>221</v>
       </c>
       <c r="B60" s="5">
-        <v>46066.321785057866</v>
+        <v>46066.48845172454</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.4885496875</v>
+        <v>46127.655216354164</v>
       </c>
       <c r="D60" s="5">
-        <v>46178.02050702546</v>
+        <v>46178.18717369213</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>222</v>
@@ -4993,11 +4993,11 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46066.3217853588</v>
+        <v>46066.48845202546</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46182.513236238425</v>
+        <v>46182.67990290509</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>55</v>
@@ -5056,11 +5056,11 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46066.32178564815</v>
+        <v>46066.488452314814</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46192.62267627315</v>
+        <v>46192.78934293981</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5119,11 +5119,11 @@
         <v>229</v>
       </c>
       <c r="B63" s="8">
-        <v>46066.32178592593</v>
+        <v>46066.48845259259</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46197.42338680556</v>
+        <v>46197.59005347222</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>230</v>
@@ -5166,11 +5166,11 @@
         <v>232</v>
       </c>
       <c r="B64" s="5">
-        <v>46066.321786203705</v>
+        <v>46066.48845287037</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46196.430463275465</v>
+        <v>46196.59712994213</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5229,11 +5229,11 @@
         <v>235</v>
       </c>
       <c r="B65" s="8">
-        <v>46066.32178646991</v>
+        <v>46066.488453136575</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46182.0022325</v>
+        <v>46182.16889916667</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>236</v>
@@ -5292,13 +5292,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46066.32178421297</v>
+        <v>46066.48845087963</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.42338039352</v>
+        <v>46197.590047060185</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.423397199076</v>
+        <v>46197.59006386574</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5357,11 +5357,11 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46066.32178489583</v>
+        <v>46066.4884515625</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46162.03787155093</v>
+        <v>46162.20453821759</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5420,11 +5420,11 @@
         <v>245</v>
       </c>
       <c r="B68" s="5">
-        <v>46066.32178524305</v>
+        <v>46066.488451909725</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46165.00380186342</v>
+        <v>46165.170468530094</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -5483,11 +5483,11 @@
         <v>248</v>
       </c>
       <c r="B69" s="8">
-        <v>46066.32178569444</v>
+        <v>46066.48845236111</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.42338636574</v>
+        <v>46197.59005303241</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>182</v>
@@ -5544,11 +5544,11 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46066.32178611111</v>
+        <v>46066.488452777776</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46185.00493481482</v>
+        <v>46185.17160148148</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>183</v>
@@ -5605,11 +5605,11 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46066.3217865162</v>
+        <v>46066.48845318287</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.4847465162</v>
+        <v>46091.65141318287</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5652,11 +5652,11 @@
         <v>255</v>
       </c>
       <c r="B72" s="5">
-        <v>46066.321786875</v>
+        <v>46066.488453541664</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46185.004934826386</v>
+        <v>46185.17160149306</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>251</v>
@@ -5715,11 +5715,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46066.32178724537</v>
+        <v>46066.48845391204</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46190.00984024306</v>
+        <v>46190.176506909724</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5778,11 +5778,11 @@
         <v>263</v>
       </c>
       <c r="B74" s="5">
-        <v>46066.32178759259</v>
+        <v>46066.48845425926</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46191.00862782408</v>
+        <v>46191.17529449074</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -5841,11 +5841,11 @@
         <v>268</v>
       </c>
       <c r="B75" s="8">
-        <v>46066.321787928246</v>
+        <v>46066.4884545949</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46192.03027746528</v>
+        <v>46192.196944131945</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>269</v>
@@ -5904,11 +5904,11 @@
         <v>271</v>
       </c>
       <c r="B76" s="5">
-        <v>46066.32178459491</v>
+        <v>46066.488451261575</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.484746145834</v>
+        <v>46091.6514128125</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>272</v>
@@ -5951,11 +5951,11 @@
         <v>274</v>
       </c>
       <c r="B77" s="8">
-        <v>46066.32178489583</v>
+        <v>46066.4884515625</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46203.02989042824</v>
+        <v>46203.19655709491</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>275</v>
@@ -6014,11 +6014,11 @@
         <v>279</v>
       </c>
       <c r="B78" s="5">
-        <v>46066.321785196764</v>
+        <v>46066.48845186342</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46203.029890543985</v>
+        <v>46203.19655721065</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>280</v>
@@ -6077,11 +6077,11 @@
         <v>281</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.47794063657</v>
+        <v>46091.64460730324</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.48533783565</v>
+        <v>46091.65200450231</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>282</v>
@@ -6130,11 +6130,11 @@
         <v>284</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.47832231481</v>
+        <v>46091.64498898148</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46204.032304085646</v>
+        <v>46204.19897075232</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>285</v>
@@ -6193,11 +6193,11 @@
         <v>287</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.47849136574</v>
+        <v>46091.64515803241</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46205.03340306713</v>
+        <v>46205.20006973379</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>288</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46204.59404633102</v>
+        <v>46209.78872840278</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>198</v>
@@ -4629,7 +4629,7 @@
         <v>46204.594040208336</v>
       </c>
       <c r="D55" s="8">
-        <v>46204.594042916666</v>
+        <v>46209.811246377314</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>206</v>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46197.59005347222</v>
+        <v>46209.79759747685</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>230</v>
@@ -5359,9 +5359,11 @@
       <c r="B67" s="8">
         <v>46066.4884515625</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="8">
+        <v>46209.79758950231</v>
+      </c>
       <c r="D67" s="8">
-        <v>46162.20453821759</v>
+        <v>46209.797607395834</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5406,13 +5408,13 @@
         <v>46161</v>
       </c>
       <c r="S67" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U67" s="10" t="s">
-        <v>58</v>
+      <c r="U67" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5487,7 +5489,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.59005303241</v>
+        <v>46209.797597094905</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>182</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="289">
   <si>
     <t>50001506 - ZCO EPM FRIO AIRE</t>
   </si>
@@ -4513,9 +4513,11 @@
       <c r="B53" s="8">
         <v>46066.48845478009</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="8">
+        <v>46209.915449293985</v>
+      </c>
       <c r="D53" s="8">
-        <v>46209.78872840278</v>
+        <v>46209.91546185185</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>198</v>
@@ -4549,9 +4551,13 @@
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
-      <c r="S53" s="9"/>
+      <c r="S53" s="9">
+        <v>1</v>
+      </c>
       <c r="T53" s="9"/>
-      <c r="U53" s="9"/>
+      <c r="U53" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
@@ -4629,7 +4635,7 @@
         <v>46204.594040208336</v>
       </c>
       <c r="D55" s="8">
-        <v>46209.811246377314</v>
+        <v>46209.916215439815</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>206</v>
@@ -4690,9 +4696,11 @@
       <c r="B56" s="5">
         <v>46066.48845053241</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46209.9154271875</v>
+      </c>
       <c r="D56" s="5">
-        <v>46204.59404793981</v>
+        <v>46209.91544646991</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4737,13 +4745,13 @@
         <v>46126</v>
       </c>
       <c r="S56" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U56" s="12" t="s">
-        <v>107</v>
+      <c r="U56" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -5170,7 +5178,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46196.59712994213</v>
+        <v>46209.91544568287</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5220,8 +5228,8 @@
       <c r="T64" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="U64" s="10" t="s">
-        <v>58</v>
+      <c r="U64" s="12" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="289">
   <si>
     <t>50001506 - ZCO EPM FRIO AIRE</t>
   </si>
@@ -4033,9 +4033,11 @@
       <c r="B45" s="8">
         <v>46066.48845261574</v>
       </c>
-      <c r="C45" s="9"/>
+      <c r="C45" s="8">
+        <v>46210.52807011574</v>
+      </c>
       <c r="D45" s="8">
-        <v>46157.63330313658</v>
+        <v>46210.52808679398</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4069,9 +4071,13 @@
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
-      <c r="S45" s="9"/>
+      <c r="S45" s="9">
+        <v>1</v>
+      </c>
       <c r="T45" s="9"/>
-      <c r="U45" s="9"/>
+      <c r="U45" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -4641,7 +4641,7 @@
         <v>46204.594040208336</v>
       </c>
       <c r="D55" s="8">
-        <v>46209.916215439815</v>
+        <v>46211.525319189815</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>206</v>
@@ -4706,7 +4706,7 @@
         <v>46209.9154271875</v>
       </c>
       <c r="D56" s="5">
-        <v>46209.91544646991</v>
+        <v>46211.57175387732</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -1504,13 +1504,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46066.48844969907</v>
+        <v>46066.32178303241</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.7222975926</v>
+        <v>46092.55563092593</v>
       </c>
       <c r="D4" s="5">
-        <v>46109.73760709491</v>
+        <v>46109.57094042824</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1553,13 +1553,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46066.48845001157</v>
+        <v>46066.32178334491</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.72226699074</v>
+        <v>46092.55560032408</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.88422799768</v>
+        <v>46133.71756133102</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1616,13 +1616,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46066.488450219906</v>
+        <v>46066.32178355324</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.722267523146</v>
+        <v>46092.55560085648</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.72229813658</v>
+        <v>46092.555631469906</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1679,13 +1679,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46066.488450439814</v>
+        <v>46066.32178377315</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.722267951394</v>
+        <v>46092.55560128472</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72229795139</v>
+        <v>46092.55563128472</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1742,13 +1742,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46066.48845065972</v>
+        <v>46066.32178399306</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.72226836806</v>
+        <v>46092.55560170139</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.77389357639</v>
+        <v>46100.60722690972</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1805,13 +1805,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46066.488450868055</v>
+        <v>46066.321784201384</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72226905092</v>
+        <v>46092.55560238426</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.72229799769</v>
+        <v>46092.55563133102</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1868,11 +1868,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46066.48845106481</v>
+        <v>46066.32178439815</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.54322979167</v>
+        <v>46097.376563125</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1915,13 +1915,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46066.488451296296</v>
+        <v>46066.32178462963</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.54322114583</v>
+        <v>46097.37655447917</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.54323589121</v>
+        <v>46097.376569224536</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1980,11 +1980,11 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46066.48845153935</v>
+        <v>46066.321784872685</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46155.16784707176</v>
+        <v>46155.00118040509</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2043,13 +2043,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46066.488451770834</v>
+        <v>46066.32178510417</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.52534087963</v>
+        <v>46114.35867421296</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.525368125</v>
+        <v>46114.35870145833</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2096,13 +2096,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46066.48845050926</v>
+        <v>46066.32178384259</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.54271081019</v>
+        <v>46097.376044143515</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.54272628472</v>
+        <v>46097.37605961805</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2161,13 +2161,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46066.48845109953</v>
+        <v>46066.321784432876</v>
       </c>
       <c r="C15" s="8">
-        <v>46113.568070243055</v>
+        <v>46113.40140357639</v>
       </c>
       <c r="D15" s="8">
-        <v>46113.56808707176</v>
+        <v>46113.40142040509</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2226,13 +2226,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46066.48845135416</v>
+        <v>46066.321784687505</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.52531328704</v>
+        <v>46114.35864662037</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.52533150463</v>
+        <v>46114.358664837964</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2291,13 +2291,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46066.48845160879</v>
+        <v>46066.321784942134</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.5253246412</v>
+        <v>46114.35865797454</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.525341712964</v>
+        <v>46114.3586750463</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2356,13 +2356,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46066.48845217592</v>
+        <v>46066.32178550926</v>
       </c>
       <c r="C18" s="5">
-        <v>46167.553913634256</v>
+        <v>46167.38724696759</v>
       </c>
       <c r="D18" s="5">
-        <v>46167.553930208334</v>
+        <v>46167.38726354166</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2409,13 +2409,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46066.48845243055</v>
+        <v>46066.32178576389</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.54280456019</v>
+        <v>46097.376137893516</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.542820752315</v>
+        <v>46097.37615408565</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2474,13 +2474,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46066.48845268518</v>
+        <v>46066.32178601852</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.52545371528</v>
+        <v>46114.35878704861</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.52558519676</v>
+        <v>46114.358918530095</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2539,13 +2539,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46066.48845292824</v>
+        <v>46066.32178626157</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.54331421296</v>
+        <v>46097.3766475463</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.54333050926</v>
+        <v>46097.37666384259</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2604,13 +2604,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46066.488453171296</v>
+        <v>46066.32178650463</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.62955415509</v>
+        <v>46122.46288748842</v>
       </c>
       <c r="D22" s="5">
-        <v>46122.62957178241</v>
+        <v>46122.46290511574</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2669,13 +2669,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46066.48844994213</v>
+        <v>46066.32178327546</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.52550582176</v>
+        <v>46114.35883915509</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.525521250005</v>
+        <v>46114.35885458333</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2734,13 +2734,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46066.4884502662</v>
+        <v>46066.32178359954</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.623377384254</v>
+        <v>46157.4567107176</v>
       </c>
       <c r="D24" s="5">
-        <v>46184.581514722224</v>
+        <v>46184.41484805556</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2799,13 +2799,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46066.48845053241</v>
+        <v>46066.321783865744</v>
       </c>
       <c r="C25" s="8">
-        <v>46184.576328055555</v>
+        <v>46184.40966138889</v>
       </c>
       <c r="D25" s="8">
-        <v>46184.576358645834</v>
+        <v>46184.40969197916</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2850,13 +2850,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46066.48845078704</v>
+        <v>46066.32178412037</v>
       </c>
       <c r="C26" s="5">
-        <v>46128.626209062495</v>
+        <v>46128.45954239584</v>
       </c>
       <c r="D26" s="5">
-        <v>46128.62625043982</v>
+        <v>46128.45958377315</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2915,13 +2915,13 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46066.48845104167</v>
+        <v>46066.321784375</v>
       </c>
       <c r="C27" s="8">
-        <v>46128.62622789352</v>
+        <v>46128.45956122685</v>
       </c>
       <c r="D27" s="8">
-        <v>46128.62647177083</v>
+        <v>46128.45980510417</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -2976,13 +2976,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46066.488451296296</v>
+        <v>46066.32178462963</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.62622443287</v>
+        <v>46128.459557766204</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.62623707176</v>
+        <v>46128.45957040509</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3037,13 +3037,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46066.48845152778</v>
+        <v>46066.32178486111</v>
       </c>
       <c r="C29" s="8">
-        <v>46182.6798675</v>
+        <v>46182.51320083333</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.90442258102</v>
+        <v>46191.73775591435</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3102,13 +3102,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46066.488451770834</v>
+        <v>46066.32178510417</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.5436782176</v>
+        <v>46097.377011550925</v>
       </c>
       <c r="D30" s="5">
-        <v>46169.847689456015</v>
+        <v>46169.68102278935</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3163,11 +3163,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46066.48845204861</v>
+        <v>46066.321785381944</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46182.67989730324</v>
+        <v>46182.51323063657</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3222,13 +3222,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46066.48845232639</v>
+        <v>46066.32178565972</v>
       </c>
       <c r="C32" s="5">
-        <v>46126.86007825231</v>
+        <v>46126.69341158565</v>
       </c>
       <c r="D32" s="5">
-        <v>46126.86009107639</v>
+        <v>46126.69342440972</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3287,13 +3287,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46066.48845209491</v>
+        <v>46066.32178542824</v>
       </c>
       <c r="C33" s="8">
-        <v>46126.85960539352</v>
+        <v>46126.69293872685</v>
       </c>
       <c r="D33" s="8">
-        <v>46126.85960659722</v>
+        <v>46126.69293993055</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3348,13 +3348,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46066.48845266204</v>
+        <v>46066.32178599537</v>
       </c>
       <c r="C34" s="5">
-        <v>46126.859660057875</v>
+        <v>46126.6929933912</v>
       </c>
       <c r="D34" s="5">
-        <v>46126.85966126157</v>
+        <v>46126.69299459491</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3409,13 +3409,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46066.488452986116</v>
+        <v>46066.321786319444</v>
       </c>
       <c r="C35" s="8">
-        <v>46126.807703032406</v>
+        <v>46126.64103636574</v>
       </c>
       <c r="D35" s="8">
-        <v>46176.19802159722</v>
+        <v>46176.03135493056</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3474,13 +3474,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46066.488453321756</v>
+        <v>46066.32178665509</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.54288607639</v>
+        <v>46097.37621940972</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.54288770833</v>
+        <v>46097.37622104167</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3535,13 +3535,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46066.48845363426</v>
+        <v>46066.321786967594</v>
       </c>
       <c r="C37" s="8">
-        <v>46126.80768694445</v>
+        <v>46126.64102027778</v>
       </c>
       <c r="D37" s="8">
-        <v>46126.807688877314</v>
+        <v>46126.64102221065</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3596,13 +3596,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46066.48845402778</v>
+        <v>46066.321787361114</v>
       </c>
       <c r="C38" s="5">
-        <v>46114.526590381945</v>
+        <v>46114.35992371528</v>
       </c>
       <c r="D38" s="5">
-        <v>46114.52659163195</v>
+        <v>46114.359924965276</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3657,13 +3657,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46066.488454363425</v>
+        <v>46066.32178769676</v>
       </c>
       <c r="C39" s="8">
-        <v>46157.62563210649</v>
+        <v>46157.458965439815</v>
       </c>
       <c r="D39" s="8">
-        <v>46157.62564773148</v>
+        <v>46157.45898106482</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3722,13 +3722,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46066.48845471065</v>
+        <v>46066.32178804398</v>
       </c>
       <c r="C40" s="5">
-        <v>46157.62343446759</v>
+        <v>46157.456767800926</v>
       </c>
       <c r="D40" s="5">
-        <v>46157.623435497684</v>
+        <v>46157.45676883102</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3783,13 +3783,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46066.48845502315</v>
+        <v>46066.32178835648</v>
       </c>
       <c r="C41" s="8">
-        <v>46157.6235034375</v>
+        <v>46157.456836770834</v>
       </c>
       <c r="D41" s="8">
-        <v>46157.6235046875</v>
+        <v>46157.45683802084</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -3844,13 +3844,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46066.48845533565</v>
+        <v>46066.32178866898</v>
       </c>
       <c r="C42" s="5">
-        <v>46154.86731165509</v>
+        <v>46154.70064498842</v>
       </c>
       <c r="D42" s="5">
-        <v>46157.62625247685</v>
+        <v>46157.45958581018</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3909,13 +3909,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46066.48845152778</v>
+        <v>46066.32178486111</v>
       </c>
       <c r="C43" s="8">
-        <v>46154.86717563657</v>
+        <v>46154.70050896991</v>
       </c>
       <c r="D43" s="8">
-        <v>46154.86717763889</v>
+        <v>46154.70051097222</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3970,13 +3970,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46066.488452164354</v>
+        <v>46066.32178549768</v>
       </c>
       <c r="C44" s="5">
-        <v>46154.86724839121</v>
+        <v>46154.70058172454</v>
       </c>
       <c r="D44" s="5">
-        <v>46154.86724965277</v>
+        <v>46154.700582986115</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4031,13 +4031,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46066.48845261574</v>
+        <v>46066.32178594907</v>
       </c>
       <c r="C45" s="8">
-        <v>46210.52807011574</v>
+        <v>46210.361403449075</v>
       </c>
       <c r="D45" s="8">
-        <v>46210.52808679398</v>
+        <v>46210.361420127316</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4084,13 +4084,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.75399846065</v>
+        <v>46070.587331793984</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.526401400464</v>
+        <v>46114.35973473379</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.52642072916</v>
+        <v>46114.359754062505</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4149,13 +4149,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46066.48845297453</v>
+        <v>46066.321786307875</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.5266481713</v>
+        <v>46114.35998150463</v>
       </c>
       <c r="D47" s="8">
-        <v>46114.526663310186</v>
+        <v>46114.359996643514</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>167</v>
@@ -4214,13 +4214,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.64445680556</v>
+        <v>46091.47779013889</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.52669101852</v>
+        <v>46114.36002435185</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.526705543976</v>
+        <v>46114.36003887732</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4277,11 +4277,11 @@
         <v>178</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.6445032176</v>
+        <v>46091.47783655093</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46198.82239263889</v>
+        <v>46198.65572597222</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>179</v>
@@ -4338,13 +4338,13 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46066.48845348379</v>
+        <v>46066.321786817134</v>
       </c>
       <c r="C50" s="5">
-        <v>46157.6332930787</v>
+        <v>46157.46662641204</v>
       </c>
       <c r="D50" s="5">
-        <v>46157.63338287037</v>
+        <v>46157.46671620371</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4387,13 +4387,13 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46066.48845392361</v>
+        <v>46066.321787256944</v>
       </c>
       <c r="C51" s="8">
-        <v>46157.625740578704</v>
+        <v>46157.45907391203</v>
       </c>
       <c r="D51" s="8">
-        <v>46157.625757002315</v>
+        <v>46157.459090335644</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4452,13 +4452,13 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46066.48845438658</v>
+        <v>46066.321787719906</v>
       </c>
       <c r="C52" s="5">
-        <v>46157.633274479165</v>
+        <v>46157.4666078125</v>
       </c>
       <c r="D52" s="5">
-        <v>46157.6332940162</v>
+        <v>46157.46662734954</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4517,13 +4517,13 @@
         <v>197</v>
       </c>
       <c r="B53" s="8">
-        <v>46066.48845478009</v>
+        <v>46066.321788113426</v>
       </c>
       <c r="C53" s="8">
-        <v>46209.915449293985</v>
+        <v>46209.74878262731</v>
       </c>
       <c r="D53" s="8">
-        <v>46209.91546185185</v>
+        <v>46209.74879518518</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>198</v>
@@ -4570,13 +4570,13 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46066.48845520834</v>
+        <v>46066.32178854167</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.69727907407</v>
+        <v>46195.53061240741</v>
       </c>
       <c r="D54" s="5">
-        <v>46195.69729675926</v>
+        <v>46195.53063009259</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4635,13 +4635,13 @@
         <v>205</v>
       </c>
       <c r="B55" s="8">
-        <v>46066.4884557176</v>
+        <v>46066.321789050926</v>
       </c>
       <c r="C55" s="8">
-        <v>46204.594040208336</v>
+        <v>46204.427373541665</v>
       </c>
       <c r="D55" s="8">
-        <v>46211.525319189815</v>
+        <v>46211.35865252315</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>206</v>
@@ -4700,13 +4700,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46066.48845053241</v>
+        <v>46066.321783865744</v>
       </c>
       <c r="C56" s="5">
-        <v>46209.9154271875</v>
+        <v>46209.74876052083</v>
       </c>
       <c r="D56" s="5">
-        <v>46211.57175387732</v>
+        <v>46211.405087210645</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4765,11 +4765,11 @@
         <v>213</v>
       </c>
       <c r="B57" s="8">
-        <v>46066.488450902776</v>
+        <v>46066.32178423611</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.7832978125</v>
+        <v>46191.61663114584</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>185</v>
@@ -4812,13 +4812,13 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46066.48845119213</v>
+        <v>46066.32178452546</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.78328978009</v>
+        <v>46191.61662311343</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.783308530095</v>
+        <v>46191.616641863424</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>216</v>
@@ -4877,13 +4877,13 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46066.488451446756</v>
+        <v>46066.32178478009</v>
       </c>
       <c r="C59" s="8">
-        <v>46127.655113113426</v>
+        <v>46127.48844644676</v>
       </c>
       <c r="D59" s="8">
-        <v>46127.65513109954</v>
+        <v>46127.48846443287</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>219</v>
@@ -4942,13 +4942,13 @@
         <v>221</v>
       </c>
       <c r="B60" s="5">
-        <v>46066.48845172454</v>
+        <v>46066.321785057866</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.655216354164</v>
+        <v>46127.4885496875</v>
       </c>
       <c r="D60" s="5">
-        <v>46178.18717369213</v>
+        <v>46178.02050702546</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>222</v>
@@ -5007,11 +5007,11 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46066.48845202546</v>
+        <v>46066.3217853588</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46182.67990290509</v>
+        <v>46182.513236238425</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>55</v>
@@ -5070,11 +5070,11 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46066.488452314814</v>
+        <v>46066.32178564815</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46192.78934293981</v>
+        <v>46192.62267627315</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5133,11 +5133,11 @@
         <v>229</v>
       </c>
       <c r="B63" s="8">
-        <v>46066.48845259259</v>
+        <v>46066.32178592593</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46209.79759747685</v>
+        <v>46209.630930810185</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>230</v>
@@ -5180,11 +5180,11 @@
         <v>232</v>
       </c>
       <c r="B64" s="5">
-        <v>46066.48845287037</v>
+        <v>46066.321786203705</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46209.91544568287</v>
+        <v>46209.748779016205</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5243,11 +5243,11 @@
         <v>235</v>
       </c>
       <c r="B65" s="8">
-        <v>46066.488453136575</v>
+        <v>46066.32178646991</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46182.16889916667</v>
+        <v>46182.0022325</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>236</v>
@@ -5306,13 +5306,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46066.48845087963</v>
+        <v>46066.32178421297</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.590047060185</v>
+        <v>46197.42338039352</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.59006386574</v>
+        <v>46197.423397199076</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5371,13 +5371,13 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46066.4884515625</v>
+        <v>46066.32178489583</v>
       </c>
       <c r="C67" s="8">
-        <v>46209.79758950231</v>
+        <v>46209.63092283565</v>
       </c>
       <c r="D67" s="8">
-        <v>46209.797607395834</v>
+        <v>46209.63094072917</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5436,11 +5436,11 @@
         <v>245</v>
       </c>
       <c r="B68" s="5">
-        <v>46066.488451909725</v>
+        <v>46066.32178524305</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46165.170468530094</v>
+        <v>46165.00380186342</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -5499,11 +5499,11 @@
         <v>248</v>
       </c>
       <c r="B69" s="8">
-        <v>46066.48845236111</v>
+        <v>46066.32178569444</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46209.797597094905</v>
+        <v>46209.63093042824</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>182</v>
@@ -5560,11 +5560,11 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46066.488452777776</v>
+        <v>46066.32178611111</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46185.17160148148</v>
+        <v>46185.00493481482</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>183</v>
@@ -5621,11 +5621,11 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46066.48845318287</v>
+        <v>46066.3217865162</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.65141318287</v>
+        <v>46091.4847465162</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5668,11 +5668,11 @@
         <v>255</v>
       </c>
       <c r="B72" s="5">
-        <v>46066.488453541664</v>
+        <v>46066.321786875</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46185.17160149306</v>
+        <v>46185.004934826386</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>251</v>
@@ -5731,11 +5731,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46066.48845391204</v>
+        <v>46066.32178724537</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46190.176506909724</v>
+        <v>46190.00984024306</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5794,11 +5794,11 @@
         <v>263</v>
       </c>
       <c r="B74" s="5">
-        <v>46066.48845425926</v>
+        <v>46066.32178759259</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46191.17529449074</v>
+        <v>46191.00862782408</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -5857,11 +5857,11 @@
         <v>268</v>
       </c>
       <c r="B75" s="8">
-        <v>46066.4884545949</v>
+        <v>46066.321787928246</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46192.196944131945</v>
+        <v>46192.03027746528</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>269</v>
@@ -5920,11 +5920,11 @@
         <v>271</v>
       </c>
       <c r="B76" s="5">
-        <v>46066.488451261575</v>
+        <v>46066.32178459491</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.6514128125</v>
+        <v>46091.484746145834</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>272</v>
@@ -5967,11 +5967,11 @@
         <v>274</v>
       </c>
       <c r="B77" s="8">
-        <v>46066.4884515625</v>
+        <v>46066.32178489583</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46203.19655709491</v>
+        <v>46203.02989042824</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>275</v>
@@ -6030,11 +6030,11 @@
         <v>279</v>
       </c>
       <c r="B78" s="5">
-        <v>46066.48845186342</v>
+        <v>46066.321785196764</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46203.19655721065</v>
+        <v>46203.029890543985</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>280</v>
@@ -6093,11 +6093,11 @@
         <v>281</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.64460730324</v>
+        <v>46091.47794063657</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.65200450231</v>
+        <v>46091.48533783565</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>282</v>
@@ -6146,11 +6146,11 @@
         <v>284</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.64498898148</v>
+        <v>46091.47832231481</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46204.19897075232</v>
+        <v>46204.032304085646</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>285</v>
@@ -6209,11 +6209,11 @@
         <v>287</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.64515803241</v>
+        <v>46091.47849136574</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46205.20006973379</v>
+        <v>46205.03340306713</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>288</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -1504,13 +1504,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46066.32178303241</v>
+        <v>46066.48844969907</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55563092593</v>
+        <v>46092.7222975926</v>
       </c>
       <c r="D4" s="5">
-        <v>46109.57094042824</v>
+        <v>46109.73760709491</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1553,13 +1553,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46066.32178334491</v>
+        <v>46066.48845001157</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55560032408</v>
+        <v>46092.72226699074</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.71756133102</v>
+        <v>46133.88422799768</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1616,13 +1616,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46066.32178355324</v>
+        <v>46066.488450219906</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55560085648</v>
+        <v>46092.722267523146</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.555631469906</v>
+        <v>46092.72229813658</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1679,13 +1679,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46066.32178377315</v>
+        <v>46066.488450439814</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55560128472</v>
+        <v>46092.722267951394</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.55563128472</v>
+        <v>46092.72229795139</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1742,13 +1742,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46066.32178399306</v>
+        <v>46066.48845065972</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55560170139</v>
+        <v>46092.72226836806</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.60722690972</v>
+        <v>46100.77389357639</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1805,13 +1805,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46066.321784201384</v>
+        <v>46066.488450868055</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55560238426</v>
+        <v>46092.72226905092</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55563133102</v>
+        <v>46092.72229799769</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1868,11 +1868,11 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46066.32178439815</v>
+        <v>46066.48845106481</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.376563125</v>
+        <v>46097.54322979167</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1915,13 +1915,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46066.32178462963</v>
+        <v>46066.488451296296</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.37655447917</v>
+        <v>46097.54322114583</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.376569224536</v>
+        <v>46097.54323589121</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1980,11 +1980,11 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46066.321784872685</v>
+        <v>46066.48845153935</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46155.00118040509</v>
+        <v>46155.16784707176</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2043,13 +2043,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46066.32178510417</v>
+        <v>46066.488451770834</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.35867421296</v>
+        <v>46114.52534087963</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.35870145833</v>
+        <v>46114.525368125</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2096,13 +2096,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46066.32178384259</v>
+        <v>46066.48845050926</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.376044143515</v>
+        <v>46097.54271081019</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.37605961805</v>
+        <v>46097.54272628472</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2161,13 +2161,13 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46066.321784432876</v>
+        <v>46066.48845109953</v>
       </c>
       <c r="C15" s="8">
-        <v>46113.40140357639</v>
+        <v>46113.568070243055</v>
       </c>
       <c r="D15" s="8">
-        <v>46113.40142040509</v>
+        <v>46113.56808707176</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2226,13 +2226,13 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46066.321784687505</v>
+        <v>46066.48845135416</v>
       </c>
       <c r="C16" s="5">
-        <v>46114.35864662037</v>
+        <v>46114.52531328704</v>
       </c>
       <c r="D16" s="5">
-        <v>46114.358664837964</v>
+        <v>46114.52533150463</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2291,13 +2291,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46066.321784942134</v>
+        <v>46066.48845160879</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.35865797454</v>
+        <v>46114.5253246412</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.3586750463</v>
+        <v>46114.525341712964</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2356,13 +2356,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>46066.32178550926</v>
+        <v>46066.48845217592</v>
       </c>
       <c r="C18" s="5">
-        <v>46167.38724696759</v>
+        <v>46167.553913634256</v>
       </c>
       <c r="D18" s="5">
-        <v>46167.38726354166</v>
+        <v>46167.553930208334</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2409,13 +2409,13 @@
         <v>78</v>
       </c>
       <c r="B19" s="8">
-        <v>46066.32178576389</v>
+        <v>46066.48845243055</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.376137893516</v>
+        <v>46097.54280456019</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.37615408565</v>
+        <v>46097.542820752315</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>79</v>
@@ -2474,13 +2474,13 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>46066.32178601852</v>
+        <v>46066.48845268518</v>
       </c>
       <c r="C20" s="5">
-        <v>46114.35878704861</v>
+        <v>46114.52545371528</v>
       </c>
       <c r="D20" s="5">
-        <v>46114.358918530095</v>
+        <v>46114.52558519676</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>82</v>
@@ -2539,13 +2539,13 @@
         <v>84</v>
       </c>
       <c r="B21" s="8">
-        <v>46066.32178626157</v>
+        <v>46066.48845292824</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.3766475463</v>
+        <v>46097.54331421296</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.37666384259</v>
+        <v>46097.54333050926</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>85</v>
@@ -2604,13 +2604,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46066.32178650463</v>
+        <v>46066.488453171296</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.46288748842</v>
+        <v>46122.62955415509</v>
       </c>
       <c r="D22" s="5">
-        <v>46122.46290511574</v>
+        <v>46122.62957178241</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2669,13 +2669,13 @@
         <v>91</v>
       </c>
       <c r="B23" s="8">
-        <v>46066.32178327546</v>
+        <v>46066.48844994213</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.35883915509</v>
+        <v>46114.52550582176</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.35885458333</v>
+        <v>46114.525521250005</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>92</v>
@@ -2734,13 +2734,13 @@
         <v>94</v>
       </c>
       <c r="B24" s="5">
-        <v>46066.32178359954</v>
+        <v>46066.4884502662</v>
       </c>
       <c r="C24" s="5">
-        <v>46157.4567107176</v>
+        <v>46157.623377384254</v>
       </c>
       <c r="D24" s="5">
-        <v>46184.41484805556</v>
+        <v>46184.581514722224</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>95</v>
@@ -2799,13 +2799,13 @@
         <v>99</v>
       </c>
       <c r="B25" s="8">
-        <v>46066.321783865744</v>
+        <v>46066.48845053241</v>
       </c>
       <c r="C25" s="8">
-        <v>46184.40966138889</v>
+        <v>46184.576328055555</v>
       </c>
       <c r="D25" s="8">
-        <v>46184.40969197916</v>
+        <v>46184.576358645834</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>100</v>
@@ -2850,13 +2850,13 @@
         <v>102</v>
       </c>
       <c r="B26" s="5">
-        <v>46066.32178412037</v>
+        <v>46066.48845078704</v>
       </c>
       <c r="C26" s="5">
-        <v>46128.45954239584</v>
+        <v>46128.626209062495</v>
       </c>
       <c r="D26" s="5">
-        <v>46128.45958377315</v>
+        <v>46128.62625043982</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>103</v>
@@ -2915,13 +2915,13 @@
         <v>108</v>
       </c>
       <c r="B27" s="8">
-        <v>46066.321784375</v>
+        <v>46066.48845104167</v>
       </c>
       <c r="C27" s="8">
-        <v>46128.45956122685</v>
+        <v>46128.62622789352</v>
       </c>
       <c r="D27" s="8">
-        <v>46128.45980510417</v>
+        <v>46128.62647177083</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>109</v>
@@ -2976,13 +2976,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46066.32178462963</v>
+        <v>46066.488451296296</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.459557766204</v>
+        <v>46128.62622443287</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.45957040509</v>
+        <v>46128.62623707176</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3037,13 +3037,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46066.32178486111</v>
+        <v>46066.48845152778</v>
       </c>
       <c r="C29" s="8">
-        <v>46182.51320083333</v>
+        <v>46182.6798675</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.73775591435</v>
+        <v>46191.90442258102</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3102,13 +3102,13 @@
         <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46066.32178510417</v>
+        <v>46066.488451770834</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.377011550925</v>
+        <v>46097.5436782176</v>
       </c>
       <c r="D30" s="5">
-        <v>46169.68102278935</v>
+        <v>46169.847689456015</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3163,11 +3163,11 @@
         <v>121</v>
       </c>
       <c r="B31" s="8">
-        <v>46066.321785381944</v>
+        <v>46066.48845204861</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46182.51323063657</v>
+        <v>46182.67989730324</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>122</v>
@@ -3222,13 +3222,13 @@
         <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46066.32178565972</v>
+        <v>46066.48845232639</v>
       </c>
       <c r="C32" s="5">
-        <v>46126.69341158565</v>
+        <v>46126.86007825231</v>
       </c>
       <c r="D32" s="5">
-        <v>46126.69342440972</v>
+        <v>46126.86009107639</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>125</v>
@@ -3287,13 +3287,13 @@
         <v>127</v>
       </c>
       <c r="B33" s="8">
-        <v>46066.32178542824</v>
+        <v>46066.48845209491</v>
       </c>
       <c r="C33" s="8">
-        <v>46126.69293872685</v>
+        <v>46126.85960539352</v>
       </c>
       <c r="D33" s="8">
-        <v>46126.69293993055</v>
+        <v>46126.85960659722</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>128</v>
@@ -3348,13 +3348,13 @@
         <v>130</v>
       </c>
       <c r="B34" s="5">
-        <v>46066.32178599537</v>
+        <v>46066.48845266204</v>
       </c>
       <c r="C34" s="5">
-        <v>46126.6929933912</v>
+        <v>46126.859660057875</v>
       </c>
       <c r="D34" s="5">
-        <v>46126.69299459491</v>
+        <v>46126.85966126157</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>
@@ -3409,13 +3409,13 @@
         <v>133</v>
       </c>
       <c r="B35" s="8">
-        <v>46066.321786319444</v>
+        <v>46066.488452986116</v>
       </c>
       <c r="C35" s="8">
-        <v>46126.64103636574</v>
+        <v>46126.807703032406</v>
       </c>
       <c r="D35" s="8">
-        <v>46176.03135493056</v>
+        <v>46176.19802159722</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -3474,13 +3474,13 @@
         <v>136</v>
       </c>
       <c r="B36" s="5">
-        <v>46066.32178665509</v>
+        <v>46066.488453321756</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.37621940972</v>
+        <v>46097.54288607639</v>
       </c>
       <c r="D36" s="5">
-        <v>46097.37622104167</v>
+        <v>46097.54288770833</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>137</v>
@@ -3535,13 +3535,13 @@
         <v>139</v>
       </c>
       <c r="B37" s="8">
-        <v>46066.321786967594</v>
+        <v>46066.48845363426</v>
       </c>
       <c r="C37" s="8">
-        <v>46126.64102027778</v>
+        <v>46126.80768694445</v>
       </c>
       <c r="D37" s="8">
-        <v>46126.64102221065</v>
+        <v>46126.807688877314</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>140</v>
@@ -3596,13 +3596,13 @@
         <v>142</v>
       </c>
       <c r="B38" s="5">
-        <v>46066.321787361114</v>
+        <v>46066.48845402778</v>
       </c>
       <c r="C38" s="5">
-        <v>46114.35992371528</v>
+        <v>46114.526590381945</v>
       </c>
       <c r="D38" s="5">
-        <v>46114.359924965276</v>
+        <v>46114.52659163195</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>143</v>
@@ -3657,13 +3657,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46066.32178769676</v>
+        <v>46066.488454363425</v>
       </c>
       <c r="C39" s="8">
-        <v>46157.458965439815</v>
+        <v>46157.62563210649</v>
       </c>
       <c r="D39" s="8">
-        <v>46157.45898106482</v>
+        <v>46157.62564773148</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3722,13 +3722,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46066.32178804398</v>
+        <v>46066.48845471065</v>
       </c>
       <c r="C40" s="5">
-        <v>46157.456767800926</v>
+        <v>46157.62343446759</v>
       </c>
       <c r="D40" s="5">
-        <v>46157.45676883102</v>
+        <v>46157.623435497684</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3783,13 +3783,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="8">
-        <v>46066.32178835648</v>
+        <v>46066.48845502315</v>
       </c>
       <c r="C41" s="8">
-        <v>46157.456836770834</v>
+        <v>46157.6235034375</v>
       </c>
       <c r="D41" s="8">
-        <v>46157.45683802084</v>
+        <v>46157.6235046875</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>154</v>
@@ -3844,13 +3844,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46066.32178866898</v>
+        <v>46066.48845533565</v>
       </c>
       <c r="C42" s="5">
-        <v>46154.70064498842</v>
+        <v>46154.86731165509</v>
       </c>
       <c r="D42" s="5">
-        <v>46157.45958581018</v>
+        <v>46157.62625247685</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3909,13 +3909,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="8">
-        <v>46066.32178486111</v>
+        <v>46066.48845152778</v>
       </c>
       <c r="C43" s="8">
-        <v>46154.70050896991</v>
+        <v>46154.86717563657</v>
       </c>
       <c r="D43" s="8">
-        <v>46154.70051097222</v>
+        <v>46154.86717763889</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>160</v>
@@ -3970,13 +3970,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46066.32178549768</v>
+        <v>46066.488452164354</v>
       </c>
       <c r="C44" s="5">
-        <v>46154.70058172454</v>
+        <v>46154.86724839121</v>
       </c>
       <c r="D44" s="5">
-        <v>46154.700582986115</v>
+        <v>46154.86724965277</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4031,13 +4031,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46066.32178594907</v>
+        <v>46066.48845261574</v>
       </c>
       <c r="C45" s="8">
-        <v>46210.361403449075</v>
+        <v>46210.52807011574</v>
       </c>
       <c r="D45" s="8">
-        <v>46210.361420127316</v>
+        <v>46210.52808679398</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4084,13 +4084,13 @@
         <v>168</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.587331793984</v>
+        <v>46070.75399846065</v>
       </c>
       <c r="C46" s="5">
-        <v>46114.35973473379</v>
+        <v>46114.526401400464</v>
       </c>
       <c r="D46" s="5">
-        <v>46114.359754062505</v>
+        <v>46114.52642072916</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>169</v>
@@ -4149,13 +4149,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46066.321786307875</v>
+        <v>46066.48845297453</v>
       </c>
       <c r="C47" s="8">
-        <v>46114.35998150463</v>
+        <v>46114.5266481713</v>
       </c>
       <c r="D47" s="8">
-        <v>46114.359996643514</v>
+        <v>46114.526663310186</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>167</v>
@@ -4214,13 +4214,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46091.47779013889</v>
+        <v>46091.64445680556</v>
       </c>
       <c r="C48" s="5">
-        <v>46114.36002435185</v>
+        <v>46114.52669101852</v>
       </c>
       <c r="D48" s="5">
-        <v>46114.36003887732</v>
+        <v>46114.526705543976</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4277,11 +4277,11 @@
         <v>178</v>
       </c>
       <c r="B49" s="8">
-        <v>46091.47783655093</v>
+        <v>46091.6445032176</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46198.65572597222</v>
+        <v>46198.82239263889</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>179</v>
@@ -4338,13 +4338,13 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46066.321786817134</v>
+        <v>46066.48845348379</v>
       </c>
       <c r="C50" s="5">
-        <v>46157.46662641204</v>
+        <v>46157.6332930787</v>
       </c>
       <c r="D50" s="5">
-        <v>46157.46671620371</v>
+        <v>46157.63338287037</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4387,13 +4387,13 @@
         <v>187</v>
       </c>
       <c r="B51" s="8">
-        <v>46066.321787256944</v>
+        <v>46066.48845392361</v>
       </c>
       <c r="C51" s="8">
-        <v>46157.45907391203</v>
+        <v>46157.625740578704</v>
       </c>
       <c r="D51" s="8">
-        <v>46157.459090335644</v>
+        <v>46157.625757002315</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>188</v>
@@ -4452,13 +4452,13 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46066.321787719906</v>
+        <v>46066.48845438658</v>
       </c>
       <c r="C52" s="5">
-        <v>46157.4666078125</v>
+        <v>46157.633274479165</v>
       </c>
       <c r="D52" s="5">
-        <v>46157.46662734954</v>
+        <v>46157.6332940162</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4517,13 +4517,13 @@
         <v>197</v>
       </c>
       <c r="B53" s="8">
-        <v>46066.321788113426</v>
+        <v>46066.48845478009</v>
       </c>
       <c r="C53" s="8">
-        <v>46209.74878262731</v>
+        <v>46209.915449293985</v>
       </c>
       <c r="D53" s="8">
-        <v>46209.74879518518</v>
+        <v>46209.91546185185</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>198</v>
@@ -4570,13 +4570,13 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46066.32178854167</v>
+        <v>46066.48845520834</v>
       </c>
       <c r="C54" s="5">
-        <v>46195.53061240741</v>
+        <v>46195.69727907407</v>
       </c>
       <c r="D54" s="5">
-        <v>46195.53063009259</v>
+        <v>46195.69729675926</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4635,13 +4635,13 @@
         <v>205</v>
       </c>
       <c r="B55" s="8">
-        <v>46066.321789050926</v>
+        <v>46066.4884557176</v>
       </c>
       <c r="C55" s="8">
-        <v>46204.427373541665</v>
+        <v>46204.594040208336</v>
       </c>
       <c r="D55" s="8">
-        <v>46211.35865252315</v>
+        <v>46211.525319189815</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>206</v>
@@ -4700,13 +4700,13 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46066.321783865744</v>
+        <v>46066.48845053241</v>
       </c>
       <c r="C56" s="5">
-        <v>46209.74876052083</v>
+        <v>46209.9154271875</v>
       </c>
       <c r="D56" s="5">
-        <v>46211.405087210645</v>
+        <v>46211.57175387732</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4765,11 +4765,11 @@
         <v>213</v>
       </c>
       <c r="B57" s="8">
-        <v>46066.32178423611</v>
+        <v>46066.488450902776</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.61663114584</v>
+        <v>46191.7832978125</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>185</v>
@@ -4812,13 +4812,13 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46066.32178452546</v>
+        <v>46066.48845119213</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.61662311343</v>
+        <v>46191.78328978009</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.616641863424</v>
+        <v>46191.783308530095</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>216</v>
@@ -4877,13 +4877,13 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46066.32178478009</v>
+        <v>46066.488451446756</v>
       </c>
       <c r="C59" s="8">
-        <v>46127.48844644676</v>
+        <v>46127.655113113426</v>
       </c>
       <c r="D59" s="8">
-        <v>46127.48846443287</v>
+        <v>46127.65513109954</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>219</v>
@@ -4942,13 +4942,13 @@
         <v>221</v>
       </c>
       <c r="B60" s="5">
-        <v>46066.321785057866</v>
+        <v>46066.48845172454</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.4885496875</v>
+        <v>46127.655216354164</v>
       </c>
       <c r="D60" s="5">
-        <v>46178.02050702546</v>
+        <v>46178.18717369213</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>222</v>
@@ -5007,11 +5007,11 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46066.3217853588</v>
+        <v>46066.48845202546</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46182.513236238425</v>
+        <v>46182.67990290509</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>55</v>
@@ -5070,11 +5070,11 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46066.32178564815</v>
+        <v>46066.488452314814</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46192.62267627315</v>
+        <v>46192.78934293981</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5133,11 +5133,11 @@
         <v>229</v>
       </c>
       <c r="B63" s="8">
-        <v>46066.32178592593</v>
+        <v>46066.48845259259</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46209.630930810185</v>
+        <v>46209.79759747685</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>230</v>
@@ -5180,11 +5180,11 @@
         <v>232</v>
       </c>
       <c r="B64" s="5">
-        <v>46066.321786203705</v>
+        <v>46066.48845287037</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46209.748779016205</v>
+        <v>46209.91544568287</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5243,11 +5243,11 @@
         <v>235</v>
       </c>
       <c r="B65" s="8">
-        <v>46066.32178646991</v>
+        <v>46066.488453136575</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46182.0022325</v>
+        <v>46182.16889916667</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>236</v>
@@ -5306,13 +5306,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46066.32178421297</v>
+        <v>46066.48845087963</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.42338039352</v>
+        <v>46197.590047060185</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.423397199076</v>
+        <v>46197.59006386574</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5371,13 +5371,13 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46066.32178489583</v>
+        <v>46066.4884515625</v>
       </c>
       <c r="C67" s="8">
-        <v>46209.63092283565</v>
+        <v>46209.79758950231</v>
       </c>
       <c r="D67" s="8">
-        <v>46209.63094072917</v>
+        <v>46209.797607395834</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5436,11 +5436,11 @@
         <v>245</v>
       </c>
       <c r="B68" s="5">
-        <v>46066.32178524305</v>
+        <v>46066.488451909725</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46165.00380186342</v>
+        <v>46165.170468530094</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -5499,11 +5499,11 @@
         <v>248</v>
       </c>
       <c r="B69" s="8">
-        <v>46066.32178569444</v>
+        <v>46066.48845236111</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46209.63093042824</v>
+        <v>46209.797597094905</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>182</v>
@@ -5560,11 +5560,11 @@
         <v>250</v>
       </c>
       <c r="B70" s="5">
-        <v>46066.32178611111</v>
+        <v>46066.488452777776</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46185.00493481482</v>
+        <v>46185.17160148148</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>183</v>
@@ -5621,11 +5621,11 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46066.3217865162</v>
+        <v>46066.48845318287</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.4847465162</v>
+        <v>46091.65141318287</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5668,11 +5668,11 @@
         <v>255</v>
       </c>
       <c r="B72" s="5">
-        <v>46066.321786875</v>
+        <v>46066.488453541664</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46185.004934826386</v>
+        <v>46185.17160149306</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>251</v>
@@ -5731,11 +5731,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46066.32178724537</v>
+        <v>46066.48845391204</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46190.00984024306</v>
+        <v>46190.176506909724</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5794,11 +5794,11 @@
         <v>263</v>
       </c>
       <c r="B74" s="5">
-        <v>46066.32178759259</v>
+        <v>46066.48845425926</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46191.00862782408</v>
+        <v>46191.17529449074</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -5857,11 +5857,11 @@
         <v>268</v>
       </c>
       <c r="B75" s="8">
-        <v>46066.321787928246</v>
+        <v>46066.4884545949</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46192.03027746528</v>
+        <v>46192.196944131945</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>269</v>
@@ -5920,11 +5920,11 @@
         <v>271</v>
       </c>
       <c r="B76" s="5">
-        <v>46066.32178459491</v>
+        <v>46066.488451261575</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.484746145834</v>
+        <v>46091.6514128125</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>272</v>
@@ -5967,11 +5967,11 @@
         <v>274</v>
       </c>
       <c r="B77" s="8">
-        <v>46066.32178489583</v>
+        <v>46066.4884515625</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46203.02989042824</v>
+        <v>46203.19655709491</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>275</v>
@@ -6030,11 +6030,11 @@
         <v>279</v>
       </c>
       <c r="B78" s="5">
-        <v>46066.321785196764</v>
+        <v>46066.48845186342</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46203.029890543985</v>
+        <v>46203.19655721065</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>280</v>
@@ -6093,11 +6093,11 @@
         <v>281</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.47794063657</v>
+        <v>46091.64460730324</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.48533783565</v>
+        <v>46091.65200450231</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>282</v>
@@ -6146,11 +6146,11 @@
         <v>284</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.47832231481</v>
+        <v>46091.64498898148</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46204.032304085646</v>
+        <v>46204.19897075232</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>285</v>
@@ -6209,11 +6209,11 @@
         <v>287</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.47849136574</v>
+        <v>46091.64515803241</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46205.03340306713</v>
+        <v>46205.20006973379</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>288</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -6213,7 +6213,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46205.20006973379</v>
+        <v>46212.167523298616</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>288</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -181,7 +181,7 @@
     <t>Recepcion Tableros</t>
   </si>
   <si>
-    <t>Embalaje,Ingenieria de servicio:</t>
+    <t>ot 4221- 4222-4223 - Embalaje,Ingenieria de servicio:</t>
   </si>
   <si>
     <t>Baja</t>
@@ -544,7 +544,7 @@
     <t xml:space="preserve">Check Planos </t>
   </si>
   <si>
-    <t>Montaje Rodete,Montaje sensores y accesorios,Montaje Alabe,Montaje motor,Control de calidad Armado,Armado</t>
+    <t>ot 4221 -  Montaje Rodete,ot 4221 -  Montaje sensores y accesorios,ot 4221 -  Montaje Alabe,ot 4221 -  Montaje motor,Control de calidad Armado,Armado</t>
   </si>
   <si>
     <t>1213595645393033</t>
@@ -559,10 +559,10 @@
     <t>francisca.gonzalez@zitron.com</t>
   </si>
   <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
+    <t>ot 4221 -  Pruebas FAT</t>
+  </si>
+  <si>
+    <t>ot 4221 -  RE-PINTADO</t>
   </si>
   <si>
     <t>1213263334883446</t>
@@ -649,7 +649,7 @@
     <t xml:space="preserve">Armado,Check Planos </t>
   </si>
   <si>
-    <t>Fabricacion externa ,Revestimiento</t>
+    <t>Fabricacion externa ,ot 4221 - Revestimiento</t>
   </si>
   <si>
     <t>1213263334883453</t>
@@ -664,7 +664,7 @@
     <t>Recepcion Alabe</t>
   </si>
   <si>
-    <t>Bodega:,Montaje Alabe</t>
+    <t>Bodega:,ot 4221 -  Montaje Alabe</t>
   </si>
   <si>
     <t>1213263334883455</t>
@@ -673,7 +673,7 @@
     <t>Recepcion Rodete</t>
   </si>
   <si>
-    <t>Bodega:,Montaje Rodete</t>
+    <t>Bodega:,ot 4221 -  Montaje Rodete</t>
   </si>
   <si>
     <t>1213263334883456</t>
@@ -682,7 +682,7 @@
     <t>Recepcion Motor</t>
   </si>
   <si>
-    <t>Bodega:,Montaje motor</t>
+    <t>Bodega:,ot 4221 -  Montaje motor</t>
   </si>
   <si>
     <t>1213263334883457</t>
@@ -697,7 +697,7 @@
     <t>Recepcion sensores y accesorios</t>
   </si>
   <si>
-    <t>Bodega:,Montaje sensores y accesorios</t>
+    <t>Bodega:,ot 4221 -  Montaje sensores y accesorios</t>
   </si>
   <si>
     <t>1213263334883459</t>
@@ -706,67 +706,67 @@
     <t>Montaje:</t>
   </si>
   <si>
-    <t>Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensores y accesorios</t>
+    <t>ot 4221 - Revestimiento,ot 4221 -  Montaje motor,ot 4221 -  Montaje Alabe,ot 4221 -  Montaje Rodete,ot 4221 -  Montaje sensores y accesorios</t>
   </si>
   <si>
     <t>1213263334883460</t>
   </si>
   <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje Rodete,Montaje sensores y accesorios,Montaje Alabe,Montaje motor</t>
+    <t>ot 4221 - Revestimiento</t>
+  </si>
+  <si>
+    <t>Montaje:,ot 4221 -  Montaje Rodete,ot 4221 -  Montaje sensores y accesorios,ot 4221 -  Montaje Alabe,ot 4221 -  Montaje motor</t>
   </si>
   <si>
     <t>1213263334883461</t>
   </si>
   <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento,Recepcion Motor,Check Planos </t>
-  </si>
-  <si>
-    <t>Pruebas FAT,Montaje:</t>
+    <t>ot 4221 -  Montaje motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot 4221 - Revestimiento,Recepcion Motor,Check Planos </t>
+  </si>
+  <si>
+    <t>ot 4221 -  Pruebas FAT,Montaje:</t>
   </si>
   <si>
     <t>1213263334883462</t>
   </si>
   <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento,Recepcion Alabe,Check Planos </t>
+    <t>ot 4221 -  Montaje Alabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot 4221 - Revestimiento,Recepcion Alabe,Check Planos </t>
   </si>
   <si>
     <t>1213263334883463</t>
   </si>
   <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento,Recepcion Rodete,Check Planos </t>
+    <t>ot 4221 -  Montaje Rodete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot 4221 - Revestimiento,Recepcion Rodete,Check Planos </t>
   </si>
   <si>
     <t>1213263336252671</t>
   </si>
   <si>
-    <t>Montaje sensores y accesorios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento,Recepcion sensores y accesorios,Check Planos </t>
+    <t>ot 4221 -  Montaje sensores y accesorios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot 4221 - Revestimiento,Recepcion sensores y accesorios,Check Planos </t>
   </si>
   <si>
     <t>1213263336252672</t>
   </si>
   <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensores y accesorios</t>
+    <t>ot 4221 -  Montaje motor,ot 4221 -  Montaje Alabe,ot 4221 -  Montaje Rodete,ot 4221 -  Montaje sensores y accesorios</t>
   </si>
   <si>
     <t>1213263336252673</t>
   </si>
   <si>
-    <t>Coordinacion Entrega con Cliente</t>
+    <t>ot 4221- 4222-4223Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1213263336252674</t>
@@ -775,7 +775,7 @@
     <t>Logistica:</t>
   </si>
   <si>
-    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
+    <t>ot 4221- 4222-4223Coordinacion Entrega con Cliente,ot 4221- 4222-4223 - Embalaje,ot 4221- 4222-4223PACKING LIST,ot 4196 - 4197-4198 Despacho</t>
   </si>
   <si>
     <t>1213263336252675</t>
@@ -787,25 +787,25 @@
     <t>kpinto@zitron.com</t>
   </si>
   <si>
-    <t>Embalaje,Logistica:</t>
+    <t>ot 4221- 4222-4223 - Embalaje,Logistica:</t>
   </si>
   <si>
     <t>1213263336252676</t>
   </si>
   <si>
-    <t>Embalaje</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Revision tableros pruebas</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Logistica:</t>
+    <t>ot 4221- 4222-4223 - Embalaje</t>
+  </si>
+  <si>
+    <t>ot 4221- 4222-4223Coordinacion Entrega con Cliente,Revision tableros pruebas</t>
+  </si>
+  <si>
+    <t>ot 4221- 4222-4223PACKING LIST,Logistica:</t>
   </si>
   <si>
     <t>1213263336252677</t>
   </si>
   <si>
-    <t>PACKING LIST</t>
+    <t>ot 4221- 4222-4223PACKING LIST</t>
   </si>
   <si>
     <t>Nicolás Mol</t>
@@ -814,13 +814,13 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>Despacho,Logistica:</t>
+    <t>ot 4221- 4222-4223Despacho,Logistica:</t>
   </si>
   <si>
     <t>1213263336252678</t>
   </si>
   <si>
-    <t>Despacho</t>
+    <t>ot 4221- 4222-4223Despacho</t>
   </si>
   <si>
     <t>Costos,Gestion,Instalación Componentes</t>
@@ -847,7 +847,7 @@
     <t>nicolas.tello@zitron.com</t>
   </si>
   <si>
-    <t>Despacho,Analisis de costeo</t>
+    <t>ot 4221- 4222-4223Despacho,Analisis de costeo</t>
   </si>
   <si>
     <t>1213263336252682</t>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46209.91544568287</v>
+        <v>46212.62747910879</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>233</v>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46182.16889916667</v>
+        <v>46212.62753224537</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>236</v>
@@ -5312,7 +5312,7 @@
         <v>46197.590047060185</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.59006386574</v>
+        <v>46212.627548449076</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5377,7 +5377,7 @@
         <v>46209.79758950231</v>
       </c>
       <c r="D67" s="8">
-        <v>46209.797607395834</v>
+        <v>46212.627565393515</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46165.170468530094</v>
+        <v>46212.62757856482</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46209.797597094905</v>
+        <v>46212.62758842592</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>182</v>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46185.17160148148</v>
+        <v>46212.627620520834</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>183</v>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46185.17160149306</v>
+        <v>46212.627884490736</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>251</v>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46190.176506909724</v>
+        <v>46212.62785697917</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46191.17529449074</v>
+        <v>46212.627920659725</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46192.196944131945</v>
+        <v>46212.627943680556</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>269</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -6213,7 +6213,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46212.167523298616</v>
+        <v>46213.17280854167</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>288</v>
@@ -6260,8 +6260,8 @@
       <c r="S81" s="9">
         <v>0</v>
       </c>
-      <c r="T81" s="12" t="s">
-        <v>117</v>
+      <c r="T81" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="U81" s="10" t="s">
         <v>58</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="286">
   <si>
     <t>50001506 - ZCO EPM FRIO AIRE</t>
   </si>
@@ -280,9 +280,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
   </si>
   <si>
@@ -299,12 +296,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales</t>
@@ -2619,11 +2610,9 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="5">
         <v>46036</v>
       </c>
@@ -2646,7 +2635,7 @@
         <v>66</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="5">
         <v>46036</v>
@@ -2666,7 +2655,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" s="8">
         <v>46066.48844994213</v>
@@ -2678,7 +2667,7 @@
         <v>46114.525521250005</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2711,7 +2700,7 @@
         <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="8">
         <v>46036</v>
@@ -2731,7 +2720,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46066.4884502662</v>
@@ -2743,17 +2732,15 @@
         <v>46184.581514722224</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>97</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H24" s="6"/>
       <c r="I24" s="5">
         <v>46036</v>
       </c>
@@ -2776,7 +2763,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="5">
         <v>46036</v>
@@ -2796,7 +2783,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B25" s="8">
         <v>46066.48845053241</v>
@@ -2808,7 +2795,7 @@
         <v>46184.576358645834</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2832,7 +2819,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2847,7 +2834,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5">
         <v>46066.48845078704</v>
@@ -2859,16 +2846,16 @@
         <v>46128.62625043982</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I26" s="5">
         <v>46038</v>
@@ -2886,13 +2873,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q26" s="5">
         <v>46038</v>
@@ -2907,12 +2894,12 @@
         <v>57</v>
       </c>
       <c r="U26" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B27" s="8">
         <v>46066.48845104167</v>
@@ -2924,16 +2911,16 @@
         <v>46128.62647177083</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I27" s="8">
         <v>46038</v>
@@ -2951,13 +2938,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2973,7 +2960,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B28" s="5">
         <v>46066.488451296296</v>
@@ -2985,16 +2972,16 @@
         <v>46128.62623707176</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I28" s="5">
         <v>46042</v>
@@ -3012,13 +2999,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3034,7 +3021,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B29" s="8">
         <v>46066.48845152778</v>
@@ -3046,16 +3033,16 @@
         <v>46191.90442258102</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I29" s="8">
         <v>46034</v>
@@ -3073,13 +3060,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q29" s="8">
         <v>46034</v>
@@ -3091,7 +3078,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="U29" s="11" t="s">
         <v>33</v>
@@ -3099,7 +3086,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46066.488451770834</v>
@@ -3111,16 +3098,16 @@
         <v>46169.847689456015</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I30" s="5">
         <v>46034</v>
@@ -3138,13 +3125,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3160,7 +3147,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46066.48845204861</v>
@@ -3170,16 +3157,16 @@
         <v>46182.67989730324</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I31" s="8">
         <v>46043</v>
@@ -3197,13 +3184,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3219,7 +3206,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46066.48845232639</v>
@@ -3231,16 +3218,16 @@
         <v>46126.86009107639</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I32" s="5">
         <v>46041</v>
@@ -3258,13 +3245,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q32" s="5">
         <v>46038</v>
@@ -3284,7 +3271,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B33" s="8">
         <v>46066.48845209491</v>
@@ -3296,16 +3283,16 @@
         <v>46126.85960659722</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I33" s="8">
         <v>46041</v>
@@ -3323,13 +3310,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>88</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3345,7 +3332,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46066.48845266204</v>
@@ -3357,16 +3344,16 @@
         <v>46126.85966126157</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I34" s="5">
         <v>46042</v>
@@ -3384,13 +3371,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="O34" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="O34" s="6" t="s">
-        <v>128</v>
-      </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3406,7 +3393,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B35" s="8">
         <v>46066.488452986116</v>
@@ -3418,16 +3405,16 @@
         <v>46176.19802159722</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I35" s="8">
         <v>46031</v>
@@ -3445,13 +3432,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q35" s="8">
         <v>46031</v>
@@ -3471,7 +3458,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46066.488453321756</v>
@@ -3483,16 +3470,16 @@
         <v>46097.54288770833</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I36" s="5">
         <v>46031</v>
@@ -3510,13 +3497,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3532,7 +3519,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B37" s="8">
         <v>46066.48845363426</v>
@@ -3544,16 +3531,16 @@
         <v>46126.807688877314</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I37" s="8">
         <v>46052</v>
@@ -3571,13 +3558,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="O37" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="O37" s="9" t="s">
-        <v>137</v>
-      </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3593,7 +3580,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46066.48845402778</v>
@@ -3605,16 +3592,16 @@
         <v>46114.52659163195</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I38" s="5">
         <v>46052</v>
@@ -3632,13 +3619,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="O38" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="O38" s="6" t="s">
-        <v>137</v>
-      </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3654,7 +3641,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B39" s="8">
         <v>46066.488454363425</v>
@@ -3666,16 +3653,16 @@
         <v>46157.62564773148</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I39" s="8">
         <v>46038</v>
@@ -3693,13 +3680,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q39" s="8">
         <v>46038</v>
@@ -3719,7 +3706,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46066.48845471065</v>
@@ -3731,16 +3718,16 @@
         <v>46157.623435497684</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I40" s="5">
         <v>46038</v>
@@ -3758,13 +3745,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3780,7 +3767,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46066.48845502315</v>
@@ -3792,16 +3779,16 @@
         <v>46157.6235046875</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I41" s="8">
         <v>46058</v>
@@ -3819,13 +3806,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3841,7 +3828,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46066.48845533565</v>
@@ -3853,16 +3840,16 @@
         <v>46157.62625247685</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I42" s="5">
         <v>46038</v>
@@ -3880,13 +3867,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q42" s="5">
         <v>46038</v>
@@ -3906,7 +3893,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B43" s="8">
         <v>46066.48845152778</v>
@@ -3918,16 +3905,16 @@
         <v>46154.86717763889</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I43" s="8">
         <v>46038</v>
@@ -3945,13 +3932,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3967,7 +3954,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46066.488452164354</v>
@@ -3979,16 +3966,16 @@
         <v>46154.86724965277</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I44" s="5">
         <v>46078</v>
@@ -4006,13 +3993,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="O44" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="O44" s="6" t="s">
-        <v>160</v>
-      </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4028,7 +4015,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46066.48845261574</v>
@@ -4040,7 +4027,7 @@
         <v>46210.52808679398</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4064,7 +4051,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4081,7 +4068,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46070.75399846065</v>
@@ -4093,16 +4080,16 @@
         <v>46114.52642072916</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I46" s="5">
         <v>46036</v>
@@ -4120,13 +4107,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q46" s="5">
         <v>46036</v>
@@ -4146,7 +4133,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46066.48845297453</v>
@@ -4158,16 +4145,16 @@
         <v>46114.526663310186</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>170</v>
-      </c>
       <c r="H47" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I47" s="8">
         <v>46091</v>
@@ -4185,13 +4172,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q47" s="8">
         <v>46091</v>
@@ -4211,7 +4198,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5">
         <v>46091.64445680556</v>
@@ -4223,16 +4210,16 @@
         <v>46114.526705543976</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4248,13 +4235,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Q48" s="5">
         <v>46098</v>
@@ -4274,7 +4261,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B49" s="8">
         <v>46091.6445032176</v>
@@ -4284,16 +4271,16 @@
         <v>46198.82239263889</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4309,13 +4296,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q49" s="8">
         <v>46183</v>
@@ -4335,7 +4322,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46066.48845348379</v>
@@ -4347,7 +4334,7 @@
         <v>46157.63338287037</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4371,7 +4358,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4384,7 +4371,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46066.48845392361</v>
@@ -4396,16 +4383,16 @@
         <v>46157.625757002315</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I51" s="8">
         <v>46087</v>
@@ -4423,13 +4410,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="8">
         <v>46087</v>
@@ -4449,7 +4436,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46066.48845438658</v>
@@ -4461,16 +4448,16 @@
         <v>46157.6332940162</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I52" s="5">
         <v>46092</v>
@@ -4488,13 +4475,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="O52" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="O52" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="P52" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="5">
         <v>46091</v>
@@ -4514,7 +4501,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46066.48845478009</v>
@@ -4526,7 +4513,7 @@
         <v>46209.91546185185</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4550,7 +4537,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4567,7 +4554,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46066.48845520834</v>
@@ -4579,16 +4566,16 @@
         <v>46195.69729675926</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I54" s="5">
         <v>46094</v>
@@ -4606,13 +4593,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46094</v>
@@ -4632,7 +4619,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B55" s="8">
         <v>46066.4884557176</v>
@@ -4644,16 +4631,16 @@
         <v>46211.525319189815</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I55" s="8">
         <v>46105</v>
@@ -4671,13 +4658,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Q55" s="8">
         <v>46105</v>
@@ -4697,7 +4684,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46066.48845053241</v>
@@ -4709,16 +4696,16 @@
         <v>46211.57175387732</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -4736,13 +4723,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Q56" s="5">
         <v>46125</v>
@@ -4762,7 +4749,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B57" s="8">
         <v>46066.488450902776</v>
@@ -4772,7 +4759,7 @@
         <v>46191.7832978125</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4796,7 +4783,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4809,7 +4796,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5">
         <v>46066.48845119213</v>
@@ -4821,16 +4808,16 @@
         <v>46191.783308530095</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I58" s="5">
         <v>46154</v>
@@ -4848,13 +4835,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Q58" s="5">
         <v>46154</v>
@@ -4874,7 +4861,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B59" s="8">
         <v>46066.488451446756</v>
@@ -4886,16 +4873,16 @@
         <v>46127.65513109954</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I59" s="8">
         <v>46091</v>
@@ -4913,13 +4900,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Q59" s="8">
         <v>46091</v>
@@ -4939,7 +4926,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B60" s="5">
         <v>46066.48845172454</v>
@@ -4951,16 +4938,16 @@
         <v>46178.18717369213</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I60" s="5">
         <v>46176</v>
@@ -4978,13 +4965,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q60" s="5">
         <v>46176</v>
@@ -5004,7 +4991,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B61" s="8">
         <v>46066.48845202546</v>
@@ -5020,10 +5007,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I61" s="8">
         <v>46146</v>
@@ -5041,13 +5028,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="8">
         <v>46146</v>
@@ -5062,12 +5049,12 @@
         <v>57</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B62" s="5">
         <v>46066.488452314814</v>
@@ -5077,16 +5064,16 @@
         <v>46192.78934293981</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I62" s="5">
         <v>46156</v>
@@ -5104,13 +5091,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q62" s="5">
         <v>46156</v>
@@ -5130,7 +5117,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B63" s="8">
         <v>46066.48845259259</v>
@@ -5140,7 +5127,7 @@
         <v>46209.79759747685</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5164,7 +5151,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5177,7 +5164,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46066.48845287037</v>
@@ -5187,17 +5174,15 @@
         <v>46212.62747910879</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H64" s="6"/>
       <c r="I64" s="5">
         <v>46127</v>
       </c>
@@ -5214,13 +5199,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="Q64" s="5">
         <v>46125</v>
@@ -5232,15 +5217,15 @@
         <v>0</v>
       </c>
       <c r="T64" s="12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B65" s="8">
         <v>46066.488453136575</v>
@@ -5250,17 +5235,15 @@
         <v>46212.62753224537</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H65" s="9"/>
       <c r="I65" s="8">
         <v>46178</v>
       </c>
@@ -5277,13 +5260,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q65" s="8">
         <v>46178</v>
@@ -5303,7 +5286,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B66" s="5">
         <v>46066.48845087963</v>
@@ -5315,17 +5298,15 @@
         <v>46212.627548449076</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H66" s="6"/>
       <c r="I66" s="5">
         <v>46156</v>
       </c>
@@ -5342,13 +5323,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q66" s="5">
         <v>46156</v>
@@ -5368,7 +5349,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B67" s="8">
         <v>46066.4884515625</v>
@@ -5380,17 +5361,15 @@
         <v>46212.627565393515</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H67" s="9"/>
       <c r="I67" s="8">
         <v>46160</v>
       </c>
@@ -5407,13 +5386,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q67" s="8">
         <v>46160</v>
@@ -5433,7 +5412,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46066.488451909725</v>
@@ -5443,17 +5422,15 @@
         <v>46212.62757856482</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H68" s="6"/>
       <c r="I68" s="5">
         <v>46162</v>
       </c>
@@ -5470,13 +5447,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q68" s="5">
         <v>46162</v>
@@ -5496,7 +5473,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B69" s="8">
         <v>46066.48845236111</v>
@@ -5506,17 +5483,15 @@
         <v>46212.62758842592</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H69" s="9"/>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
         <v>46182</v>
@@ -5531,13 +5506,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="Q69" s="8">
         <v>46182</v>
@@ -5557,7 +5532,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
         <v>46066.488452777776</v>
@@ -5567,17 +5542,15 @@
         <v>46212.627620520834</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H70" s="6"/>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
         <v>46184</v>
@@ -5592,13 +5565,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q70" s="5">
         <v>46184</v>
@@ -5618,7 +5591,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B71" s="8">
         <v>46066.48845318287</v>
@@ -5628,7 +5601,7 @@
         <v>46091.65141318287</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5652,7 +5625,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5665,7 +5638,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
         <v>46066.488453541664</v>
@@ -5675,16 +5648,16 @@
         <v>46212.627884490736</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I72" s="5">
         <v>46185</v>
@@ -5702,13 +5675,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q72" s="5">
         <v>46184</v>
@@ -5728,7 +5701,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B73" s="8">
         <v>46066.48845391204</v>
@@ -5738,17 +5711,15 @@
         <v>46212.62785697917</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H73" s="9"/>
       <c r="I73" s="8">
         <v>46188</v>
       </c>
@@ -5765,13 +5736,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q73" s="8">
         <v>46189</v>
@@ -5791,7 +5762,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
         <v>46066.48845425926</v>
@@ -5801,16 +5772,16 @@
         <v>46212.627920659725</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I74" s="5">
         <v>46191</v>
@@ -5828,13 +5799,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="Q74" s="5">
         <v>46190</v>
@@ -5854,7 +5825,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B75" s="8">
         <v>46066.4884545949</v>
@@ -5864,16 +5835,16 @@
         <v>46212.627943680556</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I75" s="8">
         <v>46192</v>
@@ -5891,13 +5862,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q75" s="8">
         <v>46191</v>
@@ -5917,7 +5888,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B76" s="5">
         <v>46066.488451261575</v>
@@ -5927,7 +5898,7 @@
         <v>46091.6514128125</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5951,7 +5922,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5964,7 +5935,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B77" s="8">
         <v>46066.4884515625</v>
@@ -5974,16 +5945,16 @@
         <v>46203.19655709491</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I77" s="8">
         <v>46195</v>
@@ -6001,13 +5972,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q77" s="8">
         <v>46192</v>
@@ -6027,7 +5998,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B78" s="5">
         <v>46066.48845186342</v>
@@ -6037,16 +6008,16 @@
         <v>46203.19655721065</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I78" s="5">
         <v>46195</v>
@@ -6064,13 +6035,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>272</v>
       </c>
       <c r="Q78" s="5">
         <v>46192</v>
@@ -6090,7 +6061,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B79" s="8">
         <v>46091.64460730324</v>
@@ -6100,7 +6071,7 @@
         <v>46091.65200450231</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6124,7 +6095,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6143,7 +6114,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B80" s="5">
         <v>46091.64498898148</v>
@@ -6153,7 +6124,7 @@
         <v>46204.19897075232</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6180,13 +6151,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="Q80" s="5">
         <v>46195</v>
@@ -6206,7 +6177,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B81" s="8">
         <v>46091.64515803241</v>
@@ -6216,7 +6187,7 @@
         <v>46213.17280854167</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6243,13 +6214,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="O81" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="O81" s="9" t="s">
-        <v>285</v>
-      </c>
       <c r="P81" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q81" s="8">
         <v>46204</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -1975,7 +1975,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46155.16784707176</v>
+        <v>46220.91415710648</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="287">
   <si>
     <t>50001506 - ZCO EPM FRIO AIRE</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
@@ -2601,7 +2604,7 @@
         <v>46122.62955415509</v>
       </c>
       <c r="D22" s="5">
-        <v>46122.62957178241</v>
+        <v>46223.81708695602</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -2610,9 +2613,11 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="I22" s="5">
         <v>46036</v>
       </c>
@@ -2635,7 +2640,7 @@
         <v>66</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>46036</v>
@@ -2655,7 +2660,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" s="8">
         <v>46066.48844994213</v>
@@ -2667,7 +2672,7 @@
         <v>46114.525521250005</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2700,7 +2705,7 @@
         <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="8">
         <v>46036</v>
@@ -2720,7 +2725,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5">
         <v>46066.4884502662</v>
@@ -2729,18 +2734,20 @@
         <v>46157.623377384254</v>
       </c>
       <c r="D24" s="5">
-        <v>46184.581514722224</v>
+        <v>46223.81708303241</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="I24" s="5">
         <v>46036</v>
       </c>
@@ -2763,7 +2770,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="5">
         <v>46036</v>
@@ -2783,7 +2790,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" s="8">
         <v>46066.48845053241</v>
@@ -2795,7 +2802,7 @@
         <v>46184.576358645834</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2819,7 +2826,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2834,7 +2841,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B26" s="5">
         <v>46066.48845078704</v>
@@ -2846,16 +2853,16 @@
         <v>46128.62625043982</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I26" s="5">
         <v>46038</v>
@@ -2873,13 +2880,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="5">
         <v>46038</v>
@@ -2894,12 +2901,12 @@
         <v>57</v>
       </c>
       <c r="U26" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B27" s="8">
         <v>46066.48845104167</v>
@@ -2911,16 +2918,16 @@
         <v>46128.62647177083</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I27" s="8">
         <v>46038</v>
@@ -2938,13 +2945,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2960,7 +2967,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46066.488451296296</v>
@@ -2972,16 +2979,16 @@
         <v>46128.62623707176</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I28" s="5">
         <v>46042</v>
@@ -2999,13 +3006,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3021,7 +3028,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="8">
         <v>46066.48845152778</v>
@@ -3033,16 +3040,16 @@
         <v>46191.90442258102</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I29" s="8">
         <v>46034</v>
@@ -3060,13 +3067,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q29" s="8">
         <v>46034</v>
@@ -3078,7 +3085,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U29" s="11" t="s">
         <v>33</v>
@@ -3086,7 +3093,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46066.488451770834</v>
@@ -3098,16 +3105,16 @@
         <v>46169.847689456015</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I30" s="5">
         <v>46034</v>
@@ -3125,13 +3132,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3147,7 +3154,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46066.48845204861</v>
@@ -3157,16 +3164,16 @@
         <v>46182.67989730324</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I31" s="8">
         <v>46043</v>
@@ -3184,13 +3191,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3206,7 +3213,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46066.48845232639</v>
@@ -3218,16 +3225,16 @@
         <v>46126.86009107639</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I32" s="5">
         <v>46041</v>
@@ -3245,13 +3252,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q32" s="5">
         <v>46038</v>
@@ -3271,7 +3278,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46066.48845209491</v>
@@ -3283,16 +3290,16 @@
         <v>46126.85960659722</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I33" s="8">
         <v>46041</v>
@@ -3310,13 +3317,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>88</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3332,7 +3339,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46066.48845266204</v>
@@ -3344,16 +3351,16 @@
         <v>46126.85966126157</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I34" s="5">
         <v>46042</v>
@@ -3371,13 +3378,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3393,7 +3400,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46066.488452986116</v>
@@ -3405,16 +3412,16 @@
         <v>46176.19802159722</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I35" s="8">
         <v>46031</v>
@@ -3432,13 +3439,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q35" s="8">
         <v>46031</v>
@@ -3458,7 +3465,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46066.488453321756</v>
@@ -3470,16 +3477,16 @@
         <v>46097.54288770833</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I36" s="5">
         <v>46031</v>
@@ -3497,13 +3504,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3519,7 +3526,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46066.48845363426</v>
@@ -3531,16 +3538,16 @@
         <v>46126.807688877314</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I37" s="8">
         <v>46052</v>
@@ -3558,13 +3565,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3580,7 +3587,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46066.48845402778</v>
@@ -3592,16 +3599,16 @@
         <v>46114.52659163195</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I38" s="5">
         <v>46052</v>
@@ -3619,13 +3626,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3641,7 +3648,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46066.488454363425</v>
@@ -3653,16 +3660,16 @@
         <v>46157.62564773148</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I39" s="8">
         <v>46038</v>
@@ -3680,13 +3687,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q39" s="8">
         <v>46038</v>
@@ -3706,7 +3713,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46066.48845471065</v>
@@ -3718,16 +3725,16 @@
         <v>46157.623435497684</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I40" s="5">
         <v>46038</v>
@@ -3745,13 +3752,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3767,7 +3774,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46066.48845502315</v>
@@ -3779,16 +3786,16 @@
         <v>46157.6235046875</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I41" s="8">
         <v>46058</v>
@@ -3806,13 +3813,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3828,7 +3835,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46066.48845533565</v>
@@ -3840,16 +3847,16 @@
         <v>46157.62625247685</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I42" s="5">
         <v>46038</v>
@@ -3867,13 +3874,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q42" s="5">
         <v>46038</v>
@@ -3893,7 +3900,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46066.48845152778</v>
@@ -3905,16 +3912,16 @@
         <v>46154.86717763889</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I43" s="8">
         <v>46038</v>
@@ -3932,13 +3939,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3954,7 +3961,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46066.488452164354</v>
@@ -3966,16 +3973,16 @@
         <v>46154.86724965277</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I44" s="5">
         <v>46078</v>
@@ -3993,13 +4000,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4015,7 +4022,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="8">
         <v>46066.48845261574</v>
@@ -4027,7 +4034,7 @@
         <v>46210.52808679398</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4051,7 +4058,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4068,7 +4075,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46070.75399846065</v>
@@ -4080,16 +4087,16 @@
         <v>46114.52642072916</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I46" s="5">
         <v>46036</v>
@@ -4107,13 +4114,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q46" s="5">
         <v>46036</v>
@@ -4133,7 +4140,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46066.48845297453</v>
@@ -4145,16 +4152,16 @@
         <v>46114.526663310186</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I47" s="8">
         <v>46091</v>
@@ -4172,13 +4179,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q47" s="8">
         <v>46091</v>
@@ -4198,7 +4205,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
         <v>46091.64445680556</v>
@@ -4210,16 +4217,16 @@
         <v>46114.526705543976</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4235,13 +4242,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q48" s="5">
         <v>46098</v>
@@ -4261,7 +4268,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B49" s="8">
         <v>46091.6445032176</v>
@@ -4271,16 +4278,16 @@
         <v>46198.82239263889</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4296,13 +4303,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="8">
         <v>46183</v>
@@ -4322,7 +4329,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46066.48845348379</v>
@@ -4334,7 +4341,7 @@
         <v>46157.63338287037</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4358,7 +4365,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4371,7 +4378,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46066.48845392361</v>
@@ -4383,16 +4390,16 @@
         <v>46157.625757002315</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I51" s="8">
         <v>46087</v>
@@ -4410,13 +4417,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q51" s="8">
         <v>46087</v>
@@ -4436,7 +4443,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46066.48845438658</v>
@@ -4448,16 +4455,16 @@
         <v>46157.6332940162</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I52" s="5">
         <v>46092</v>
@@ -4475,13 +4482,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="5">
         <v>46091</v>
@@ -4501,7 +4508,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46066.48845478009</v>
@@ -4513,7 +4520,7 @@
         <v>46209.91546185185</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4537,7 +4544,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4554,7 +4561,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46066.48845520834</v>
@@ -4566,16 +4573,16 @@
         <v>46195.69729675926</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I54" s="5">
         <v>46094</v>
@@ -4593,13 +4600,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46094</v>
@@ -4619,7 +4626,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B55" s="8">
         <v>46066.4884557176</v>
@@ -4631,16 +4638,16 @@
         <v>46211.525319189815</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I55" s="8">
         <v>46105</v>
@@ -4658,13 +4665,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q55" s="8">
         <v>46105</v>
@@ -4684,7 +4691,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46066.48845053241</v>
@@ -4696,16 +4703,16 @@
         <v>46211.57175387732</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -4723,13 +4730,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46125</v>
@@ -4749,7 +4756,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="8">
         <v>46066.488450902776</v>
@@ -4759,7 +4766,7 @@
         <v>46191.7832978125</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4783,7 +4790,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4796,7 +4803,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46066.48845119213</v>
@@ -4808,16 +4815,16 @@
         <v>46191.783308530095</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I58" s="5">
         <v>46154</v>
@@ -4835,13 +4842,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q58" s="5">
         <v>46154</v>
@@ -4861,7 +4868,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B59" s="8">
         <v>46066.488451446756</v>
@@ -4873,16 +4880,16 @@
         <v>46127.65513109954</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I59" s="8">
         <v>46091</v>
@@ -4900,13 +4907,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q59" s="8">
         <v>46091</v>
@@ -4926,7 +4933,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46066.48845172454</v>
@@ -4938,16 +4945,16 @@
         <v>46178.18717369213</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I60" s="5">
         <v>46176</v>
@@ -4965,13 +4972,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q60" s="5">
         <v>46176</v>
@@ -4991,7 +4998,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="8">
         <v>46066.48845202546</v>
@@ -5007,10 +5014,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I61" s="8">
         <v>46146</v>
@@ -5028,13 +5035,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q61" s="8">
         <v>46146</v>
@@ -5049,12 +5056,12 @@
         <v>57</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46066.488452314814</v>
@@ -5064,16 +5071,16 @@
         <v>46192.78934293981</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I62" s="5">
         <v>46156</v>
@@ -5091,13 +5098,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q62" s="5">
         <v>46156</v>
@@ -5117,7 +5124,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B63" s="8">
         <v>46066.48845259259</v>
@@ -5127,7 +5134,7 @@
         <v>46209.79759747685</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5151,7 +5158,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5164,25 +5171,27 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5">
         <v>46066.48845287037</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46212.62747910879</v>
+        <v>46223.817218703705</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="I64" s="5">
         <v>46127</v>
       </c>
@@ -5199,13 +5208,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q64" s="5">
         <v>46125</v>
@@ -5217,33 +5226,35 @@
         <v>0</v>
       </c>
       <c r="T64" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B65" s="8">
         <v>46066.488453136575</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46212.62753224537</v>
+        <v>46223.817218055556</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="I65" s="8">
         <v>46178</v>
       </c>
@@ -5260,13 +5271,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q65" s="8">
         <v>46178</v>
@@ -5286,7 +5297,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B66" s="5">
         <v>46066.48845087963</v>
@@ -5295,18 +5306,20 @@
         <v>46197.590047060185</v>
       </c>
       <c r="D66" s="5">
-        <v>46212.627548449076</v>
+        <v>46223.81723587963</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H66" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="I66" s="5">
         <v>46156</v>
       </c>
@@ -5323,13 +5336,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q66" s="5">
         <v>46156</v>
@@ -5349,7 +5362,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B67" s="8">
         <v>46066.4884515625</v>
@@ -5358,18 +5371,20 @@
         <v>46209.79758950231</v>
       </c>
       <c r="D67" s="8">
-        <v>46212.627565393515</v>
+        <v>46223.81722695602</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="I67" s="8">
         <v>46160</v>
       </c>
@@ -5386,13 +5401,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q67" s="8">
         <v>46160</v>
@@ -5412,25 +5427,27 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46066.488451909725</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46212.62757856482</v>
+        <v>46223.81721620371</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H68" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="I68" s="5">
         <v>46162</v>
       </c>
@@ -5447,13 +5464,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q68" s="5">
         <v>46162</v>
@@ -5473,25 +5490,27 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B69" s="8">
         <v>46066.48845236111</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46212.62758842592</v>
+        <v>46223.81721555555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H69" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
         <v>46182</v>
@@ -5506,13 +5525,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q69" s="8">
         <v>46182</v>
@@ -5532,25 +5551,27 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B70" s="5">
         <v>46066.488452777776</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46212.627620520834</v>
+        <v>46223.81721487269</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H70" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
         <v>46184</v>
@@ -5565,13 +5586,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q70" s="5">
         <v>46184</v>
@@ -5591,7 +5612,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B71" s="8">
         <v>46066.48845318287</v>
@@ -5601,7 +5622,7 @@
         <v>46091.65141318287</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5625,7 +5646,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5638,7 +5659,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B72" s="5">
         <v>46066.488453541664</v>
@@ -5648,16 +5669,16 @@
         <v>46212.627884490736</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I72" s="5">
         <v>46185</v>
@@ -5675,13 +5696,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q72" s="5">
         <v>46184</v>
@@ -5701,25 +5722,27 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B73" s="8">
         <v>46066.48845391204</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46212.62785697917</v>
+        <v>46223.817302129624</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="9"/>
+        <v>89</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="I73" s="8">
         <v>46188</v>
       </c>
@@ -5736,13 +5759,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q73" s="8">
         <v>46189</v>
@@ -5762,7 +5785,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B74" s="5">
         <v>46066.48845425926</v>
@@ -5772,16 +5795,16 @@
         <v>46212.627920659725</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I74" s="5">
         <v>46191</v>
@@ -5799,13 +5822,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q74" s="5">
         <v>46190</v>
@@ -5825,7 +5848,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B75" s="8">
         <v>46066.4884545949</v>
@@ -5835,16 +5858,16 @@
         <v>46212.627943680556</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I75" s="8">
         <v>46192</v>
@@ -5862,13 +5885,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q75" s="8">
         <v>46191</v>
@@ -5888,7 +5911,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B76" s="5">
         <v>46066.488451261575</v>
@@ -5898,7 +5921,7 @@
         <v>46091.6514128125</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5922,7 +5945,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5935,7 +5958,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B77" s="8">
         <v>46066.4884515625</v>
@@ -5945,16 +5968,16 @@
         <v>46203.19655709491</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I77" s="8">
         <v>46195</v>
@@ -5972,13 +5995,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q77" s="8">
         <v>46192</v>
@@ -5998,7 +6021,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B78" s="5">
         <v>46066.48845186342</v>
@@ -6008,16 +6031,16 @@
         <v>46203.19655721065</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I78" s="5">
         <v>46195</v>
@@ -6035,13 +6058,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q78" s="5">
         <v>46192</v>
@@ -6061,7 +6084,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B79" s="8">
         <v>46091.64460730324</v>
@@ -6071,7 +6094,7 @@
         <v>46091.65200450231</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6095,7 +6118,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6114,7 +6137,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B80" s="5">
         <v>46091.64498898148</v>
@@ -6124,7 +6147,7 @@
         <v>46204.19897075232</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6151,13 +6174,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q80" s="5">
         <v>46195</v>
@@ -6177,7 +6200,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B81" s="8">
         <v>46091.64515803241</v>
@@ -6187,7 +6210,7 @@
         <v>46213.17280854167</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6214,13 +6237,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q81" s="8">
         <v>46204</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="288">
   <si>
     <t>50001506 - ZCO EPM FRIO AIRE</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2616,7 +2619,7 @@
         <v>89</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I22" s="5">
         <v>46036</v>
@@ -2640,7 +2643,7 @@
         <v>66</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>46036</v>
@@ -2660,7 +2663,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8">
         <v>46066.48844994213</v>
@@ -2672,7 +2675,7 @@
         <v>46114.525521250005</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2705,7 +2708,7 @@
         <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="8">
         <v>46036</v>
@@ -2725,7 +2728,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46066.4884502662</v>
@@ -2737,7 +2740,7 @@
         <v>46223.81708303241</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2746,7 +2749,7 @@
         <v>89</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I24" s="5">
         <v>46036</v>
@@ -2770,7 +2773,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="5">
         <v>46036</v>
@@ -2790,7 +2793,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" s="8">
         <v>46066.48845053241</v>
@@ -2802,7 +2805,7 @@
         <v>46184.576358645834</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2826,7 +2829,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2841,7 +2844,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5">
         <v>46066.48845078704</v>
@@ -2853,16 +2856,16 @@
         <v>46128.62625043982</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I26" s="5">
         <v>46038</v>
@@ -2880,13 +2883,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="5">
         <v>46038</v>
@@ -2901,12 +2904,12 @@
         <v>57</v>
       </c>
       <c r="U26" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="8">
         <v>46066.48845104167</v>
@@ -2918,16 +2921,16 @@
         <v>46128.62647177083</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I27" s="8">
         <v>46038</v>
@@ -2945,13 +2948,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2967,7 +2970,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46066.488451296296</v>
@@ -2979,16 +2982,16 @@
         <v>46128.62623707176</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I28" s="5">
         <v>46042</v>
@@ -3006,13 +3009,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3028,7 +3031,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46066.48845152778</v>
@@ -3040,16 +3043,16 @@
         <v>46191.90442258102</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I29" s="8">
         <v>46034</v>
@@ -3067,13 +3070,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q29" s="8">
         <v>46034</v>
@@ -3085,7 +3088,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U29" s="11" t="s">
         <v>33</v>
@@ -3093,7 +3096,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46066.488451770834</v>
@@ -3105,16 +3108,16 @@
         <v>46169.847689456015</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I30" s="5">
         <v>46034</v>
@@ -3132,13 +3135,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3154,7 +3157,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="8">
         <v>46066.48845204861</v>
@@ -3164,16 +3167,16 @@
         <v>46182.67989730324</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I31" s="8">
         <v>46043</v>
@@ -3191,13 +3194,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3213,7 +3216,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46066.48845232639</v>
@@ -3225,16 +3228,16 @@
         <v>46126.86009107639</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I32" s="5">
         <v>46041</v>
@@ -3252,13 +3255,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q32" s="5">
         <v>46038</v>
@@ -3278,7 +3281,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46066.48845209491</v>
@@ -3290,16 +3293,16 @@
         <v>46126.85960659722</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I33" s="8">
         <v>46041</v>
@@ -3317,13 +3320,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>88</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3339,7 +3342,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46066.48845266204</v>
@@ -3351,16 +3354,16 @@
         <v>46126.85966126157</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I34" s="5">
         <v>46042</v>
@@ -3378,13 +3381,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3400,7 +3403,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46066.488452986116</v>
@@ -3412,16 +3415,16 @@
         <v>46176.19802159722</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I35" s="8">
         <v>46031</v>
@@ -3439,13 +3442,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q35" s="8">
         <v>46031</v>
@@ -3465,7 +3468,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46066.488453321756</v>
@@ -3477,16 +3480,16 @@
         <v>46097.54288770833</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I36" s="5">
         <v>46031</v>
@@ -3504,13 +3507,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3526,7 +3529,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46066.48845363426</v>
@@ -3538,16 +3541,16 @@
         <v>46126.807688877314</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I37" s="8">
         <v>46052</v>
@@ -3565,13 +3568,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3587,7 +3590,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46066.48845402778</v>
@@ -3599,16 +3602,16 @@
         <v>46114.52659163195</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I38" s="5">
         <v>46052</v>
@@ -3626,13 +3629,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3648,7 +3651,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46066.488454363425</v>
@@ -3660,16 +3663,16 @@
         <v>46157.62564773148</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I39" s="8">
         <v>46038</v>
@@ -3687,13 +3690,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q39" s="8">
         <v>46038</v>
@@ -3713,7 +3716,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46066.48845471065</v>
@@ -3725,16 +3728,16 @@
         <v>46157.623435497684</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I40" s="5">
         <v>46038</v>
@@ -3752,13 +3755,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3774,7 +3777,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46066.48845502315</v>
@@ -3786,16 +3789,16 @@
         <v>46157.6235046875</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I41" s="8">
         <v>46058</v>
@@ -3813,13 +3816,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3835,7 +3838,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46066.48845533565</v>
@@ -3847,16 +3850,16 @@
         <v>46157.62625247685</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I42" s="5">
         <v>46038</v>
@@ -3874,13 +3877,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q42" s="5">
         <v>46038</v>
@@ -3900,7 +3903,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46066.48845152778</v>
@@ -3912,16 +3915,16 @@
         <v>46154.86717763889</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I43" s="8">
         <v>46038</v>
@@ -3939,13 +3942,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3961,7 +3964,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46066.488452164354</v>
@@ -3973,16 +3976,16 @@
         <v>46154.86724965277</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I44" s="5">
         <v>46078</v>
@@ -4000,13 +4003,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4022,7 +4025,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46066.48845261574</v>
@@ -4034,7 +4037,7 @@
         <v>46210.52808679398</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4058,7 +4061,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4075,7 +4078,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46070.75399846065</v>
@@ -4087,16 +4090,16 @@
         <v>46114.52642072916</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I46" s="5">
         <v>46036</v>
@@ -4114,13 +4117,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q46" s="5">
         <v>46036</v>
@@ -4140,7 +4143,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46066.48845297453</v>
@@ -4152,16 +4155,16 @@
         <v>46114.526663310186</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I47" s="8">
         <v>46091</v>
@@ -4179,13 +4182,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q47" s="8">
         <v>46091</v>
@@ -4205,7 +4208,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46091.64445680556</v>
@@ -4217,16 +4220,16 @@
         <v>46114.526705543976</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4242,13 +4245,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q48" s="5">
         <v>46098</v>
@@ -4268,7 +4271,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B49" s="8">
         <v>46091.6445032176</v>
@@ -4278,16 +4281,16 @@
         <v>46198.82239263889</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4303,13 +4306,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="8">
         <v>46183</v>
@@ -4329,7 +4332,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46066.48845348379</v>
@@ -4341,7 +4344,7 @@
         <v>46157.63338287037</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4365,7 +4368,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4378,7 +4381,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46066.48845392361</v>
@@ -4390,16 +4393,16 @@
         <v>46157.625757002315</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I51" s="8">
         <v>46087</v>
@@ -4417,13 +4420,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="8">
         <v>46087</v>
@@ -4443,7 +4446,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46066.48845438658</v>
@@ -4455,16 +4458,16 @@
         <v>46157.6332940162</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I52" s="5">
         <v>46092</v>
@@ -4482,13 +4485,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="5">
         <v>46091</v>
@@ -4508,7 +4511,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="8">
         <v>46066.48845478009</v>
@@ -4520,7 +4523,7 @@
         <v>46209.91546185185</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4544,7 +4547,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4561,7 +4564,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46066.48845520834</v>
@@ -4573,16 +4576,16 @@
         <v>46195.69729675926</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I54" s="5">
         <v>46094</v>
@@ -4600,13 +4603,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q54" s="5">
         <v>46094</v>
@@ -4626,7 +4629,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B55" s="8">
         <v>46066.4884557176</v>
@@ -4638,16 +4641,16 @@
         <v>46211.525319189815</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I55" s="8">
         <v>46105</v>
@@ -4665,13 +4668,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="8">
         <v>46105</v>
@@ -4691,7 +4694,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46066.48845053241</v>
@@ -4703,16 +4706,16 @@
         <v>46211.57175387732</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -4730,13 +4733,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="5">
         <v>46125</v>
@@ -4756,7 +4759,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B57" s="8">
         <v>46066.488450902776</v>
@@ -4766,7 +4769,7 @@
         <v>46191.7832978125</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4790,7 +4793,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4803,7 +4806,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46066.48845119213</v>
@@ -4815,16 +4818,16 @@
         <v>46191.783308530095</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I58" s="5">
         <v>46154</v>
@@ -4842,13 +4845,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q58" s="5">
         <v>46154</v>
@@ -4868,7 +4871,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="8">
         <v>46066.488451446756</v>
@@ -4880,16 +4883,16 @@
         <v>46127.65513109954</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I59" s="8">
         <v>46091</v>
@@ -4907,13 +4910,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q59" s="8">
         <v>46091</v>
@@ -4933,7 +4936,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46066.48845172454</v>
@@ -4945,16 +4948,16 @@
         <v>46178.18717369213</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I60" s="5">
         <v>46176</v>
@@ -4972,13 +4975,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q60" s="5">
         <v>46176</v>
@@ -4998,7 +5001,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B61" s="8">
         <v>46066.48845202546</v>
@@ -5014,10 +5017,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I61" s="8">
         <v>46146</v>
@@ -5035,13 +5038,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q61" s="8">
         <v>46146</v>
@@ -5056,12 +5059,12 @@
         <v>57</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46066.488452314814</v>
@@ -5071,16 +5074,16 @@
         <v>46192.78934293981</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I62" s="5">
         <v>46156</v>
@@ -5098,13 +5101,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q62" s="5">
         <v>46156</v>
@@ -5124,7 +5127,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B63" s="8">
         <v>46066.48845259259</v>
@@ -5134,7 +5137,7 @@
         <v>46209.79759747685</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5158,7 +5161,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5171,7 +5174,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5">
         <v>46066.48845287037</v>
@@ -5181,7 +5184,7 @@
         <v>46223.817218703705</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5190,7 +5193,7 @@
         <v>89</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I64" s="5">
         <v>46127</v>
@@ -5208,13 +5211,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="5">
         <v>46125</v>
@@ -5226,15 +5229,15 @@
         <v>0</v>
       </c>
       <c r="T64" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B65" s="8">
         <v>46066.488453136575</v>
@@ -5244,7 +5247,7 @@
         <v>46223.817218055556</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5253,7 +5256,7 @@
         <v>89</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I65" s="8">
         <v>46178</v>
@@ -5271,13 +5274,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q65" s="8">
         <v>46178</v>
@@ -5297,7 +5300,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B66" s="5">
         <v>46066.48845087963</v>
@@ -5309,7 +5312,7 @@
         <v>46223.81723587963</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5318,7 +5321,7 @@
         <v>89</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I66" s="5">
         <v>46156</v>
@@ -5336,13 +5339,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="5">
         <v>46156</v>
@@ -5362,7 +5365,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B67" s="8">
         <v>46066.4884515625</v>
@@ -5374,7 +5377,7 @@
         <v>46223.81722695602</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5383,7 +5386,7 @@
         <v>89</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I67" s="8">
         <v>46160</v>
@@ -5401,13 +5404,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q67" s="8">
         <v>46160</v>
@@ -5427,7 +5430,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B68" s="5">
         <v>46066.488451909725</v>
@@ -5437,7 +5440,7 @@
         <v>46223.81721620371</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5446,7 +5449,7 @@
         <v>89</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I68" s="5">
         <v>46162</v>
@@ -5464,13 +5467,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q68" s="5">
         <v>46162</v>
@@ -5490,7 +5493,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B69" s="8">
         <v>46066.48845236111</v>
@@ -5500,7 +5503,7 @@
         <v>46223.81721555555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5509,7 +5512,7 @@
         <v>89</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5525,13 +5528,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q69" s="8">
         <v>46182</v>
@@ -5551,7 +5554,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B70" s="5">
         <v>46066.488452777776</v>
@@ -5561,7 +5564,7 @@
         <v>46223.81721487269</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5570,7 +5573,7 @@
         <v>89</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5586,13 +5589,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q70" s="5">
         <v>46184</v>
@@ -5612,7 +5615,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B71" s="8">
         <v>46066.48845318287</v>
@@ -5622,7 +5625,7 @@
         <v>46091.65141318287</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5646,7 +5649,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5659,7 +5662,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B72" s="5">
         <v>46066.488453541664</v>
@@ -5669,16 +5672,16 @@
         <v>46212.627884490736</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I72" s="5">
         <v>46185</v>
@@ -5696,13 +5699,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q72" s="5">
         <v>46184</v>
@@ -5722,7 +5725,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B73" s="8">
         <v>46066.48845391204</v>
@@ -5732,7 +5735,7 @@
         <v>46223.817302129624</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5741,7 +5744,7 @@
         <v>89</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I73" s="8">
         <v>46188</v>
@@ -5759,13 +5762,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q73" s="8">
         <v>46189</v>
@@ -5785,7 +5788,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B74" s="5">
         <v>46066.48845425926</v>
@@ -5795,16 +5798,16 @@
         <v>46212.627920659725</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I74" s="5">
         <v>46191</v>
@@ -5822,13 +5825,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q74" s="5">
         <v>46190</v>
@@ -5848,7 +5851,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B75" s="8">
         <v>46066.4884545949</v>
@@ -5858,16 +5861,16 @@
         <v>46212.627943680556</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I75" s="8">
         <v>46192</v>
@@ -5885,13 +5888,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q75" s="8">
         <v>46191</v>
@@ -5911,7 +5914,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B76" s="5">
         <v>46066.488451261575</v>
@@ -5921,7 +5924,7 @@
         <v>46091.6514128125</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5945,7 +5948,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5958,7 +5961,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B77" s="8">
         <v>46066.4884515625</v>
@@ -5968,16 +5971,16 @@
         <v>46203.19655709491</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I77" s="8">
         <v>46195</v>
@@ -5995,13 +5998,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q77" s="8">
         <v>46192</v>
@@ -6021,7 +6024,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B78" s="5">
         <v>46066.48845186342</v>
@@ -6031,16 +6034,16 @@
         <v>46203.19655721065</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I78" s="5">
         <v>46195</v>
@@ -6058,13 +6061,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="5">
         <v>46192</v>
@@ -6084,7 +6087,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B79" s="8">
         <v>46091.64460730324</v>
@@ -6094,7 +6097,7 @@
         <v>46091.65200450231</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6118,7 +6121,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6137,7 +6140,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B80" s="5">
         <v>46091.64498898148</v>
@@ -6147,7 +6150,7 @@
         <v>46204.19897075232</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6174,13 +6177,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q80" s="5">
         <v>46195</v>
@@ -6200,7 +6203,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B81" s="8">
         <v>46091.64515803241</v>
@@ -6210,7 +6213,7 @@
         <v>46213.17280854167</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6237,13 +6240,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q81" s="8">
         <v>46204</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="290">
   <si>
     <t>50001506 - ZCO EPM FRIO AIRE</t>
   </si>
@@ -599,6 +599,12 @@
   </si>
   <si>
     <t xml:space="preserve">Bodega:,Generación OC </t>
+  </si>
+  <si>
+    <t>1216916071174880</t>
+  </si>
+  <si>
+    <t>|</t>
   </si>
   <si>
     <t>1213263334883449</t>
@@ -1398,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U81"/>
+  <dimension ref="A1:U82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -3225,7 +3231,7 @@
         <v>46126.86007825231</v>
       </c>
       <c r="D32" s="5">
-        <v>46126.86009107639</v>
+        <v>46228.46784878473</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -4278,7 +4284,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46198.82239263889</v>
+        <v>46230.548913391205</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4341,7 +4347,7 @@
         <v>46157.6332930787</v>
       </c>
       <c r="D50" s="5">
-        <v>46157.63338287037</v>
+        <v>46230.56959944444</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4514,19 +4520,17 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46066.48845478009</v>
-      </c>
-      <c r="C53" s="8">
-        <v>46209.915449293985</v>
-      </c>
+        <v>46230.56959699074</v>
+      </c>
+      <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46209.91546185185</v>
+        <v>46230.56965446759</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>26</v>
@@ -4541,146 +4545,130 @@
         <v>26</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>26</v>
+        <v>184</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>198</v>
+        <v>26</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
-      <c r="S53" s="9">
-        <v>1</v>
-      </c>
+      <c r="S53" s="9"/>
       <c r="T53" s="9"/>
-      <c r="U53" s="11" t="s">
-        <v>33</v>
-      </c>
+      <c r="U53" s="9"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B54" s="5">
+        <v>46066.48845478009</v>
+      </c>
+      <c r="C54" s="5">
+        <v>46209.915449293985</v>
+      </c>
+      <c r="D54" s="5">
+        <v>46209.91546185185</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="B54" s="5">
-        <v>46066.48845520834</v>
-      </c>
-      <c r="C54" s="5">
-        <v>46195.69727907407</v>
-      </c>
-      <c r="D54" s="5">
-        <v>46195.69729675926</v>
-      </c>
-      <c r="E54" s="6" t="s">
+      <c r="F54" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O54" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="I54" s="5">
-        <v>46094</v>
-      </c>
-      <c r="J54" s="5">
-        <v>46104</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N54" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="O54" s="6" t="s">
-        <v>192</v>
-      </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q54" s="5">
-        <v>46094</v>
-      </c>
-      <c r="R54" s="5">
-        <v>46104</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q54" s="6"/>
+      <c r="R54" s="6"/>
       <c r="S54" s="6">
         <v>1</v>
       </c>
-      <c r="T54" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="T54" s="6"/>
       <c r="U54" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B55" s="8">
+        <v>46066.48845520834</v>
+      </c>
+      <c r="C55" s="8">
+        <v>46195.69727907407</v>
+      </c>
+      <c r="D55" s="8">
+        <v>46195.69729675926</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B55" s="8">
-        <v>46066.4884557176</v>
-      </c>
-      <c r="C55" s="8">
-        <v>46204.594040208336</v>
-      </c>
-      <c r="D55" s="8">
-        <v>46211.525319189815</v>
-      </c>
-      <c r="E55" s="9" t="s">
+      <c r="I55" s="8">
+        <v>46094</v>
+      </c>
+      <c r="J55" s="8">
+        <v>46104</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="O55" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="I55" s="8">
-        <v>46105</v>
-      </c>
-      <c r="J55" s="8">
-        <v>46122</v>
-      </c>
-      <c r="K55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="O55" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>207</v>
-      </c>
       <c r="Q55" s="8">
-        <v>46105</v>
+        <v>46094</v>
       </c>
       <c r="R55" s="8">
-        <v>46122</v>
+        <v>46104</v>
       </c>
       <c r="S55" s="9">
         <v>1</v>
@@ -4694,58 +4682,58 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B56" s="5">
+        <v>46066.4884557176</v>
+      </c>
+      <c r="C56" s="5">
+        <v>46204.594040208336</v>
+      </c>
+      <c r="D56" s="5">
+        <v>46211.525319189815</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="I56" s="5">
+        <v>46105</v>
+      </c>
+      <c r="J56" s="5">
+        <v>46122</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="O56" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B56" s="5">
-        <v>46066.48845053241</v>
-      </c>
-      <c r="C56" s="5">
-        <v>46209.9154271875</v>
-      </c>
-      <c r="D56" s="5">
-        <v>46211.57175387732</v>
-      </c>
-      <c r="E56" s="6" t="s">
+      <c r="P56" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="I56" s="5">
-        <v>46125</v>
-      </c>
-      <c r="J56" s="5">
-        <v>46126</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N56" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="O56" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>211</v>
-      </c>
       <c r="Q56" s="5">
-        <v>46125</v>
+        <v>46105</v>
       </c>
       <c r="R56" s="5">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="S56" s="6">
         <v>1</v>
@@ -4759,131 +4747,131 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B57" s="8">
+        <v>46066.48845053241</v>
+      </c>
+      <c r="C57" s="8">
+        <v>46209.9154271875</v>
+      </c>
+      <c r="D57" s="8">
+        <v>46211.57175387732</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="I57" s="8">
+        <v>46125</v>
+      </c>
+      <c r="J57" s="8">
+        <v>46126</v>
+      </c>
+      <c r="K57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="O57" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B57" s="8">
-        <v>46066.488450902776</v>
-      </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="8">
-        <v>46191.7832978125</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
-      <c r="K57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O57" s="9" t="s">
+      <c r="P57" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="P57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q57" s="9"/>
-      <c r="R57" s="9"/>
-      <c r="S57" s="9"/>
-      <c r="T57" s="9"/>
-      <c r="U57" s="9"/>
+      <c r="Q57" s="8">
+        <v>46125</v>
+      </c>
+      <c r="R57" s="8">
+        <v>46126</v>
+      </c>
+      <c r="S57" s="9">
+        <v>1</v>
+      </c>
+      <c r="T57" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U57" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46066.48845119213</v>
-      </c>
-      <c r="C58" s="5">
-        <v>46191.78328978009</v>
-      </c>
+        <v>46066.488450902776</v>
+      </c>
+      <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46191.783308530095</v>
+        <v>46191.7832978125</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O58" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="I58" s="5">
-        <v>46154</v>
-      </c>
-      <c r="J58" s="5">
-        <v>46155</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N58" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="O58" s="6" t="s">
-        <v>111</v>
-      </c>
       <c r="P58" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q58" s="5">
-        <v>46154</v>
-      </c>
-      <c r="R58" s="5">
-        <v>46155</v>
-      </c>
-      <c r="S58" s="6">
-        <v>1</v>
-      </c>
-      <c r="T58" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="U58" s="11" t="s">
-        <v>33</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q58" s="6"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="6"/>
+      <c r="T58" s="6"/>
+      <c r="U58" s="6"/>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B59" s="8">
+        <v>46066.48845119213</v>
+      </c>
+      <c r="C59" s="8">
+        <v>46191.78328978009</v>
+      </c>
+      <c r="D59" s="8">
+        <v>46191.783308530095</v>
+      </c>
+      <c r="E59" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="B59" s="8">
-        <v>46066.488451446756</v>
-      </c>
-      <c r="C59" s="8">
-        <v>46127.655113113426</v>
-      </c>
-      <c r="D59" s="8">
-        <v>46127.65513109954</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>218</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -4895,10 +4883,10 @@
         <v>189</v>
       </c>
       <c r="I59" s="8">
-        <v>46091</v>
+        <v>46154</v>
       </c>
       <c r="J59" s="8">
-        <v>46092</v>
+        <v>46155</v>
       </c>
       <c r="K59" s="9" t="s">
         <v>26</v>
@@ -4913,22 +4901,22 @@
         <v>184</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q59" s="8">
-        <v>46091</v>
+        <v>46154</v>
       </c>
       <c r="R59" s="8">
-        <v>46092</v>
+        <v>46155</v>
       </c>
       <c r="S59" s="9">
         <v>1</v>
       </c>
-      <c r="T59" s="10" t="s">
-        <v>32</v>
+      <c r="T59" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="U59" s="11" t="s">
         <v>33</v>
@@ -4936,19 +4924,19 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B60" s="5">
+        <v>46066.488451446756</v>
+      </c>
+      <c r="C60" s="5">
+        <v>46127.655113113426</v>
+      </c>
+      <c r="D60" s="5">
+        <v>46127.65513109954</v>
+      </c>
+      <c r="E60" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="B60" s="5">
-        <v>46066.48845172454</v>
-      </c>
-      <c r="C60" s="5">
-        <v>46127.655216354164</v>
-      </c>
-      <c r="D60" s="5">
-        <v>46178.18717369213</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4960,10 +4948,10 @@
         <v>189</v>
       </c>
       <c r="I60" s="5">
-        <v>46176</v>
+        <v>46091</v>
       </c>
       <c r="J60" s="5">
-        <v>46177</v>
+        <v>46092</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>26</v>
@@ -4978,16 +4966,16 @@
         <v>184</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q60" s="5">
-        <v>46176</v>
+        <v>46091</v>
       </c>
       <c r="R60" s="5">
-        <v>46177</v>
+        <v>46092</v>
       </c>
       <c r="S60" s="6">
         <v>1</v>
@@ -5001,17 +4989,19 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B61" s="8">
+        <v>46066.48845172454</v>
+      </c>
+      <c r="C61" s="8">
+        <v>46127.655216354164</v>
+      </c>
+      <c r="D61" s="8">
+        <v>46178.18717369213</v>
+      </c>
+      <c r="E61" s="9" t="s">
         <v>223</v>
-      </c>
-      <c r="B61" s="8">
-        <v>46066.48845202546</v>
-      </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="8">
-        <v>46182.67990290509</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>55</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -5023,10 +5013,10 @@
         <v>189</v>
       </c>
       <c r="I61" s="8">
-        <v>46146</v>
+        <v>46176</v>
       </c>
       <c r="J61" s="8">
-        <v>46147</v>
+        <v>46177</v>
       </c>
       <c r="K61" s="9" t="s">
         <v>26</v>
@@ -5041,25 +5031,25 @@
         <v>184</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>224</v>
       </c>
       <c r="Q61" s="8">
-        <v>46146</v>
+        <v>46176</v>
       </c>
       <c r="R61" s="8">
-        <v>46147</v>
+        <v>46177</v>
       </c>
       <c r="S61" s="9">
-        <v>0</v>
-      </c>
-      <c r="T61" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="U61" s="12" t="s">
-        <v>106</v>
+        <v>1</v>
+      </c>
+      <c r="T61" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U61" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5067,14 +5057,14 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46066.488452314814</v>
+        <v>46066.48845202546</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46192.78934293981</v>
+        <v>46182.67990290509</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>55</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5086,10 +5076,10 @@
         <v>189</v>
       </c>
       <c r="I62" s="5">
-        <v>46156</v>
+        <v>46146</v>
       </c>
       <c r="J62" s="5">
-        <v>46157</v>
+        <v>46147</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>26</v>
@@ -5104,150 +5094,150 @@
         <v>184</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q62" s="5">
-        <v>46156</v>
+        <v>46146</v>
       </c>
       <c r="R62" s="5">
-        <v>46157</v>
+        <v>46147</v>
       </c>
       <c r="S62" s="6">
         <v>0</v>
       </c>
-      <c r="T62" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U62" s="10" t="s">
-        <v>58</v>
+      <c r="T62" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="U62" s="12" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46066.48845259259</v>
+        <v>46066.488452314814</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46209.79759747685</v>
+        <v>46192.78934293981</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="I63" s="8">
+        <v>46156</v>
+      </c>
+      <c r="J63" s="8">
+        <v>46157</v>
+      </c>
+      <c r="K63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="O63" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H63" s="9"/>
-      <c r="I63" s="9"/>
-      <c r="J63" s="9"/>
-      <c r="K63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M63" s="9" t="s">
+      <c r="Q63" s="8">
+        <v>46156</v>
+      </c>
+      <c r="R63" s="8">
+        <v>46157</v>
+      </c>
+      <c r="S63" s="9">
         <v>0</v>
       </c>
-      <c r="N63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O63" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q63" s="9"/>
-      <c r="R63" s="9"/>
-      <c r="S63" s="9"/>
-      <c r="T63" s="9"/>
-      <c r="U63" s="9"/>
+      <c r="T63" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U63" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5">
-        <v>46066.48845287037</v>
+        <v>46066.48845259259</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46223.817218703705</v>
+        <v>46209.79759747685</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O64" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="I64" s="5">
-        <v>46127</v>
-      </c>
-      <c r="J64" s="5">
-        <v>46146</v>
-      </c>
-      <c r="K64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N64" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>209</v>
-      </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q64" s="5">
-        <v>46125</v>
-      </c>
-      <c r="R64" s="5">
-        <v>46142</v>
-      </c>
-      <c r="S64" s="6">
-        <v>0</v>
-      </c>
-      <c r="T64" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="U64" s="12" t="s">
-        <v>106</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6"/>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46066.488453136575</v>
+        <v>46066.48845287037</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46223.817218055556</v>
+        <v>46223.817218703705</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5259,10 +5249,10 @@
         <v>90</v>
       </c>
       <c r="I65" s="8">
-        <v>46178</v>
+        <v>46127</v>
       </c>
       <c r="J65" s="8">
-        <v>46181</v>
+        <v>46146</v>
       </c>
       <c r="K65" s="9" t="s">
         <v>26</v>
@@ -5274,45 +5264,43 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="Q65" s="8">
-        <v>46178</v>
+        <v>46125</v>
       </c>
       <c r="R65" s="8">
-        <v>46181</v>
+        <v>46142</v>
       </c>
       <c r="S65" s="9">
         <v>0</v>
       </c>
-      <c r="T65" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U65" s="10" t="s">
-        <v>58</v>
+      <c r="T65" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="U65" s="12" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46066.48845087963</v>
-      </c>
-      <c r="C66" s="5">
-        <v>46197.590047060185</v>
-      </c>
+        <v>46066.488453136575</v>
+      </c>
+      <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46223.81723587963</v>
+        <v>46223.817218055556</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5324,10 +5312,10 @@
         <v>90</v>
       </c>
       <c r="I66" s="5">
-        <v>46156</v>
+        <v>46178</v>
       </c>
       <c r="J66" s="5">
-        <v>46157</v>
+        <v>46181</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>26</v>
@@ -5339,45 +5327,45 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q66" s="5">
-        <v>46156</v>
+        <v>46178</v>
       </c>
       <c r="R66" s="5">
-        <v>46157</v>
+        <v>46181</v>
       </c>
       <c r="S66" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T66" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U66" s="11" t="s">
-        <v>33</v>
+      <c r="U66" s="10" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B67" s="8">
+        <v>46066.48845087963</v>
+      </c>
+      <c r="C67" s="8">
+        <v>46197.590047060185</v>
+      </c>
+      <c r="D67" s="8">
+        <v>46223.81723587963</v>
+      </c>
+      <c r="E67" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="B67" s="8">
-        <v>46066.4884515625</v>
-      </c>
-      <c r="C67" s="8">
-        <v>46209.79758950231</v>
-      </c>
-      <c r="D67" s="8">
-        <v>46223.81722695602</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5389,10 +5377,10 @@
         <v>90</v>
       </c>
       <c r="I67" s="8">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="J67" s="8">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="K67" s="9" t="s">
         <v>26</v>
@@ -5404,19 +5392,19 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q67" s="8">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="R67" s="8">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="S67" s="9">
         <v>1</v>
@@ -5430,17 +5418,19 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B68" s="5">
+        <v>46066.4884515625</v>
+      </c>
+      <c r="C68" s="5">
+        <v>46209.79758950231</v>
+      </c>
+      <c r="D68" s="5">
+        <v>46223.81722695602</v>
+      </c>
+      <c r="E68" s="6" t="s">
         <v>244</v>
-      </c>
-      <c r="B68" s="5">
-        <v>46066.488451909725</v>
-      </c>
-      <c r="C68" s="6"/>
-      <c r="D68" s="5">
-        <v>46223.81721620371</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>245</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5452,10 +5442,10 @@
         <v>90</v>
       </c>
       <c r="I68" s="5">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="J68" s="5">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>26</v>
@@ -5467,43 +5457,43 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q68" s="5">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="R68" s="5">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="S68" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U68" s="10" t="s">
-        <v>58</v>
+      <c r="U68" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46066.48845236111</v>
+        <v>46066.488451909725</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46223.81721555555</v>
+        <v>46223.81721620371</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5514,9 +5504,11 @@
       <c r="H69" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="I69" s="9"/>
+      <c r="I69" s="8">
+        <v>46162</v>
+      </c>
       <c r="J69" s="8">
-        <v>46182</v>
+        <v>46164</v>
       </c>
       <c r="K69" s="9" t="s">
         <v>26</v>
@@ -5528,19 +5520,19 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>248</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="Q69" s="8">
-        <v>46182</v>
+        <v>46162</v>
       </c>
       <c r="R69" s="8">
-        <v>46182</v>
+        <v>46164</v>
       </c>
       <c r="S69" s="9">
         <v>0</v>
@@ -5557,14 +5549,14 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46066.488452777776</v>
+        <v>46066.48845236111</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46223.81721487269</v>
+        <v>46223.81721555555</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5577,7 +5569,7 @@
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>26</v>
@@ -5589,19 +5581,19 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="P70" s="6" t="s">
-        <v>250</v>
-      </c>
       <c r="Q70" s="5">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="R70" s="5">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="S70" s="6">
         <v>0</v>
@@ -5618,163 +5610,161 @@
         <v>251</v>
       </c>
       <c r="B71" s="8">
-        <v>46066.48845318287</v>
+        <v>46066.488452777776</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.65141318287</v>
+        <v>46223.81721487269</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I71" s="9"/>
+      <c r="J71" s="8">
+        <v>46184</v>
+      </c>
+      <c r="K71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="O71" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H71" s="9"/>
-      <c r="I71" s="9"/>
-      <c r="J71" s="9"/>
-      <c r="K71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M71" s="9" t="s">
+      <c r="Q71" s="8">
+        <v>46184</v>
+      </c>
+      <c r="R71" s="8">
+        <v>46184</v>
+      </c>
+      <c r="S71" s="9">
         <v>0</v>
       </c>
-      <c r="N71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O71" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q71" s="9"/>
-      <c r="R71" s="9"/>
-      <c r="S71" s="9"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
+      <c r="T71" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U71" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B72" s="5">
-        <v>46066.488453541664</v>
+        <v>46066.48845318287</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46212.627884490736</v>
+        <v>46091.65141318287</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O72" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="H72" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="I72" s="5">
-        <v>46185</v>
-      </c>
-      <c r="J72" s="5">
-        <v>46185</v>
-      </c>
-      <c r="K72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N72" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="O72" s="6" t="s">
-        <v>182</v>
-      </c>
       <c r="P72" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q72" s="5">
-        <v>46184</v>
-      </c>
-      <c r="R72" s="5">
-        <v>46184</v>
-      </c>
-      <c r="S72" s="6">
-        <v>0</v>
-      </c>
-      <c r="T72" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U72" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="6"/>
+      <c r="T72" s="6"/>
+      <c r="U72" s="6"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B73" s="8">
-        <v>46066.48845391204</v>
+        <v>46066.488453541664</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46223.817302129624</v>
+        <v>46212.627884490736</v>
       </c>
       <c r="E73" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="I73" s="8">
+        <v>46185</v>
+      </c>
+      <c r="J73" s="8">
+        <v>46185</v>
+      </c>
+      <c r="K73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="O73" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="F73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="I73" s="8">
-        <v>46188</v>
-      </c>
-      <c r="J73" s="8">
-        <v>46190</v>
-      </c>
-      <c r="K73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N73" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="O73" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="Q73" s="8">
-        <v>46189</v>
+        <v>46184</v>
       </c>
       <c r="R73" s="8">
-        <v>46189</v>
+        <v>46184</v>
       </c>
       <c r="S73" s="9">
         <v>0</v>
@@ -5788,56 +5778,56 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
-        <v>46066.48845425926</v>
+        <v>46066.48845391204</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46212.627920659725</v>
+        <v>46223.817302129624</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I74" s="5">
+        <v>46188</v>
+      </c>
+      <c r="J74" s="5">
+        <v>46190</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="I74" s="5">
-        <v>46191</v>
-      </c>
-      <c r="J74" s="5">
-        <v>46191</v>
-      </c>
-      <c r="K74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N74" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>266</v>
-      </c>
       <c r="Q74" s="5">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="R74" s="5">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="S74" s="6">
         <v>0</v>
@@ -5851,56 +5841,56 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B75" s="8">
-        <v>46066.4884545949</v>
+        <v>46066.48845425926</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46212.627943680556</v>
+        <v>46212.627920659725</v>
       </c>
       <c r="E75" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="I75" s="8">
+        <v>46191</v>
+      </c>
+      <c r="J75" s="8">
+        <v>46191</v>
+      </c>
+      <c r="K75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="O75" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="P75" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="I75" s="8">
-        <v>46192</v>
-      </c>
-      <c r="J75" s="8">
-        <v>46192</v>
-      </c>
-      <c r="K75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N75" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="O75" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>269</v>
-      </c>
       <c r="Q75" s="8">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="R75" s="8">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="S75" s="9">
         <v>0</v>
@@ -5914,136 +5904,136 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46066.488451261575</v>
+        <v>46066.4884545949</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46091.6514128125</v>
+        <v>46212.627943680556</v>
       </c>
       <c r="E76" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="I76" s="5">
+        <v>46192</v>
+      </c>
+      <c r="J76" s="5">
+        <v>46192</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="F76" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M76" s="6" t="s">
+      <c r="Q76" s="5">
+        <v>46191</v>
+      </c>
+      <c r="R76" s="5">
+        <v>46191</v>
+      </c>
+      <c r="S76" s="6">
         <v>0</v>
       </c>
-      <c r="N76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O76" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
+      <c r="T76" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U76" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B77" s="8">
-        <v>46066.4884515625</v>
+        <v>46066.488451261575</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46203.19655709491</v>
+        <v>46091.6514128125</v>
       </c>
       <c r="E77" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O77" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="I77" s="8">
-        <v>46195</v>
-      </c>
-      <c r="J77" s="8">
-        <v>46203</v>
-      </c>
-      <c r="K77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N77" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="O77" s="9" t="s">
-        <v>277</v>
-      </c>
       <c r="P77" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q77" s="8">
-        <v>46192</v>
-      </c>
-      <c r="R77" s="8">
-        <v>46202</v>
-      </c>
-      <c r="S77" s="9">
-        <v>0</v>
-      </c>
-      <c r="T77" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U77" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q77" s="9"/>
+      <c r="R77" s="9"/>
+      <c r="S77" s="9"/>
+      <c r="T77" s="9"/>
+      <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B78" s="5">
-        <v>46066.48845186342</v>
+        <v>46066.4884515625</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46203.19655721065</v>
+        <v>46203.19655709491</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I78" s="5">
         <v>46195</v>
@@ -6061,13 +6051,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q78" s="5">
         <v>46192</v>
@@ -6090,24 +6080,30 @@
         <v>280</v>
       </c>
       <c r="B79" s="8">
-        <v>46091.64460730324</v>
+        <v>46066.48845186342</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46091.65200450231</v>
+        <v>46203.19655721065</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>281</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="9"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
+        <v>277</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="I79" s="8">
+        <v>46195</v>
+      </c>
+      <c r="J79" s="8">
+        <v>46203</v>
+      </c>
       <c r="K79" s="9" t="s">
         <v>26</v>
       </c>
@@ -6115,24 +6111,28 @@
         <v>26</v>
       </c>
       <c r="M79" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>26</v>
+        <v>273</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q79" s="9"/>
-      <c r="R79" s="9"/>
+        <v>273</v>
+      </c>
+      <c r="Q79" s="8">
+        <v>46192</v>
+      </c>
+      <c r="R79" s="8">
+        <v>46202</v>
+      </c>
       <c r="S79" s="9">
         <v>0</v>
       </c>
-      <c r="T79" s="11" t="s">
-        <v>57</v>
+      <c r="T79" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="U79" s="10" t="s">
         <v>58</v>
@@ -6140,62 +6140,52 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.64498898148</v>
+        <v>46091.64460730324</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46204.19897075232</v>
+        <v>46091.65200450231</v>
       </c>
       <c r="E80" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O80" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="F80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I80" s="5">
-        <v>46195</v>
-      </c>
-      <c r="J80" s="5">
-        <v>46203</v>
-      </c>
-      <c r="K80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>268</v>
-      </c>
       <c r="P80" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>46195</v>
-      </c>
-      <c r="R80" s="5">
-        <v>46203</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
       <c r="S80" s="6">
         <v>0</v>
       </c>
-      <c r="T80" s="10" t="s">
-        <v>32</v>
+      <c r="T80" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="U80" s="10" t="s">
         <v>58</v>
@@ -6203,17 +6193,17 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.64515803241</v>
+        <v>46091.64498898148</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46213.17280854167</v>
+        <v>46204.19897075232</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6225,10 +6215,10 @@
         <v>51</v>
       </c>
       <c r="I81" s="8">
-        <v>46204</v>
+        <v>46195</v>
       </c>
       <c r="J81" s="8">
-        <v>46212</v>
+        <v>46203</v>
       </c>
       <c r="K81" s="9" t="s">
         <v>26</v>
@@ -6240,19 +6230,19 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="Q81" s="8">
-        <v>46204</v>
+        <v>46195</v>
       </c>
       <c r="R81" s="8">
-        <v>46212</v>
+        <v>46203</v>
       </c>
       <c r="S81" s="9">
         <v>0</v>
@@ -6261,6 +6251,69 @@
         <v>32</v>
       </c>
       <c r="U81" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B82" s="5">
+        <v>46091.64515803241</v>
+      </c>
+      <c r="C82" s="6"/>
+      <c r="D82" s="5">
+        <v>46213.17280854167</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I82" s="5">
+        <v>46204</v>
+      </c>
+      <c r="J82" s="5">
+        <v>46212</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q82" s="5">
+        <v>46204</v>
+      </c>
+      <c r="R82" s="5">
+        <v>46212</v>
+      </c>
+      <c r="S82" s="6">
+        <v>0</v>
+      </c>
+      <c r="T82" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U82" s="10" t="s">
         <v>58</v>
       </c>
     </row>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="288">
   <si>
     <t>50001506 - ZCO EPM FRIO AIRE</t>
   </si>
@@ -599,12 +599,6 @@
   </si>
   <si>
     <t xml:space="preserve">Bodega:,Generación OC </t>
-  </si>
-  <si>
-    <t>1216916071174880</t>
-  </si>
-  <si>
-    <t>|</t>
   </si>
   <si>
     <t>1213263334883449</t>
@@ -1404,7 +1398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U82"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -4520,17 +4514,19 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46230.56959699074</v>
-      </c>
-      <c r="C53" s="9"/>
+        <v>46066.48845478009</v>
+      </c>
+      <c r="C53" s="8">
+        <v>46209.915449293985</v>
+      </c>
       <c r="D53" s="8">
-        <v>46230.56965446759</v>
+        <v>46209.91546185185</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>26</v>
@@ -4545,48 +4541,58 @@
         <v>26</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>184</v>
+        <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>26</v>
+        <v>198</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
-      <c r="S53" s="9"/>
+      <c r="S53" s="9">
+        <v>1</v>
+      </c>
       <c r="T53" s="9"/>
-      <c r="U53" s="9"/>
+      <c r="U53" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46066.48845478009</v>
+        <v>46066.48845520834</v>
       </c>
       <c r="C54" s="5">
-        <v>46209.915449293985</v>
+        <v>46195.69727907407</v>
       </c>
       <c r="D54" s="5">
-        <v>46209.91546185185</v>
+        <v>46195.69729675926</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
+        <v>201</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="I54" s="5">
+        <v>46094</v>
+      </c>
+      <c r="J54" s="5">
+        <v>46104</v>
+      </c>
       <c r="K54" s="6" t="s">
         <v>26</v>
       </c>
@@ -4594,57 +4600,63 @@
         <v>26</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
+        <v>203</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>46094</v>
+      </c>
+      <c r="R54" s="5">
+        <v>46104</v>
+      </c>
       <c r="S54" s="6">
         <v>1</v>
       </c>
-      <c r="T54" s="6"/>
+      <c r="T54" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="U54" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B55" s="8">
+        <v>46066.4884557176</v>
+      </c>
+      <c r="C55" s="8">
+        <v>46204.594040208336</v>
+      </c>
+      <c r="D55" s="8">
+        <v>46211.525319189815</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B55" s="8">
-        <v>46066.48845520834</v>
-      </c>
-      <c r="C55" s="8">
-        <v>46195.69727907407</v>
-      </c>
-      <c r="D55" s="8">
-        <v>46195.69729675926</v>
-      </c>
-      <c r="E55" s="9" t="s">
+      <c r="H55" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>204</v>
-      </c>
       <c r="I55" s="8">
-        <v>46094</v>
+        <v>46105</v>
       </c>
       <c r="J55" s="8">
-        <v>46104</v>
+        <v>46122</v>
       </c>
       <c r="K55" s="9" t="s">
         <v>26</v>
@@ -4656,19 +4668,19 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="8">
-        <v>46094</v>
+        <v>46105</v>
       </c>
       <c r="R55" s="8">
-        <v>46104</v>
+        <v>46122</v>
       </c>
       <c r="S55" s="9">
         <v>1</v>
@@ -4682,34 +4694,34 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46066.4884557176</v>
+        <v>46066.48845053241</v>
       </c>
       <c r="C56" s="5">
-        <v>46204.594040208336</v>
+        <v>46209.9154271875</v>
       </c>
       <c r="D56" s="5">
-        <v>46211.525319189815</v>
+        <v>46211.57175387732</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="I56" s="5">
-        <v>46105</v>
+        <v>46125</v>
       </c>
       <c r="J56" s="5">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>26</v>
@@ -4721,19 +4733,19 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="5">
-        <v>46105</v>
+        <v>46125</v>
       </c>
       <c r="R56" s="5">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="S56" s="6">
         <v>1</v>
@@ -4747,35 +4759,27 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B57" s="8">
-        <v>46066.48845053241</v>
-      </c>
-      <c r="C57" s="8">
-        <v>46209.9154271875</v>
-      </c>
+        <v>46066.488450902776</v>
+      </c>
+      <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46211.57175387732</v>
+        <v>46191.7832978125</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="I57" s="8">
-        <v>46125</v>
-      </c>
-      <c r="J57" s="8">
-        <v>46126</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
       <c r="K57" s="9" t="s">
         <v>26</v>
       </c>
@@ -4783,95 +4787,103 @@
         <v>26</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>199</v>
+        <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q57" s="8">
-        <v>46125</v>
-      </c>
-      <c r="R57" s="8">
-        <v>46126</v>
-      </c>
-      <c r="S57" s="9">
-        <v>1</v>
-      </c>
-      <c r="T57" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U57" s="11" t="s">
-        <v>33</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q57" s="9"/>
+      <c r="R57" s="9"/>
+      <c r="S57" s="9"/>
+      <c r="T57" s="9"/>
+      <c r="U57" s="9"/>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46066.488450902776</v>
-      </c>
-      <c r="C58" s="6"/>
+        <v>46066.48845119213</v>
+      </c>
+      <c r="C58" s="5">
+        <v>46191.78328978009</v>
+      </c>
       <c r="D58" s="5">
-        <v>46191.7832978125</v>
+        <v>46191.783308530095</v>
       </c>
       <c r="E58" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="I58" s="5">
+        <v>46154</v>
+      </c>
+      <c r="J58" s="5">
+        <v>46155</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N58" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M58" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N58" s="6" t="s">
-        <v>26</v>
-      </c>
       <c r="O58" s="6" t="s">
-        <v>215</v>
+        <v>111</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="6"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
+        <v>216</v>
+      </c>
+      <c r="Q58" s="5">
+        <v>46154</v>
+      </c>
+      <c r="R58" s="5">
+        <v>46155</v>
+      </c>
+      <c r="S58" s="6">
+        <v>1</v>
+      </c>
+      <c r="T58" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="U58" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46066.48845119213</v>
+        <v>46066.488451446756</v>
       </c>
       <c r="C59" s="8">
-        <v>46191.78328978009</v>
+        <v>46127.655113113426</v>
       </c>
       <c r="D59" s="8">
-        <v>46191.783308530095</v>
+        <v>46127.65513109954</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -4883,10 +4895,10 @@
         <v>189</v>
       </c>
       <c r="I59" s="8">
-        <v>46154</v>
+        <v>46091</v>
       </c>
       <c r="J59" s="8">
-        <v>46155</v>
+        <v>46092</v>
       </c>
       <c r="K59" s="9" t="s">
         <v>26</v>
@@ -4901,22 +4913,22 @@
         <v>184</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q59" s="8">
-        <v>46154</v>
+        <v>46091</v>
       </c>
       <c r="R59" s="8">
-        <v>46155</v>
+        <v>46092</v>
       </c>
       <c r="S59" s="9">
         <v>1</v>
       </c>
-      <c r="T59" s="11" t="s">
-        <v>57</v>
+      <c r="T59" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="U59" s="11" t="s">
         <v>33</v>
@@ -4924,19 +4936,19 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46066.488451446756</v>
+        <v>46066.48845172454</v>
       </c>
       <c r="C60" s="5">
-        <v>46127.655113113426</v>
+        <v>46127.655216354164</v>
       </c>
       <c r="D60" s="5">
-        <v>46127.65513109954</v>
+        <v>46178.18717369213</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4948,10 +4960,10 @@
         <v>189</v>
       </c>
       <c r="I60" s="5">
-        <v>46091</v>
+        <v>46176</v>
       </c>
       <c r="J60" s="5">
-        <v>46092</v>
+        <v>46177</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>26</v>
@@ -4966,16 +4978,16 @@
         <v>184</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q60" s="5">
-        <v>46091</v>
+        <v>46176</v>
       </c>
       <c r="R60" s="5">
-        <v>46092</v>
+        <v>46177</v>
       </c>
       <c r="S60" s="6">
         <v>1</v>
@@ -4989,19 +5001,17 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46066.48845172454</v>
-      </c>
-      <c r="C61" s="8">
-        <v>46127.655216354164</v>
-      </c>
+        <v>46066.48845202546</v>
+      </c>
+      <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46178.18717369213</v>
+        <v>46182.67990290509</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>223</v>
+        <v>55</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -5013,10 +5023,10 @@
         <v>189</v>
       </c>
       <c r="I61" s="8">
-        <v>46176</v>
+        <v>46146</v>
       </c>
       <c r="J61" s="8">
-        <v>46177</v>
+        <v>46147</v>
       </c>
       <c r="K61" s="9" t="s">
         <v>26</v>
@@ -5031,25 +5041,25 @@
         <v>184</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>224</v>
       </c>
       <c r="Q61" s="8">
-        <v>46176</v>
+        <v>46146</v>
       </c>
       <c r="R61" s="8">
-        <v>46177</v>
+        <v>46147</v>
       </c>
       <c r="S61" s="9">
-        <v>1</v>
-      </c>
-      <c r="T61" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U61" s="11" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="T61" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="U61" s="12" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5057,14 +5067,14 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46066.48845202546</v>
+        <v>46066.488452314814</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46182.67990290509</v>
+        <v>46192.78934293981</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>55</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5076,10 +5086,10 @@
         <v>189</v>
       </c>
       <c r="I62" s="5">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="J62" s="5">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>26</v>
@@ -5094,56 +5104,50 @@
         <v>184</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q62" s="5">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="R62" s="5">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="S62" s="6">
         <v>0</v>
       </c>
-      <c r="T62" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="U62" s="12" t="s">
-        <v>106</v>
+      <c r="T62" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U62" s="10" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46066.488452314814</v>
+        <v>46066.48845259259</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46192.78934293981</v>
+        <v>46209.79759747685</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="I63" s="8">
-        <v>46156</v>
-      </c>
-      <c r="J63" s="8">
-        <v>46157</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9"/>
       <c r="K63" s="9" t="s">
         <v>26</v>
       </c>
@@ -5151,56 +5155,52 @@
         <v>26</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>184</v>
+        <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q63" s="8">
-        <v>46156</v>
-      </c>
-      <c r="R63" s="8">
-        <v>46157</v>
-      </c>
-      <c r="S63" s="9">
-        <v>0</v>
-      </c>
-      <c r="T63" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U63" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q63" s="9"/>
+      <c r="R63" s="9"/>
+      <c r="S63" s="9"/>
+      <c r="T63" s="9"/>
+      <c r="U63" s="9"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46066.48845259259</v>
+        <v>46066.48845287037</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46209.79759747685</v>
+        <v>46223.817218703705</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I64" s="5">
+        <v>46127</v>
+      </c>
+      <c r="J64" s="5">
+        <v>46146</v>
+      </c>
       <c r="K64" s="6" t="s">
         <v>26</v>
       </c>
@@ -5208,36 +5208,46 @@
         <v>26</v>
       </c>
       <c r="M64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>46125</v>
+      </c>
+      <c r="R64" s="5">
+        <v>46142</v>
+      </c>
+      <c r="S64" s="6">
         <v>0</v>
       </c>
-      <c r="N64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
+      <c r="T64" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="U64" s="12" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B65" s="8">
-        <v>46066.48845287037</v>
+        <v>46066.488453136575</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46223.817218703705</v>
+        <v>46223.817218055556</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5249,10 +5259,10 @@
         <v>90</v>
       </c>
       <c r="I65" s="8">
-        <v>46127</v>
+        <v>46178</v>
       </c>
       <c r="J65" s="8">
-        <v>46146</v>
+        <v>46181</v>
       </c>
       <c r="K65" s="9" t="s">
         <v>26</v>
@@ -5264,43 +5274,45 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q65" s="8">
-        <v>46125</v>
+        <v>46178</v>
       </c>
       <c r="R65" s="8">
-        <v>46142</v>
+        <v>46181</v>
       </c>
       <c r="S65" s="9">
         <v>0</v>
       </c>
-      <c r="T65" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="U65" s="12" t="s">
-        <v>106</v>
+      <c r="T65" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U65" s="10" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B66" s="5">
-        <v>46066.488453136575</v>
-      </c>
-      <c r="C66" s="6"/>
+        <v>46066.48845087963</v>
+      </c>
+      <c r="C66" s="5">
+        <v>46197.590047060185</v>
+      </c>
       <c r="D66" s="5">
-        <v>46223.817218055556</v>
+        <v>46223.81723587963</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5312,10 +5324,10 @@
         <v>90</v>
       </c>
       <c r="I66" s="5">
-        <v>46178</v>
+        <v>46156</v>
       </c>
       <c r="J66" s="5">
-        <v>46181</v>
+        <v>46157</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>26</v>
@@ -5327,45 +5339,45 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="5">
-        <v>46178</v>
+        <v>46156</v>
       </c>
       <c r="R66" s="5">
-        <v>46181</v>
+        <v>46157</v>
       </c>
       <c r="S66" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U66" s="10" t="s">
-        <v>58</v>
+      <c r="U66" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46066.48845087963</v>
+        <v>46066.4884515625</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.590047060185</v>
+        <v>46209.79758950231</v>
       </c>
       <c r="D67" s="8">
-        <v>46223.81723587963</v>
+        <v>46223.81722695602</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5377,10 +5389,10 @@
         <v>90</v>
       </c>
       <c r="I67" s="8">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="J67" s="8">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="K67" s="9" t="s">
         <v>26</v>
@@ -5392,19 +5404,19 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q67" s="8">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="R67" s="8">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="S67" s="9">
         <v>1</v>
@@ -5418,19 +5430,17 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B68" s="5">
-        <v>46066.4884515625</v>
-      </c>
-      <c r="C68" s="5">
-        <v>46209.79758950231</v>
-      </c>
+        <v>46066.488451909725</v>
+      </c>
+      <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46223.81722695602</v>
+        <v>46223.81721620371</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5442,10 +5452,10 @@
         <v>90</v>
       </c>
       <c r="I68" s="5">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="J68" s="5">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>26</v>
@@ -5457,43 +5467,43 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q68" s="5">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="R68" s="5">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="S68" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T68" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U68" s="11" t="s">
-        <v>33</v>
+      <c r="U68" s="10" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46066.488451909725</v>
+        <v>46066.48845236111</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46223.81721620371</v>
+        <v>46223.81721555555</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5504,11 +5514,9 @@
       <c r="H69" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="I69" s="8">
-        <v>46162</v>
-      </c>
+      <c r="I69" s="9"/>
       <c r="J69" s="8">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="K69" s="9" t="s">
         <v>26</v>
@@ -5520,19 +5528,19 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>248</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>239</v>
+        <v>178</v>
       </c>
       <c r="Q69" s="8">
-        <v>46162</v>
+        <v>46182</v>
       </c>
       <c r="R69" s="8">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="S69" s="9">
         <v>0</v>
@@ -5549,14 +5557,14 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46066.48845236111</v>
+        <v>46066.488452777776</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46223.81721555555</v>
+        <v>46223.81721487269</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5569,7 +5577,7 @@
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>26</v>
@@ -5581,19 +5589,19 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="P70" s="6" t="s">
-        <v>178</v>
-      </c>
       <c r="Q70" s="5">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="R70" s="5">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="S70" s="6">
         <v>0</v>
@@ -5610,28 +5618,24 @@
         <v>251</v>
       </c>
       <c r="B71" s="8">
-        <v>46066.488452777776</v>
+        <v>46066.48845318287</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46223.81721487269</v>
+        <v>46091.65141318287</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>182</v>
+        <v>252</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H71" s="9"/>
       <c r="I71" s="9"/>
-      <c r="J71" s="8">
-        <v>46184</v>
-      </c>
+      <c r="J71" s="9"/>
       <c r="K71" s="9" t="s">
         <v>26</v>
       </c>
@@ -5639,56 +5643,52 @@
         <v>26</v>
       </c>
       <c r="M71" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>231</v>
+        <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>178</v>
+        <v>253</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q71" s="8">
-        <v>46184</v>
-      </c>
-      <c r="R71" s="8">
-        <v>46184</v>
-      </c>
-      <c r="S71" s="9">
-        <v>0</v>
-      </c>
-      <c r="T71" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U71" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q71" s="9"/>
+      <c r="R71" s="9"/>
+      <c r="S71" s="9"/>
+      <c r="T71" s="9"/>
+      <c r="U71" s="9"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B72" s="5">
-        <v>46066.48845318287</v>
+        <v>46066.488453541664</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46091.65141318287</v>
+        <v>46212.627884490736</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
+        <v>255</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I72" s="5">
+        <v>46185</v>
+      </c>
+      <c r="J72" s="5">
+        <v>46185</v>
+      </c>
       <c r="K72" s="6" t="s">
         <v>26</v>
       </c>
@@ -5696,75 +5696,85 @@
         <v>26</v>
       </c>
       <c r="M72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="O72" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q72" s="5">
+        <v>46184</v>
+      </c>
+      <c r="R72" s="5">
+        <v>46184</v>
+      </c>
+      <c r="S72" s="6">
         <v>0</v>
       </c>
-      <c r="N72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O72" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-      <c r="T72" s="6"/>
-      <c r="U72" s="6"/>
+      <c r="T72" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U72" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B73" s="8">
-        <v>46066.488453541664</v>
+        <v>46066.48845391204</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46212.627884490736</v>
+        <v>46223.817302129624</v>
       </c>
       <c r="E73" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I73" s="8">
+        <v>46188</v>
+      </c>
+      <c r="J73" s="8">
+        <v>46190</v>
+      </c>
+      <c r="K73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="F73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="I73" s="8">
-        <v>46185</v>
-      </c>
-      <c r="J73" s="8">
-        <v>46185</v>
-      </c>
-      <c r="K73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N73" s="9" t="s">
-        <v>254</v>
-      </c>
       <c r="O73" s="9" t="s">
-        <v>182</v>
+        <v>260</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q73" s="8">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="R73" s="8">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="S73" s="9">
         <v>0</v>
@@ -5778,56 +5788,56 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B74" s="5">
-        <v>46066.48845391204</v>
+        <v>46066.48845425926</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46223.817302129624</v>
+        <v>46212.627920659725</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>89</v>
+        <v>264</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>90</v>
+        <v>265</v>
       </c>
       <c r="I74" s="5">
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="J74" s="5">
+        <v>46191</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="P74" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q74" s="5">
         <v>46190</v>
       </c>
-      <c r="K74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N74" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>46189</v>
-      </c>
       <c r="R74" s="5">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="S74" s="6">
         <v>0</v>
@@ -5841,56 +5851,56 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46066.48845425926</v>
+        <v>46066.4884545949</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46212.627920659725</v>
+        <v>46212.627943680556</v>
       </c>
       <c r="E75" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="F75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>267</v>
-      </c>
       <c r="I75" s="8">
+        <v>46192</v>
+      </c>
+      <c r="J75" s="8">
+        <v>46192</v>
+      </c>
+      <c r="K75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="O75" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="P75" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q75" s="8">
         <v>46191</v>
       </c>
-      <c r="J75" s="8">
+      <c r="R75" s="8">
         <v>46191</v>
-      </c>
-      <c r="K75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N75" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="O75" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q75" s="8">
-        <v>46190</v>
-      </c>
-      <c r="R75" s="8">
-        <v>46190</v>
       </c>
       <c r="S75" s="9">
         <v>0</v>
@@ -5904,33 +5914,27 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B76" s="5">
-        <v>46066.4884545949</v>
+        <v>46066.488451261575</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46212.627943680556</v>
+        <v>46091.6514128125</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="I76" s="5">
-        <v>46192</v>
-      </c>
-      <c r="J76" s="5">
-        <v>46192</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="6"/>
       <c r="K76" s="6" t="s">
         <v>26</v>
       </c>
@@ -5938,56 +5942,52 @@
         <v>26</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>254</v>
+        <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q76" s="5">
-        <v>46191</v>
-      </c>
-      <c r="R76" s="5">
-        <v>46191</v>
-      </c>
-      <c r="S76" s="6">
-        <v>0</v>
-      </c>
-      <c r="T76" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U76" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6"/>
+      <c r="T76" s="6"/>
+      <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B77" s="8">
-        <v>46066.488451261575</v>
+        <v>46066.4884515625</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46091.6514128125</v>
+        <v>46203.19655709491</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H77" s="9"/>
-      <c r="I77" s="9"/>
-      <c r="J77" s="9"/>
+        <v>275</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="I77" s="8">
+        <v>46195</v>
+      </c>
+      <c r="J77" s="8">
+        <v>46203</v>
+      </c>
       <c r="K77" s="9" t="s">
         <v>26</v>
       </c>
@@ -5995,45 +5995,55 @@
         <v>26</v>
       </c>
       <c r="M77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="O77" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="P77" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q77" s="8">
+        <v>46192</v>
+      </c>
+      <c r="R77" s="8">
+        <v>46202</v>
+      </c>
+      <c r="S77" s="9">
         <v>0</v>
       </c>
-      <c r="N77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O77" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="P77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q77" s="9"/>
-      <c r="R77" s="9"/>
-      <c r="S77" s="9"/>
-      <c r="T77" s="9"/>
-      <c r="U77" s="9"/>
+      <c r="T77" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U77" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B78" s="5">
-        <v>46066.4884515625</v>
+        <v>46066.48845186342</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46203.19655709491</v>
+        <v>46203.19655721065</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I78" s="5">
         <v>46195</v>
@@ -6051,13 +6061,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="5">
         <v>46192</v>
@@ -6080,30 +6090,24 @@
         <v>280</v>
       </c>
       <c r="B79" s="8">
-        <v>46066.48845186342</v>
+        <v>46091.64460730324</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46203.19655721065</v>
+        <v>46091.65200450231</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>281</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="I79" s="8">
-        <v>46195</v>
-      </c>
-      <c r="J79" s="8">
-        <v>46203</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H79" s="9"/>
+      <c r="I79" s="9"/>
+      <c r="J79" s="9"/>
       <c r="K79" s="9" t="s">
         <v>26</v>
       </c>
@@ -6111,28 +6115,24 @@
         <v>26</v>
       </c>
       <c r="M79" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>273</v>
+        <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q79" s="8">
-        <v>46192</v>
-      </c>
-      <c r="R79" s="8">
-        <v>46202</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q79" s="9"/>
+      <c r="R79" s="9"/>
       <c r="S79" s="9">
         <v>0</v>
       </c>
-      <c r="T79" s="10" t="s">
-        <v>32</v>
+      <c r="T79" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="U79" s="10" t="s">
         <v>58</v>
@@ -6140,27 +6140,33 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B80" s="5">
-        <v>46091.64460730324</v>
+        <v>46091.64498898148</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46091.65200450231</v>
+        <v>46204.19897075232</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
+        <v>50</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I80" s="5">
+        <v>46195</v>
+      </c>
+      <c r="J80" s="5">
+        <v>46203</v>
+      </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
       </c>
@@ -6168,24 +6174,28 @@
         <v>26</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>26</v>
+        <v>281</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
+        <v>285</v>
+      </c>
+      <c r="Q80" s="5">
+        <v>46195</v>
+      </c>
+      <c r="R80" s="5">
+        <v>46203</v>
+      </c>
       <c r="S80" s="6">
         <v>0</v>
       </c>
-      <c r="T80" s="11" t="s">
-        <v>57</v>
+      <c r="T80" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="U80" s="10" t="s">
         <v>58</v>
@@ -6193,17 +6203,17 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B81" s="8">
-        <v>46091.64498898148</v>
+        <v>46091.64515803241</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46204.19897075232</v>
+        <v>46213.17280854167</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6215,10 +6225,10 @@
         <v>51</v>
       </c>
       <c r="I81" s="8">
-        <v>46195</v>
+        <v>46204</v>
       </c>
       <c r="J81" s="8">
-        <v>46203</v>
+        <v>46212</v>
       </c>
       <c r="K81" s="9" t="s">
         <v>26</v>
@@ -6230,19 +6240,19 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="Q81" s="8">
-        <v>46195</v>
+        <v>46204</v>
       </c>
       <c r="R81" s="8">
-        <v>46203</v>
+        <v>46212</v>
       </c>
       <c r="S81" s="9">
         <v>0</v>
@@ -6251,69 +6261,6 @@
         <v>32</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B82" s="5">
-        <v>46091.64515803241</v>
-      </c>
-      <c r="C82" s="6"/>
-      <c r="D82" s="5">
-        <v>46213.17280854167</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I82" s="5">
-        <v>46204</v>
-      </c>
-      <c r="J82" s="5">
-        <v>46212</v>
-      </c>
-      <c r="K82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N82" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q82" s="5">
-        <v>46204</v>
-      </c>
-      <c r="R82" s="5">
-        <v>46212</v>
-      </c>
-      <c r="S82" s="6">
-        <v>0</v>
-      </c>
-      <c r="T82" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U82" s="10" t="s">
         <v>58</v>
       </c>
     </row>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="288">
   <si>
     <t>50001506 - ZCO EPM FRIO AIRE</t>
   </si>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46230.548913391205</v>
+        <v>46231.561291562495</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4326,8 +4326,8 @@
       <c r="T49" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U49" s="10" t="s">
-        <v>58</v>
+      <c r="U49" s="12" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46191.7832978125</v>
+        <v>46230.9102021875</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -5069,9 +5069,11 @@
       <c r="B62" s="5">
         <v>46066.488452314814</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46230.910195868055</v>
+      </c>
       <c r="D62" s="5">
-        <v>46192.78934293981</v>
+        <v>46230.91021270833</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5116,13 +5118,13 @@
         <v>46157</v>
       </c>
       <c r="S62" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U62" s="10" t="s">
-        <v>58</v>
+      <c r="U62" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5134,7 +5136,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46209.79759747685</v>
+        <v>46230.91026372685</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>229</v>
@@ -5170,7 +5172,9 @@
       <c r="R63" s="9"/>
       <c r="S63" s="9"/>
       <c r="T63" s="9"/>
-      <c r="U63" s="9"/>
+      <c r="U63" s="12" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
@@ -5179,9 +5183,11 @@
       <c r="B64" s="5">
         <v>46066.48845287037</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46230.910102615744</v>
+      </c>
       <c r="D64" s="5">
-        <v>46223.817218703705</v>
+        <v>46230.91012436342</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>232</v>
@@ -5226,13 +5232,13 @@
         <v>46142</v>
       </c>
       <c r="S64" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="U64" s="12" t="s">
-        <v>106</v>
+      <c r="U64" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5242,9 +5248,11 @@
       <c r="B65" s="8">
         <v>46066.488453136575</v>
       </c>
-      <c r="C65" s="9"/>
+      <c r="C65" s="8">
+        <v>46230.910141203705</v>
+      </c>
       <c r="D65" s="8">
-        <v>46223.817218055556</v>
+        <v>46230.91015710648</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>235</v>
@@ -5289,13 +5297,13 @@
         <v>46181</v>
       </c>
       <c r="S65" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U65" s="10" t="s">
-        <v>58</v>
+      <c r="U65" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5309,7 +5317,7 @@
         <v>46197.590047060185</v>
       </c>
       <c r="D66" s="5">
-        <v>46223.81723587963</v>
+        <v>46230.91012434028</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>239</v>
@@ -5359,8 +5367,8 @@
       <c r="T66" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U66" s="11" t="s">
-        <v>33</v>
+      <c r="U66" s="12" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5374,7 +5382,7 @@
         <v>46209.79758950231</v>
       </c>
       <c r="D67" s="8">
-        <v>46223.81722695602</v>
+        <v>46230.91012446759</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5424,8 +5432,8 @@
       <c r="T67" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U67" s="11" t="s">
-        <v>33</v>
+      <c r="U67" s="12" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5435,9 +5443,11 @@
       <c r="B68" s="5">
         <v>46066.488451909725</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46230.91024295139</v>
+      </c>
       <c r="D68" s="5">
-        <v>46223.81721620371</v>
+        <v>46230.910257662035</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>245</v>
@@ -5482,13 +5492,13 @@
         <v>46164</v>
       </c>
       <c r="S68" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U68" s="10" t="s">
-        <v>58</v>
+      <c r="U68" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5498,9 +5508,11 @@
       <c r="B69" s="8">
         <v>46066.48845236111</v>
       </c>
-      <c r="C69" s="9"/>
+      <c r="C69" s="8">
+        <v>46230.910278923606</v>
+      </c>
       <c r="D69" s="8">
-        <v>46223.81721555555</v>
+        <v>46230.91029408565</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5543,13 +5555,13 @@
         <v>46182</v>
       </c>
       <c r="S69" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U69" s="10" t="s">
-        <v>58</v>
+      <c r="U69" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -4278,7 +4278,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46231.561291562495</v>
+        <v>46231.917933993056</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="290">
   <si>
     <t>50001506 - ZCO EPM FRIO AIRE</t>
   </si>
@@ -178,169 +178,175 @@
     <t>Revision tableros pruebas</t>
   </si>
   <si>
+    <t>sergio saavedra fernandez</t>
+  </si>
+  <si>
+    <t>sergio.saavedra@zitron.com</t>
+  </si>
+  <si>
     <t>Recepcion Tableros</t>
   </si>
   <si>
     <t>ot 4221- 4222-4223 - Embalaje,Ingenieria de servicio:</t>
   </si>
   <si>
+    <t>1213263333570155</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete,Analisis de costeo</t>
+  </si>
+  <si>
+    <t>1213263333570156</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>propuesta motor,Ingenieria Jefe de proyecto:,Analisis de costeo</t>
+  </si>
+  <si>
+    <t>1213263333570158</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete,Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta  alabes</t>
+  </si>
+  <si>
+    <t>1213263333570159</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Propuesta sensores y accesorios,propuesta compras a codigo // aprovisionamiento,Ingenieria Jefe de proyecto:,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1213263333570160</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
+    <t>1213263333570161</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta motor,propuesta  alabes,propuesta tableros,propuesta nucleo rodete,Propuesta sensores y accesorios,propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>1213263333570162</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor</t>
+  </si>
+  <si>
+    <t>1213263333570163</t>
+  </si>
+  <si>
+    <t>propuesta  alabes</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>1213263333570164</t>
+  </si>
+  <si>
+    <t>propuesta tableros</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Tableros ot 4222 -ot 4223</t>
+  </si>
+  <si>
+    <t>1213263333570165</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete</t>
+  </si>
+  <si>
+    <t>1213263333570166</t>
+  </si>
+  <si>
+    <t>Propuesta sensores y accesorios</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Sensores y accesorios</t>
+  </si>
+  <si>
+    <t>1213263333570167</t>
+  </si>
+  <si>
+    <t>propuesta compras a codigo // aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales</t>
+  </si>
+  <si>
+    <t>1213263333570168</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Alabe,Tableros ot 4222 -ot 4223,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento,Sensores y accesorios</t>
+  </si>
+  <si>
+    <t>1213263333570169</t>
+  </si>
+  <si>
+    <t>Alabe</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe,Fabricación Alabe</t>
+  </si>
+  <si>
     <t>Baja</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1213263333570170</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe,Alabe</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1213263333570155</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213263333570156</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>propuesta motor,Ingenieria Jefe de proyecto:,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213263333570158</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete,Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta  alabes</t>
-  </si>
-  <si>
-    <t>1213263333570159</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Propuesta sensores y accesorios,propuesta compras a codigo // aprovisionamiento,Ingenieria Jefe de proyecto:,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1213263333570160</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>1213263333570161</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta motor,propuesta  alabes,propuesta tableros,propuesta nucleo rodete,Propuesta sensores y accesorios,propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>1213263333570162</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor</t>
-  </si>
-  <si>
-    <t>1213263333570163</t>
-  </si>
-  <si>
-    <t>propuesta  alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>1213263333570164</t>
-  </si>
-  <si>
-    <t>propuesta tableros</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Tableros ot 4222 -ot 4223</t>
-  </si>
-  <si>
-    <t>1213263333570165</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete</t>
-  </si>
-  <si>
-    <t>NATALYA ESPINOZA</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete</t>
-  </si>
-  <si>
-    <t>1213263333570166</t>
-  </si>
-  <si>
-    <t>Propuesta sensores y accesorios</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Sensores y accesorios</t>
-  </si>
-  <si>
-    <t>1213263333570167</t>
-  </si>
-  <si>
-    <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales</t>
-  </si>
-  <si>
-    <t>1213263333570168</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Alabe,Tableros ot 4222 -ot 4223,rodete,Motor,Materiales a codigo // compras locales aprovisionamientomiento,Sensores y accesorios</t>
-  </si>
-  <si>
-    <t>1213263333570169</t>
-  </si>
-  <si>
-    <t>Alabe</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe,Fabricación Alabe</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213263333570170</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe,Alabe</t>
   </si>
   <si>
     <t>1213263333570171</t>
@@ -1867,9 +1873,11 @@
       <c r="B10" s="5">
         <v>46066.48845106481</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46233.52146950232</v>
+      </c>
       <c r="D10" s="5">
-        <v>46097.54322979167</v>
+        <v>46233.52148277778</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1903,9 +1911,13 @@
       </c>
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
+      <c r="S10" s="6">
+        <v>1</v>
+      </c>
       <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="U10" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
@@ -1979,9 +1991,11 @@
       <c r="B12" s="5">
         <v>46066.48845153935</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46233.52145454861</v>
+      </c>
       <c r="D12" s="5">
-        <v>46220.91415710648</v>
+        <v>46233.521690381946</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1990,10 +2004,10 @@
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="I12" s="5">
         <v>46149</v>
@@ -2014,10 +2028,10 @@
         <v>46</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q12" s="5">
         <v>46149</v>
@@ -2026,13 +2040,13 @@
         <v>46155</v>
       </c>
       <c r="S12" s="6">
-        <v>0</v>
-      </c>
-      <c r="T12" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="U12" s="10" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="T12" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -2046,7 +2060,7 @@
         <v>46114.52534087963</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.525368125</v>
+        <v>46233.52170266204</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2901,15 +2915,15 @@
         <v>1</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U26" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8">
         <v>46066.48845104167</v>
@@ -2921,7 +2935,7 @@
         <v>46128.62647177083</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -2954,7 +2968,7 @@
         <v>82</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2962,15 +2976,15 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46066.488451296296</v>
@@ -2982,7 +2996,7 @@
         <v>46128.62623707176</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3012,10 +3026,10 @@
         <v>102</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3023,15 +3037,15 @@
         <v>0</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B29" s="8">
         <v>46066.48845152778</v>
@@ -3043,7 +3057,7 @@
         <v>46191.90442258102</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3073,7 +3087,7 @@
         <v>99</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>99</v>
@@ -3088,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="U29" s="11" t="s">
         <v>33</v>
@@ -3096,7 +3110,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46066.488451770834</v>
@@ -3108,7 +3122,7 @@
         <v>46169.847689456015</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3135,13 +3149,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3149,15 +3163,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B31" s="8">
         <v>46066.48845204861</v>
@@ -3167,7 +3181,7 @@
         <v>46182.67989730324</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3194,13 +3208,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3208,15 +3222,15 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46066.48845232639</v>
@@ -3228,7 +3242,7 @@
         <v>46228.46784878473</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3258,7 +3272,7 @@
         <v>99</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>99</v>
@@ -3281,7 +3295,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B33" s="8">
         <v>46066.48845209491</v>
@@ -3293,7 +3307,7 @@
         <v>46126.85960659722</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3320,13 +3334,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>88</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3334,15 +3348,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46066.48845266204</v>
@@ -3354,7 +3368,7 @@
         <v>46126.85966126157</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3381,13 +3395,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3395,15 +3409,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B35" s="8">
         <v>46066.488452986116</v>
@@ -3415,7 +3429,7 @@
         <v>46176.19802159722</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3445,7 +3459,7 @@
         <v>99</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>99</v>
@@ -3468,7 +3482,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46066.488453321756</v>
@@ -3480,7 +3494,7 @@
         <v>46097.54288770833</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3507,13 +3521,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3521,15 +3535,15 @@
         <v>0</v>
       </c>
       <c r="T36" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B37" s="8">
         <v>46066.48845363426</v>
@@ -3541,7 +3555,7 @@
         <v>46126.807688877314</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3568,13 +3582,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3582,15 +3596,15 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46066.48845402778</v>
@@ -3602,7 +3616,7 @@
         <v>46114.52659163195</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3629,13 +3643,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3643,15 +3657,15 @@
         <v>0</v>
       </c>
       <c r="T38" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8">
         <v>46066.488454363425</v>
@@ -3663,16 +3677,16 @@
         <v>46157.62564773148</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I39" s="8">
         <v>46038</v>
@@ -3693,7 +3707,7 @@
         <v>99</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>99</v>
@@ -3716,7 +3730,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46066.48845471065</v>
@@ -3728,16 +3742,16 @@
         <v>46157.623435497684</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46038</v>
@@ -3755,13 +3769,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3769,15 +3783,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B41" s="8">
         <v>46066.48845502315</v>
@@ -3789,16 +3803,16 @@
         <v>46157.6235046875</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I41" s="8">
         <v>46058</v>
@@ -3816,13 +3830,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3830,15 +3844,15 @@
         <v>0</v>
       </c>
       <c r="T41" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46066.48845533565</v>
@@ -3850,16 +3864,16 @@
         <v>46157.62625247685</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I42" s="5">
         <v>46038</v>
@@ -3880,7 +3894,7 @@
         <v>99</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>99</v>
@@ -3895,15 +3909,15 @@
         <v>1</v>
       </c>
       <c r="T42" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
         <v>46066.48845152778</v>
@@ -3915,16 +3929,16 @@
         <v>46154.86717763889</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I43" s="8">
         <v>46038</v>
@@ -3942,13 +3956,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>93</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3956,15 +3970,15 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46066.488452164354</v>
@@ -3976,16 +3990,16 @@
         <v>46154.86724965277</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I44" s="5">
         <v>46078</v>
@@ -4003,13 +4017,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4017,15 +4031,15 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B45" s="8">
         <v>46066.48845261574</v>
@@ -4037,7 +4051,7 @@
         <v>46210.52808679398</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4061,7 +4075,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4078,7 +4092,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46070.75399846065</v>
@@ -4090,16 +4104,16 @@
         <v>46114.52642072916</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I46" s="5">
         <v>46036</v>
@@ -4117,13 +4131,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q46" s="5">
         <v>46036</v>
@@ -4143,7 +4157,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B47" s="8">
         <v>46066.48845297453</v>
@@ -4155,16 +4169,16 @@
         <v>46114.526663310186</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I47" s="8">
         <v>46091</v>
@@ -4182,13 +4196,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="8">
         <v>46091</v>
@@ -4208,7 +4222,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46091.64445680556</v>
@@ -4220,16 +4234,16 @@
         <v>46114.526705543976</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="5">
@@ -4245,13 +4259,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="5">
         <v>46098</v>
@@ -4271,7 +4285,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46091.6445032176</v>
@@ -4281,16 +4295,16 @@
         <v>46231.917933993056</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="8">
@@ -4306,13 +4320,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="8">
         <v>46183</v>
@@ -4327,12 +4341,12 @@
         <v>32</v>
       </c>
       <c r="U49" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46066.48845348379</v>
@@ -4344,7 +4358,7 @@
         <v>46230.56959944444</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4368,7 +4382,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4381,7 +4395,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B51" s="8">
         <v>46066.48845392361</v>
@@ -4393,16 +4407,16 @@
         <v>46157.625757002315</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I51" s="8">
         <v>46087</v>
@@ -4420,13 +4434,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="8">
         <v>46087</v>
@@ -4446,7 +4460,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46066.48845438658</v>
@@ -4458,16 +4472,16 @@
         <v>46157.6332940162</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I52" s="5">
         <v>46092</v>
@@ -4485,13 +4499,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q52" s="5">
         <v>46091</v>
@@ -4511,7 +4525,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B53" s="8">
         <v>46066.48845478009</v>
@@ -4523,7 +4537,7 @@
         <v>46209.91546185185</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4547,7 +4561,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4564,7 +4578,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B54" s="5">
         <v>46066.48845520834</v>
@@ -4576,16 +4590,16 @@
         <v>46195.69729675926</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I54" s="5">
         <v>46094</v>
@@ -4603,13 +4617,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q54" s="5">
         <v>46094</v>
@@ -4629,7 +4643,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B55" s="8">
         <v>46066.4884557176</v>
@@ -4641,16 +4655,16 @@
         <v>46211.525319189815</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I55" s="8">
         <v>46105</v>
@@ -4668,13 +4682,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q55" s="8">
         <v>46105</v>
@@ -4694,7 +4708,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B56" s="5">
         <v>46066.48845053241</v>
@@ -4706,16 +4720,16 @@
         <v>46211.57175387732</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -4733,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q56" s="5">
         <v>46125</v>
@@ -4759,7 +4773,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B57" s="8">
         <v>46066.488450902776</v>
@@ -4769,7 +4783,7 @@
         <v>46230.9102021875</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4793,7 +4807,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4806,7 +4820,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B58" s="5">
         <v>46066.48845119213</v>
@@ -4818,16 +4832,16 @@
         <v>46191.783308530095</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I58" s="5">
         <v>46154</v>
@@ -4845,13 +4859,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q58" s="5">
         <v>46154</v>
@@ -4863,7 +4877,7 @@
         <v>1</v>
       </c>
       <c r="T58" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U58" s="11" t="s">
         <v>33</v>
@@ -4871,7 +4885,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B59" s="8">
         <v>46066.488451446756</v>
@@ -4883,16 +4897,16 @@
         <v>46127.65513109954</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I59" s="8">
         <v>46091</v>
@@ -4910,13 +4924,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q59" s="8">
         <v>46091</v>
@@ -4936,7 +4950,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B60" s="5">
         <v>46066.48845172454</v>
@@ -4948,16 +4962,16 @@
         <v>46178.18717369213</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I60" s="5">
         <v>46176</v>
@@ -4975,13 +4989,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q60" s="5">
         <v>46176</v>
@@ -5001,7 +5015,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B61" s="8">
         <v>46066.48845202546</v>
@@ -5011,16 +5025,16 @@
         <v>46182.67990290509</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I61" s="8">
         <v>46146</v>
@@ -5038,13 +5052,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q61" s="8">
         <v>46146</v>
@@ -5056,15 +5070,15 @@
         <v>0</v>
       </c>
       <c r="T61" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B62" s="5">
         <v>46066.488452314814</v>
@@ -5076,16 +5090,16 @@
         <v>46230.91021270833</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I62" s="5">
         <v>46156</v>
@@ -5103,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q62" s="5">
         <v>46156</v>
@@ -5129,7 +5143,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B63" s="8">
         <v>46066.48845259259</v>
@@ -5139,7 +5153,7 @@
         <v>46230.91026372685</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5163,7 +5177,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5173,12 +5187,12 @@
       <c r="S63" s="9"/>
       <c r="T63" s="9"/>
       <c r="U63" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B64" s="5">
         <v>46066.48845287037</v>
@@ -5190,7 +5204,7 @@
         <v>46230.91012436342</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5217,13 +5231,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q64" s="5">
         <v>46125</v>
@@ -5235,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="T64" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="U64" s="11" t="s">
         <v>33</v>
@@ -5243,7 +5257,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B65" s="8">
         <v>46066.488453136575</v>
@@ -5255,7 +5269,7 @@
         <v>46230.91015710648</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5282,13 +5296,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q65" s="8">
         <v>46178</v>
@@ -5308,7 +5322,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B66" s="5">
         <v>46066.48845087963</v>
@@ -5320,7 +5334,7 @@
         <v>46230.91012434028</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5347,13 +5361,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q66" s="5">
         <v>46156</v>
@@ -5368,12 +5382,12 @@
         <v>32</v>
       </c>
       <c r="U66" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B67" s="8">
         <v>46066.4884515625</v>
@@ -5385,7 +5399,7 @@
         <v>46230.91012446759</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5412,13 +5426,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q67" s="8">
         <v>46160</v>
@@ -5433,12 +5447,12 @@
         <v>32</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B68" s="5">
         <v>46066.488451909725</v>
@@ -5450,7 +5464,7 @@
         <v>46230.910257662035</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5477,13 +5491,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q68" s="5">
         <v>46162</v>
@@ -5503,7 +5517,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B69" s="8">
         <v>46066.48845236111</v>
@@ -5515,7 +5529,7 @@
         <v>46230.91029408565</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5540,13 +5554,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q69" s="8">
         <v>46182</v>
@@ -5566,7 +5580,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B70" s="5">
         <v>46066.488452777776</v>
@@ -5576,7 +5590,7 @@
         <v>46223.81721487269</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5601,13 +5615,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q70" s="5">
         <v>46184</v>
@@ -5622,12 +5636,12 @@
         <v>32</v>
       </c>
       <c r="U70" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B71" s="8">
         <v>46066.48845318287</v>
@@ -5637,7 +5651,7 @@
         <v>46091.65141318287</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5661,7 +5675,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5674,7 +5688,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B72" s="5">
         <v>46066.488453541664</v>
@@ -5684,16 +5698,16 @@
         <v>46212.627884490736</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I72" s="5">
         <v>46185</v>
@@ -5711,13 +5725,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q72" s="5">
         <v>46184</v>
@@ -5732,22 +5746,22 @@
         <v>32</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B73" s="8">
         <v>46066.48845391204</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46223.817302129624</v>
+        <v>46233.52146012732</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5774,13 +5788,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q73" s="8">
         <v>46189</v>
@@ -5795,12 +5809,12 @@
         <v>32</v>
       </c>
       <c r="U73" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B74" s="5">
         <v>46066.48845425926</v>
@@ -5810,16 +5824,16 @@
         <v>46212.627920659725</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I74" s="5">
         <v>46191</v>
@@ -5837,13 +5851,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q74" s="5">
         <v>46190</v>
@@ -5858,12 +5872,12 @@
         <v>32</v>
       </c>
       <c r="U74" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B75" s="8">
         <v>46066.4884545949</v>
@@ -5873,16 +5887,16 @@
         <v>46212.627943680556</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I75" s="8">
         <v>46192</v>
@@ -5900,13 +5914,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q75" s="8">
         <v>46191</v>
@@ -5921,12 +5935,12 @@
         <v>32</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B76" s="5">
         <v>46066.488451261575</v>
@@ -5936,7 +5950,7 @@
         <v>46091.6514128125</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5960,7 +5974,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5973,7 +5987,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B77" s="8">
         <v>46066.4884515625</v>
@@ -5983,16 +5997,16 @@
         <v>46203.19655709491</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I77" s="8">
         <v>46195</v>
@@ -6010,13 +6024,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q77" s="8">
         <v>46192</v>
@@ -6031,12 +6045,12 @@
         <v>32</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B78" s="5">
         <v>46066.48845186342</v>
@@ -6046,16 +6060,16 @@
         <v>46203.19655721065</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I78" s="5">
         <v>46195</v>
@@ -6073,13 +6087,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q78" s="5">
         <v>46192</v>
@@ -6094,12 +6108,12 @@
         <v>32</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B79" s="8">
         <v>46091.64460730324</v>
@@ -6109,7 +6123,7 @@
         <v>46091.65200450231</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6133,7 +6147,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6144,15 +6158,15 @@
         <v>0</v>
       </c>
       <c r="T79" s="11" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B80" s="5">
         <v>46091.64498898148</v>
@@ -6162,7 +6176,7 @@
         <v>46204.19897075232</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6189,13 +6203,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q80" s="5">
         <v>46195</v>
@@ -6210,12 +6224,12 @@
         <v>32</v>
       </c>
       <c r="U80" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B81" s="8">
         <v>46091.64515803241</v>
@@ -6225,7 +6239,7 @@
         <v>46213.17280854167</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6252,13 +6266,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q81" s="8">
         <v>46204</v>
@@ -6273,7 +6287,7 @@
         <v>32</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -4290,9 +4290,11 @@
       <c r="B49" s="8">
         <v>46091.6445032176</v>
       </c>
-      <c r="C49" s="9"/>
+      <c r="C49" s="8">
+        <v>46237.55433462963</v>
+      </c>
       <c r="D49" s="8">
-        <v>46231.917933993056</v>
+        <v>46237.554351122686</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>
@@ -4335,13 +4337,13 @@
         <v>46183</v>
       </c>
       <c r="S49" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U49" s="12" t="s">
-        <v>107</v>
+      <c r="U49" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -5148,9 +5150,11 @@
       <c r="B63" s="8">
         <v>46066.48845259259</v>
       </c>
-      <c r="C63" s="9"/>
+      <c r="C63" s="8">
+        <v>46237.55431190973</v>
+      </c>
       <c r="D63" s="8">
-        <v>46230.91026372685</v>
+        <v>46237.5543227662</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>231</v>
@@ -5184,10 +5188,12 @@
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
-      <c r="S63" s="9"/>
+      <c r="S63" s="9">
+        <v>1</v>
+      </c>
       <c r="T63" s="9"/>
-      <c r="U63" s="12" t="s">
-        <v>107</v>
+      <c r="U63" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5331,7 +5337,7 @@
         <v>46197.590047060185</v>
       </c>
       <c r="D66" s="5">
-        <v>46230.91012434028</v>
+        <v>46237.515670775465</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>241</v>
@@ -5381,8 +5387,8 @@
       <c r="T66" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U66" s="12" t="s">
-        <v>107</v>
+      <c r="U66" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5396,7 +5402,7 @@
         <v>46209.79758950231</v>
       </c>
       <c r="D67" s="8">
-        <v>46230.91012446759</v>
+        <v>46237.51572094907</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5446,8 +5452,8 @@
       <c r="T67" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U67" s="12" t="s">
-        <v>107</v>
+      <c r="U67" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5585,9 +5591,11 @@
       <c r="B70" s="5">
         <v>46066.488452777776</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46237.55429493055</v>
+      </c>
       <c r="D70" s="5">
-        <v>46223.81721487269</v>
+        <v>46237.55435168982</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>184</v>
@@ -5630,13 +5638,13 @@
         <v>46184</v>
       </c>
       <c r="S70" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U70" s="10" t="s">
-        <v>111</v>
+      <c r="U70" s="12" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5648,7 +5656,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46091.65141318287</v>
+        <v>46237.55424878473</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>254</v>
@@ -5695,7 +5703,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46212.627884490736</v>
+        <v>46237.55431125</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>252</v>
@@ -5745,8 +5753,8 @@
       <c r="T72" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U72" s="10" t="s">
-        <v>111</v>
+      <c r="U72" s="12" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5756,9 +5764,11 @@
       <c r="B73" s="8">
         <v>46066.48845391204</v>
       </c>
-      <c r="C73" s="9"/>
+      <c r="C73" s="8">
+        <v>46237.554240625</v>
+      </c>
       <c r="D73" s="8">
-        <v>46233.52146012732</v>
+        <v>46237.55425512731</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>261</v>
@@ -5803,13 +5813,13 @@
         <v>46189</v>
       </c>
       <c r="S73" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U73" s="10" t="s">
-        <v>111</v>
+      <c r="U73" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5821,7 +5831,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46212.627920659725</v>
+        <v>46237.55425744213</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5871,8 +5881,8 @@
       <c r="T74" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U74" s="10" t="s">
-        <v>111</v>
+      <c r="U74" s="12" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="281">
   <si>
     <t>50001506 - ZCO EPM FRIO AIRE</t>
   </si>
@@ -826,7 +826,7 @@
     <t>ot 4221- 4222-4223Despacho</t>
   </si>
   <si>
-    <t>Costos,Gestion,Instalación Componentes</t>
+    <t>Costos,Gestion</t>
   </si>
   <si>
     <t>1213263336252680</t>
@@ -835,9 +835,6 @@
     <t>Cierre proyecto</t>
   </si>
   <si>
-    <t>Costos,Gestion</t>
-  </si>
-  <si>
     <t>1213263336252681</t>
   </si>
   <si>
@@ -857,30 +854,6 @@
   </si>
   <si>
     <t>Gestion</t>
-  </si>
-  <si>
-    <t>1213595645393034</t>
-  </si>
-  <si>
-    <t>Puesta en Marcha Servicios</t>
-  </si>
-  <si>
-    <t>Instalación Componentes,Pruebas Instalación Componentes</t>
-  </si>
-  <si>
-    <t>1213595645393036</t>
-  </si>
-  <si>
-    <t>Instalación Componentes</t>
-  </si>
-  <si>
-    <t>Pruebas Instalación Componentes,Puesta en Marcha Servicios</t>
-  </si>
-  <si>
-    <t>1213595645393038</t>
-  </si>
-  <si>
-    <t>Pruebas Instalación Componentes</t>
   </si>
 </sst>
 </file>
@@ -1404,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U81"/>
+  <dimension ref="A1:U78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -5894,7 +5867,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46212.627943680556</v>
+        <v>46240.719684895834</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>270</v>
@@ -5984,7 +5957,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5997,7 +5970,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B77" s="8">
         <v>46066.4884515625</v>
@@ -6007,16 +5980,16 @@
         <v>46203.19655709491</v>
       </c>
       <c r="E77" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
+      <c r="H77" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="I77" s="8">
         <v>46195</v>
@@ -6037,7 +6010,7 @@
         <v>273</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>273</v>
@@ -6060,7 +6033,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B78" s="5">
         <v>46066.48845186342</v>
@@ -6070,16 +6043,16 @@
         <v>46203.19655721065</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="I78" s="5">
         <v>46195</v>
@@ -6118,185 +6091,6 @@
         <v>32</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="B79" s="8">
-        <v>46091.64460730324</v>
-      </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="8">
-        <v>46091.65200450231</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="9"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
-      <c r="K79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O79" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q79" s="9"/>
-      <c r="R79" s="9"/>
-      <c r="S79" s="9">
-        <v>0</v>
-      </c>
-      <c r="T79" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="U79" s="10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B80" s="5">
-        <v>46091.64498898148</v>
-      </c>
-      <c r="C80" s="6"/>
-      <c r="D80" s="5">
-        <v>46204.19897075232</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I80" s="5">
-        <v>46195</v>
-      </c>
-      <c r="J80" s="5">
-        <v>46203</v>
-      </c>
-      <c r="K80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>46195</v>
-      </c>
-      <c r="R80" s="5">
-        <v>46203</v>
-      </c>
-      <c r="S80" s="6">
-        <v>0</v>
-      </c>
-      <c r="T80" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U80" s="10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="B81" s="8">
-        <v>46091.64515803241</v>
-      </c>
-      <c r="C81" s="9"/>
-      <c r="D81" s="8">
-        <v>46213.17280854167</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I81" s="8">
-        <v>46204</v>
-      </c>
-      <c r="J81" s="8">
-        <v>46212</v>
-      </c>
-      <c r="K81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="O81" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="P81" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q81" s="8">
-        <v>46204</v>
-      </c>
-      <c r="R81" s="8">
-        <v>46212</v>
-      </c>
-      <c r="S81" s="9">
-        <v>0</v>
-      </c>
-      <c r="T81" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U81" s="10" t="s">
         <v>111</v>
       </c>
     </row>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -4267,7 +4267,7 @@
         <v>46237.55433462963</v>
       </c>
       <c r="D49" s="8">
-        <v>46237.554351122686</v>
+        <v>46247.86292730324</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>180</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -157,6 +157,9 @@
     <t>Ingenieria electrica,Revision tableros pruebas</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1213263333570153</t>
   </si>
   <si>
@@ -332,9 +335,6 @@
   </si>
   <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1213263333570170</t>
@@ -1850,7 +1850,7 @@
         <v>46233.52146950232</v>
       </c>
       <c r="D10" s="5">
-        <v>46233.52148277778</v>
+        <v>46251.62699929398</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1888,13 +1888,13 @@
         <v>1</v>
       </c>
       <c r="T10" s="6"/>
-      <c r="U10" s="11" t="s">
-        <v>33</v>
+      <c r="U10" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="8">
         <v>46066.488451296296</v>
@@ -1906,16 +1906,16 @@
         <v>46097.54323589121</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I11" s="8">
         <v>46027</v>
@@ -1939,7 +1939,7 @@
         <v>41</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q11" s="8">
         <v>46027</v>
@@ -1959,28 +1959,28 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5">
         <v>46066.48845153935</v>
       </c>
       <c r="C12" s="5">
-        <v>46233.52145454861</v>
+        <v>46251.626983587965</v>
       </c>
       <c r="D12" s="5">
-        <v>46233.521690381946</v>
+        <v>46251.626985254625</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I12" s="5">
         <v>46149</v>
@@ -2001,10 +2001,10 @@
         <v>46</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q12" s="5">
         <v>46149</v>
@@ -2024,7 +2024,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" s="8">
         <v>46066.488451770834</v>
@@ -2036,7 +2036,7 @@
         <v>46233.52170266204</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2060,7 +2060,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2077,7 +2077,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" s="5">
         <v>46066.48845050926</v>
@@ -2089,7 +2089,7 @@
         <v>46097.54272628472</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2116,13 +2116,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>41</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q14" s="5">
         <v>46027</v>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" s="8">
         <v>46066.48845109953</v>
@@ -2154,7 +2154,7 @@
         <v>46113.56808707176</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2181,13 +2181,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>41</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q15" s="8">
         <v>46027</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="5">
         <v>46066.48845135416</v>
@@ -2219,7 +2219,7 @@
         <v>46114.52533150463</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2246,13 +2246,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>41</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q16" s="5">
         <v>46027</v>
@@ -2272,7 +2272,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="8">
         <v>46066.48845160879</v>
@@ -2284,7 +2284,7 @@
         <v>46114.525341712964</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -2311,13 +2311,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q17" s="8">
         <v>46027</v>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="5">
         <v>46066.48845217592</v>
@@ -2349,7 +2349,7 @@
         <v>46167.553930208334</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2373,7 +2373,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>26</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="8">
         <v>46066.48845243055</v>
@@ -2402,7 +2402,7 @@
         <v>46097.542820752315</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2429,13 +2429,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q19" s="8">
         <v>46029</v>
@@ -2455,7 +2455,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46066.48845268518</v>
@@ -2467,7 +2467,7 @@
         <v>46114.52558519676</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2494,13 +2494,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="5">
         <v>46036</v>
@@ -2520,7 +2520,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" s="8">
         <v>46066.48845292824</v>
@@ -2532,7 +2532,7 @@
         <v>46097.54333050926</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -2559,13 +2559,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="8">
         <v>46030</v>
@@ -2585,7 +2585,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46066.488453171296</v>
@@ -2597,16 +2597,16 @@
         <v>46223.81708695602</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I22" s="5">
         <v>46036</v>
@@ -2624,13 +2624,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q22" s="5">
         <v>46036</v>
@@ -2650,7 +2650,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="8">
         <v>46066.48844994213</v>
@@ -2662,7 +2662,7 @@
         <v>46114.525521250005</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2689,13 +2689,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q23" s="8">
         <v>46036</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46066.4884502662</v>
@@ -2727,16 +2727,16 @@
         <v>46223.81708303241</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I24" s="5">
         <v>46036</v>
@@ -2754,13 +2754,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="5">
         <v>46036</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B25" s="8">
         <v>46066.48845053241</v>
@@ -2792,7 +2792,7 @@
         <v>46184.576358645834</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2816,7 +2816,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2831,7 +2831,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>46066.48845078704</v>
@@ -2843,16 +2843,16 @@
         <v>46128.62625043982</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I26" s="5">
         <v>46038</v>
@@ -2870,13 +2870,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="5">
         <v>46038</v>
@@ -2888,10 +2888,10 @@
         <v>1</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U26" s="12" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -2914,10 +2914,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I27" s="8">
         <v>46038</v>
@@ -2935,10 +2935,10 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>110</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U27" s="10" t="s">
         <v>111</v>
@@ -2975,10 +2975,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I28" s="5">
         <v>46042</v>
@@ -2996,7 +2996,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>109</v>
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U28" s="10" t="s">
         <v>111</v>
@@ -3036,10 +3036,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I29" s="8">
         <v>46034</v>
@@ -3057,13 +3057,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>117</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q29" s="8">
         <v>46034</v>
@@ -3101,10 +3101,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I30" s="5">
         <v>46034</v>
@@ -3125,7 +3125,7 @@
         <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>121</v>
@@ -3136,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U30" s="10" t="s">
         <v>111</v>
@@ -3160,10 +3160,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I31" s="8">
         <v>46043</v>
@@ -3195,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U31" s="10" t="s">
         <v>111</v>
@@ -3221,10 +3221,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I32" s="5">
         <v>46041</v>
@@ -3242,13 +3242,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>127</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q32" s="5">
         <v>46038</v>
@@ -3286,10 +3286,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I33" s="8">
         <v>46041</v>
@@ -3310,7 +3310,7 @@
         <v>126</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>130</v>
@@ -3321,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U33" s="10" t="s">
         <v>111</v>
@@ -3347,10 +3347,10 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I34" s="5">
         <v>46042</v>
@@ -3382,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U34" s="10" t="s">
         <v>111</v>
@@ -3408,10 +3408,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I35" s="8">
         <v>46031</v>
@@ -3429,13 +3429,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>136</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q35" s="8">
         <v>46031</v>
@@ -3473,10 +3473,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I36" s="5">
         <v>46031</v>
@@ -3497,7 +3497,7 @@
         <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>139</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U36" s="10" t="s">
         <v>111</v>
@@ -3534,10 +3534,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I37" s="8">
         <v>46052</v>
@@ -3569,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U37" s="10" t="s">
         <v>111</v>
@@ -3595,10 +3595,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I38" s="5">
         <v>46052</v>
@@ -3630,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U38" s="10" t="s">
         <v>111</v>
@@ -3677,13 +3677,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>150</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q39" s="8">
         <v>46038</v>
@@ -3745,7 +3745,7 @@
         <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>153</v>
@@ -3756,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U40" s="10" t="s">
         <v>111</v>
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U41" s="10" t="s">
         <v>111</v>
@@ -3864,13 +3864,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>159</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q42" s="5">
         <v>46038</v>
@@ -3882,7 +3882,7 @@
         <v>1</v>
       </c>
       <c r="T42" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U42" s="10" t="s">
         <v>111</v>
@@ -3932,7 +3932,7 @@
         <v>158</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>162</v>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U43" s="10" t="s">
         <v>111</v>
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U44" s="10" t="s">
         <v>111</v>
@@ -4107,7 +4107,7 @@
         <v>167</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>168</v>
@@ -4852,7 +4852,7 @@
         <v>1</v>
       </c>
       <c r="T58" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U58" s="11" t="s">
         <v>33</v>
@@ -5000,7 +5000,7 @@
         <v>46182.67990290509</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -5045,10 +5045,10 @@
         <v>0</v>
       </c>
       <c r="T61" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5189,10 +5189,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I64" s="5">
         <v>46127</v>
@@ -5254,10 +5254,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I65" s="8">
         <v>46178</v>
@@ -5319,10 +5319,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I66" s="5">
         <v>46156</v>
@@ -5384,10 +5384,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I67" s="8">
         <v>46160</v>
@@ -5449,10 +5449,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I68" s="5">
         <v>46162</v>
@@ -5514,10 +5514,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5577,10 +5577,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5617,7 +5617,7 @@
         <v>32</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5727,7 +5727,7 @@
         <v>32</v>
       </c>
       <c r="U72" s="12" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5741,7 +5741,7 @@
         <v>46237.554240625</v>
       </c>
       <c r="D73" s="8">
-        <v>46237.55425512731</v>
+        <v>46251.62698818287</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>261</v>
@@ -5750,10 +5750,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I73" s="8">
         <v>46188</v>
@@ -5855,7 +5855,7 @@
         <v>32</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="282">
   <si>
     <t>50001506 - ZCO EPM FRIO AIRE</t>
   </si>
@@ -824,6 +824,10 @@
   </si>
   <si>
     <t>ot 4221- 4222-4223Despacho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESPACHO PARCIAL. 
+FALTA TABLERO PLC POR COMPONENTE PENDIENTE. </t>
   </si>
   <si>
     <t>Costos,Gestion</t>
@@ -1968,7 +1972,7 @@
         <v>46251.626983587965</v>
       </c>
       <c r="D12" s="5">
-        <v>46251.626985254625</v>
+        <v>46252.606471701394</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2018,8 +2022,8 @@
       <c r="T12" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U12" s="11" t="s">
-        <v>33</v>
+      <c r="U12" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -4753,9 +4757,11 @@
       <c r="B57" s="8">
         <v>46066.488450902776</v>
       </c>
-      <c r="C57" s="9"/>
+      <c r="C57" s="8">
+        <v>46252.60656390047</v>
+      </c>
       <c r="D57" s="8">
-        <v>46230.9102021875</v>
+        <v>46252.60656517361</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>186</v>
@@ -4789,9 +4795,13 @@
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
-      <c r="S57" s="9"/>
+      <c r="S57" s="9">
+        <v>1</v>
+      </c>
       <c r="T57" s="9"/>
-      <c r="U57" s="9"/>
+      <c r="U57" s="11" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
@@ -4995,9 +5005,11 @@
       <c r="B61" s="8">
         <v>46066.48845202546</v>
       </c>
-      <c r="C61" s="9"/>
+      <c r="C61" s="8">
+        <v>46252.60645265046</v>
+      </c>
       <c r="D61" s="8">
-        <v>46182.67990290509</v>
+        <v>46252.60647239583</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>58</v>
@@ -5042,13 +5054,13 @@
         <v>46147</v>
       </c>
       <c r="S61" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="U61" s="12" t="s">
-        <v>48</v>
+      <c r="U61" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -5629,7 +5641,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46237.55424878473</v>
+        <v>46252.60605559028</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>254</v>
@@ -5674,9 +5686,11 @@
       <c r="B72" s="5">
         <v>46066.488453541664</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46252.60602412037</v>
+      </c>
       <c r="D72" s="5">
-        <v>46237.55431125</v>
+        <v>46252.60604236111</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>252</v>
@@ -5721,13 +5735,13 @@
         <v>46184</v>
       </c>
       <c r="S72" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U72" s="12" t="s">
-        <v>48</v>
+      <c r="U72" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5741,7 +5755,7 @@
         <v>46237.554240625</v>
       </c>
       <c r="D73" s="8">
-        <v>46251.62698818287</v>
+        <v>46252.6060424537</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>261</v>
@@ -5791,8 +5805,8 @@
       <c r="T73" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U73" s="11" t="s">
-        <v>33</v>
+      <c r="U73" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5802,9 +5816,11 @@
       <c r="B74" s="5">
         <v>46066.48845425926</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46252.60604829861</v>
+      </c>
       <c r="D74" s="5">
-        <v>46237.55425744213</v>
+        <v>46252.60606318287</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5849,13 +5865,13 @@
         <v>46190</v>
       </c>
       <c r="S74" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U74" s="12" t="s">
-        <v>48</v>
+      <c r="U74" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5867,7 +5883,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46240.719684895834</v>
+        <v>46252.606286180555</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>270</v>
@@ -5891,7 +5907,7 @@
         <v>26</v>
       </c>
       <c r="L75" s="9" t="s">
-        <v>26</v>
+        <v>271</v>
       </c>
       <c r="M75" s="9" t="s">
         <v>26</v>
@@ -5903,7 +5919,7 @@
         <v>265</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q75" s="8">
         <v>46191</v>
@@ -5917,13 +5933,13 @@
       <c r="T75" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="U75" s="10" t="s">
-        <v>111</v>
+      <c r="U75" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B76" s="5">
         <v>46066.488451261575</v>
@@ -5933,7 +5949,7 @@
         <v>46091.6514128125</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5957,7 +5973,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5970,7 +5986,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B77" s="8">
         <v>46066.4884515625</v>
@@ -5980,16 +5996,16 @@
         <v>46203.19655709491</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I77" s="8">
         <v>46195</v>
@@ -6007,13 +6023,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q77" s="8">
         <v>46192</v>
@@ -6033,7 +6049,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B78" s="5">
         <v>46066.48845186342</v>
@@ -6043,16 +6059,16 @@
         <v>46203.19655721065</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I78" s="5">
         <v>46195</v>
@@ -6070,13 +6086,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q78" s="5">
         <v>46192</v>

--- a/data/50001506 - ZCO EPM FRIO AIRE.xlsx
+++ b/data/50001506 - ZCO EPM FRIO AIRE.xlsx
@@ -4513,7 +4513,7 @@
         <v>46209.915449293985</v>
       </c>
       <c r="D53" s="8">
-        <v>46209.91546185185</v>
+        <v>46271.67208599537</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>199</v>
